--- a/docs/qc/MoSJE-Portal-QC-Tracker.xlsx
+++ b/docs/qc/MoSJE-Portal-QC-Tracker.xlsx
@@ -20065,7 +20065,7 @@
       </c>
       <c r="F6" s="28" t="inlineStr">
         <is>
-          <t>Restore the library's Icon Button - 32x32, 1px #E5E7EB, radius 8 - and set the edit glyph to #003366. One icon treatment has to hold across every screen - the same glyph set, the same button, the same two colours - rather than icon-buttons on some screens, amber glyphs on others and text buttons on three of the NAPDDR screens.  (Anchor: The row-action controls are icon-only buttons with no text node, so the extraction does not record them. The box is measured off the capture at the Actions column, x1305-1425 on the first data row, where the two glyphs are drawn.)</t>
+          <t>Restore the library's Icon Button - 32x32, 1px #E5E7EB, radius 8 - and set the edit glyph to #003366. One icon treatment has to hold across every screen - the same glyph set, the same button, the same two colours - rather than icon-buttons on some screens, amber glyphs on others and text buttons on three of the NAPDDR screens.</t>
         </is>
       </c>
       <c r="G6" s="28" t="inlineStr">
@@ -20301,7 +20301,7 @@
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>Build the table to the design's own component: a radius-12 container, a 52px #F9FAFB header band padded 16/24, 56px data cells padded 12/24, and a #F3F4F6 row rule. This is the finding the other table findings hang off - NMB-GLOBAL-009 (row heights), NMB-GLOBAL-010 (cell colour), NMB-GLOBAL-005 (row actions), NMB-GLOBAL-019 (the extra wrapper), NMB-GLOBAL-036 (a column too narrow for its date) and NMB-SCREEN-030 (action order). The cell padding alone accounts for most of the height difference, so fixing it fixes -009 across the portal.  (Anchor: GATE 3 flagged this one, correctly and usefully: the finding is about a header BAND, and the anchor resolves to an element with no background. That is not the resolver landing beside the band - it is the finding. The build's header has no fill at all, which is why there is no band to anchor to; the anchor is the header cell itself, and its transparency is the evidence.)</t>
+          <t>Build the table to the design's own component: a radius-12 container, a 52px #F9FAFB header band padded 16/24, 56px data cells padded 12/24, and a #F3F4F6 row rule. This is the finding the other table findings hang off - NMB-GLOBAL-009 (row heights), NMB-GLOBAL-010 (cell colour), NMB-GLOBAL-005 (row actions), NMB-GLOBAL-035 (the extra wrapper), NMB-GLOBAL-036 (a column too narrow for its date) and NMB-SCREEN-030 (action order). The cell padding alone accounts for most of the height difference, so fixing it fixes -009 across the portal.</t>
         </is>
       </c>
       <c r="G10" s="28" t="inlineStr">
@@ -20360,7 +20360,7 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Draw the National Emblem at the design's 32x52 in its designed position, and compose the co-branding from the two marks the design uses rather than one flattened picture - a single image cannot be scaled per breakpoint, cannot be themed, and gives a screen reader one long string where the design has two named marks. On the citizen shell the ministry name has to come back as text for the same reason, and more urgently: it is the department's own name, on a bilingual portal. Set the band's lower edge to #F3F4F6. Note that the emblem is the National Emblem of India: its proportions are not ours to adjust, and the estate's own rule is that it ships at 3x the largest surface that renders it rather than being scaled up from a smaller file.  (Anchor: The finding is about two MARKS - the National Emblem and the co-branding block - which are images with no text node, sitting 700px apart in the same band. The box is the band itself on both sides, measured off the captures, so the crop shows both marks and the reader can see the size difference rather than being told it.)</t>
+          <t>Draw the National Emblem at the design's 32x52 in its designed position, and compose the co-branding from the two marks the design uses rather than one flattened picture - a single image cannot be scaled per breakpoint, cannot be themed, and gives a screen reader one long string where the design has two named marks. On the citizen shell the ministry name has to come back as text for the same reason, and more urgently: it is the department's own name, on a bilingual portal. Set the band's lower edge to #F3F4F6. Note that the emblem is the National Emblem of India: its proportions are not ours to adjust, and the estate's own rule is that it ships at 3x the largest surface that renders it rather than being scaled up from a smaller file.</t>
         </is>
       </c>
       <c r="G11" s="28" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
-          <t>Remove the Poppins declaration - it is one rule and it is the only thing importing that family - and let the field inherit Noto Sans at 14px #374151. The estate's standing instruction is Noto Sans across all government properties and no other family introduced. While the rule is being changed, the box wants the design's 40px height and radius 8 rather than 43 and 6.  (Anchor: The field's placeholder text is already NMB-GLOBAL-008's anchor, and two findings must not share one box. The anchor here is the field's own measured rect on both sides - 938x40 in the design, 768x43 in the build - which is also the geometry half of the finding.)</t>
+          <t>Remove the Poppins declaration - it is one rule and it is the only thing importing that family - and let the field inherit Noto Sans at 14px #374151. The estate's standing instruction is Noto Sans across all government properties and no other family introduced. While the rule is being changed, the box wants the design's 40px height and radius 8 rather than 43 and 6.</t>
         </is>
       </c>
       <c r="G12" s="28" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>Skin these with the design-system select so their border, radius, type and chevron match the rest of the interface.  (Anchor: The control IS a native &lt;select&gt; and it carries no text node of its own - its value is rendered by the browser. The box is the select's own measured rect (x1271 y567, 63x31) from the capture.)</t>
+          <t>Skin these with the design-system select so their border, radius, type and chevron match the rest of the interface.</t>
         </is>
       </c>
       <c r="G15" s="28" t="inlineStr">
@@ -20828,7 +20828,7 @@
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Draw the tile at 32x32, radius 10, filled #E5EFF9. Reserve a coloured tint for a metric that genuinely signals a state, and take the tint from the token set when you do.  (Anchor: The icon tile is an SVG on a filled div with no text, so the extraction records neither. The tile's fill was sampled from the capture at x590-650 y240-290 and measures #FDE8EF against the design's #E5EFF9.)</t>
+          <t>Draw the tile at 32x32, radius 10, filled #E5EFF9. Reserve a coloured tint for a metric that genuinely signals a state, and take the tint from the token set when you do.</t>
         </is>
       </c>
       <c r="G19" s="28" t="inlineStr">
@@ -21005,7 +21005,7 @@
       </c>
       <c r="F22" s="28" t="inlineStr">
         <is>
-          <t>Box the current page only, leave the other numbers bare, and show the design's six pages before the ellipsis. This is the same pagination the hyphen and plus sign belong to (NMB-GLOBAL-006); fixing the glyphs without fixing the boxing leaves the reader still unable to see which page they are on.  (Anchor: The page-number boxes are buttons whose only text is the numeral, so a text anchor would bind to one numeral rather than to the strip the finding is about. The box is measured off the capture across the whole pager, x323-553 y758-798, which holds the hyphen, the four numbered boxes, the ellipsis and the plus.)</t>
+          <t>Box the current page only, leave the other numbers bare, and show the design's six pages before the ellipsis. This is the same pagination the hyphen and plus sign belong to (NMB-GLOBAL-006); fixing the glyphs without fixing the boxing leaves the reader still unable to see which page they are on.</t>
         </is>
       </c>
       <c r="G22" s="28" t="inlineStr">
@@ -21064,7 +21064,7 @@
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>Drop the outer panel and let the search row and the table sit on the page ground as the design does. Nothing else needs to move: both inner cards already carry their own border and radius.  (Anchor: The finding is about a container with no text of its own, and on the design side about the ABSENCE of one. Both boxes are measured off the captures over the same region - the search row and the top of the table. The claim itself was checked by sampling one pixel in the left gutter at x312 y250: #F9FAFB in the design, #FFFFFF in the build.)</t>
+          <t>Drop the outer panel and let the search row and the table sit on the page ground as the design does. Nothing else needs to move: both inner cards already carry their own border and radius.</t>
         </is>
       </c>
       <c r="G23" s="28" t="inlineStr">
@@ -21182,7 +21182,7 @@
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>Put the tile back on the right of the name and role, range the two text lines right, and set the role as the design does - no brackets, the quieter of the two weights.  (Anchor: The account name, role and initials are the signed-in user's own data, so the extraction masks them and records no text node. The box is measured off the capture at the right of the masthead, x1252-1432 y58-130, where the tile and the two lines are drawn.)</t>
+          <t>Put the tile back on the right of the name and role, range the two text lines right, and set the role as the design does - no brackets, the quieter of the two weights.</t>
         </is>
       </c>
       <c r="G25" s="28" t="inlineStr">
@@ -21413,12 +21413,12 @@
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>Figma: Several screens draw more filters than the build offers - the citizen dashboard's State and District selects, the admin list screens' 'All States/UTs', the officer dashboard's four-filter row.  →  Live: This is raised once, as a note: show the filters each screen actually needs and style them as the design does. It is not repeated as a finding on each screen.</t>
+          <t>Figma: Several screens draw more filters than the build offers - the citizen dashboard's State and District selects, the admin list screens' 'All States/UTs', the officer dashboard's four-filter row.  →  Live: Raised once, as a note: show the filters each screen actually needs and style them as the design does. It is deliberately not repeated as a finding on each screen.</t>
         </is>
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>This is raised once, as a note: show the filters each screen actually needs and style them as the design does. It is not repeated as a finding on each screen.</t>
+          <t>Show the filters each screen actually needs and style them as the design does.</t>
         </is>
       </c>
       <c r="G29" s="28" t="n"/>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
-          <t>Give the map the design's 640px column and its 768px height. With NMB-SCREEN-028's zoom fixed as well, a reader lands on their own district at a usable size instead of on south Asia in a small panel.  (Anchor: A map panel has no text node. The box is the panel's measured rect on each side - 640x768 in the design frame, 534x500 in the build - which is itself the finding, so the crop shows the two side by side at their real sizes.)</t>
+          <t>Give the map the design's 640px column and its 768px height. With NMB-SCREEN-028's zoom fixed as well, a reader lands on their own district at a usable size instead of on south Asia in a small panel.</t>
         </is>
       </c>
       <c r="G34" s="28" t="inlineStr">
@@ -21878,7 +21878,7 @@
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>Frame the map on the results being listed - the reader's district, or the search area - rather than on the whole set. Raised as a confirm-if-intended: if a national overview is the deliberate default, say so and the design should show it that way.  (Anchor: The map is a canvas with no text node. The box is the map panel's measured rect on both sides.)</t>
+          <t>Frame the map on the results being listed - the reader's district, or the search area - rather than on the whole set. Raised as a confirm-if-intended: if a national overview is the deliberate default, say so and the design should show it that way.</t>
         </is>
       </c>
       <c r="G37" s="28" t="inlineStr">
@@ -22350,7 +22350,7 @@
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>Point these links at the citizen site's pages, or give the shell a not-found state. A route with no page should say so rather than substituting the landing screen.  (Anchor: This finding is about which page a route serves, so there is no single control to anchor to; the anchor is the page title that proves it - /about-us renders the heading 'Dashboard'.)</t>
+          <t>Point these links at the citizen site's pages, or give the shell a not-found state. A route with no page should say so rather than substituting the landing screen.</t>
         </is>
       </c>
       <c r="G45" s="28" t="inlineStr">
@@ -22409,7 +22409,7 @@
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>Build the sheet as the design draws it: 520 wide, inset 16 from the window edges, radius 16, the #E5EFF9 edge and the two shadows, over a 50% #0A0D13 scrim. Set the title to 20px SemiBold #1F2937 and every label to 14px Medium #1F2937 - one label style for the whole form - over 44px inputs bound to #D1D5DB. The same sheet is used by Add Document, Add Best Practice, Add Event and Add Feedback, so this lands on eight designed flows at once.  (Anchor: The finding is about the SHEET - its size, its inset, its radius and the scrim behind it - and a sheet has no text node. The box is the sheet's top 300px on both sides, measured off the captures, so the crop shows the edge treatment and the title together rather than describing them.)</t>
+          <t>Build the sheet as the design draws it: 520 wide, inset 16 from the window edges, radius 16, the #E5EFF9 edge and the two shadows, over a 50% #0A0D13 scrim. Set the title to 20px SemiBold #1F2937 and every label to 14px Medium #1F2937 - one label style for the whole form - over 44px inputs bound to #D1D5DB. The same sheet is used by Add Document, Add Best Practice, Add Event and Add Feedback, so this lands on eight designed flows at once.</t>
         </is>
       </c>
       <c r="G46" s="28" t="inlineStr">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>Set the draft label to the design's #8C571F and the published label to #27682A. Red is the portal's error and destructive colour; spending it on a normal editorial state teaches readers to ignore it where it matters. This is NOT the withdrawn NMB-SCREEN-029, which was about the chip's CASE and was dropped on instruction - if the chip is out of scope entirely, drop this one too, but the colour is a different defect with a different fix.</t>
+          <t>Set the draft label to the design's #8C571F and the published label to #27682A. Red is the portal's error and destructive colour; spending it on a normal editorial state teaches readers to ignore it where it matters.</t>
         </is>
       </c>
       <c r="G48" s="28" t="inlineStr">

--- a/docs/qc/MoSJE-Portal-QC-Tracker.xlsx
+++ b/docs/qc/MoSJE-Portal-QC-Tracker.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Coverage – SMILE Beggary'!$A$1:$H$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NMBA'!$A$1:$M$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage – NMBA'!$A$1:$H$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MoSJE Website'!$A$1:$M$264</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MoSJE Website'!$A$1:$M$271</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NHAPOA'!$A$1:$M$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Coverage – NHAPOA'!$A$1:$H$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TG'!$A$1:$M$34</definedName>
@@ -9061,7 +9061,7 @@
         </is>
       </c>
       <c r="G2" s="28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H2" s="28" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="G3" s="28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H3" s="28" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="G4" s="28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H4" s="28" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         </is>
       </c>
       <c r="G5" s="28" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="28" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="G6" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H6" s="28" t="inlineStr"/>
     </row>
@@ -9249,7 +9249,7 @@
         </is>
       </c>
       <c r="G7" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H7" s="28" t="inlineStr"/>
     </row>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="G8" s="28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H8" s="28" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="G9" s="28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H9" s="28" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         </is>
       </c>
       <c r="G10" s="28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H10" s="28" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="G11" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H11" s="28" t="inlineStr"/>
     </row>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="G12" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H12" s="28" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         </is>
       </c>
       <c r="G13" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H13" s="28" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="G14" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H14" s="28" t="inlineStr"/>
     </row>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="G15" s="28" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H15" s="28" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="G16" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H16" s="28" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
         </is>
       </c>
       <c r="G17" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H17" s="28" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         </is>
       </c>
       <c r="G18" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H18" s="28" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         </is>
       </c>
       <c r="G19" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H19" s="28" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         </is>
       </c>
       <c r="G20" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H20" s="28" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         </is>
       </c>
       <c r="G21" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H21" s="28" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         </is>
       </c>
       <c r="G22" s="28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H22" s="28" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         </is>
       </c>
       <c r="G23" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H23" s="28" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         </is>
       </c>
       <c r="G24" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H24" s="28" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="G25" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H25" s="28" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         </is>
       </c>
       <c r="G26" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H26" s="28" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         </is>
       </c>
       <c r="G27" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H27" s="28" t="inlineStr"/>
     </row>
@@ -10061,7 +10061,7 @@
         </is>
       </c>
       <c r="G28" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H28" s="28" t="inlineStr">
         <is>
@@ -10101,7 +10101,7 @@
         </is>
       </c>
       <c r="G29" s="28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H29" s="28" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         </is>
       </c>
       <c r="G30" s="28" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H30" s="28" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="G32" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H32" s="28" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="G33" s="28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H33" s="28" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         </is>
       </c>
       <c r="G34" s="28" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H34" s="28" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         </is>
       </c>
       <c r="G35" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H35" s="28" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         </is>
       </c>
       <c r="G36" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H36" s="28" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         </is>
       </c>
       <c r="G37" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H37" s="28" t="inlineStr">
         <is>
@@ -10461,7 +10461,7 @@
         </is>
       </c>
       <c r="G38" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H38" s="28" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         </is>
       </c>
       <c r="G39" s="28" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H39" s="28" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         </is>
       </c>
       <c r="G40" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H40" s="28" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         </is>
       </c>
       <c r="G41" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H41" s="28" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         </is>
       </c>
       <c r="G42" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H42" s="28" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         </is>
       </c>
       <c r="G43" s="28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H43" s="28" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="G44" s="28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H44" s="28" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="G45" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H45" s="28" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="G46" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H46" s="28" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="G47" s="28" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H47" s="28" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="G48" s="28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H48" s="28" t="inlineStr">
         <is>
@@ -10901,7 +10901,7 @@
         </is>
       </c>
       <c r="G49" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H49" s="28" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         </is>
       </c>
       <c r="G50" s="28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H50" s="28" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="G51" s="28" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H51" s="28" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="G52" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H52" s="28" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="G53" s="28" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H53" s="28" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         </is>
       </c>
       <c r="G54" s="28" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H54" s="28" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         </is>
       </c>
       <c r="G55" s="28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H55" s="28" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         </is>
       </c>
       <c r="G56" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H56" s="28" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="G57" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H57" s="28" t="inlineStr">
         <is>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="G58" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H58" s="28" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="G59" s="28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H59" s="28" t="inlineStr"/>
     </row>
@@ -11333,7 +11333,7 @@
         </is>
       </c>
       <c r="G60" s="28" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H60" s="28" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         </is>
       </c>
       <c r="G61" s="28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H61" s="28" t="inlineStr"/>
     </row>
@@ -11405,7 +11405,7 @@
         </is>
       </c>
       <c r="G62" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H62" s="28" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         </is>
       </c>
       <c r="G63" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H63" s="28" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         </is>
       </c>
       <c r="G64" s="28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H64" s="28" t="inlineStr">
         <is>
@@ -11525,7 +11525,7 @@
         </is>
       </c>
       <c r="G65" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H65" s="28" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         </is>
       </c>
       <c r="G66" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H66" s="28" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         </is>
       </c>
       <c r="G67" s="28" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H67" s="28" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="G68" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H68" s="28" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         </is>
       </c>
       <c r="G69" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H69" s="28" t="inlineStr">
         <is>
@@ -11721,7 +11721,7 @@
         </is>
       </c>
       <c r="G70" s="28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H70" s="28" t="inlineStr"/>
     </row>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="G71" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H71" s="28" t="inlineStr"/>
     </row>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="G72" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H72" s="28" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         </is>
       </c>
       <c r="G73" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H73" s="28" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         </is>
       </c>
       <c r="G74" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H74" s="28" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         </is>
       </c>
       <c r="G75" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H75" s="28" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         </is>
       </c>
       <c r="G76" s="28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H76" s="28" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         </is>
       </c>
       <c r="G77" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H77" s="28" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         </is>
       </c>
       <c r="G78" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H78" s="28" t="inlineStr"/>
     </row>
@@ -12057,7 +12057,7 @@
         </is>
       </c>
       <c r="G79" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H79" s="28" t="inlineStr"/>
     </row>
@@ -12093,7 +12093,7 @@
         </is>
       </c>
       <c r="G80" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H80" s="28" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         </is>
       </c>
       <c r="G81" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H81" s="28" t="inlineStr"/>
     </row>
@@ -12161,7 +12161,7 @@
         </is>
       </c>
       <c r="G82" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H82" s="28" t="inlineStr"/>
     </row>
@@ -12193,7 +12193,7 @@
         </is>
       </c>
       <c r="G83" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H83" s="28" t="inlineStr"/>
     </row>
@@ -12225,7 +12225,7 @@
         </is>
       </c>
       <c r="G84" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H84" s="28" t="inlineStr"/>
     </row>
@@ -12257,7 +12257,7 @@
         </is>
       </c>
       <c r="G85" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H85" s="28" t="inlineStr"/>
     </row>
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="G86" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H86" s="28" t="inlineStr"/>
     </row>
@@ -12321,7 +12321,7 @@
         </is>
       </c>
       <c r="G87" s="28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H87" s="28" t="inlineStr"/>
     </row>
@@ -12357,7 +12357,7 @@
         </is>
       </c>
       <c r="G88" s="28" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H88" s="28" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="G89" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H89" s="28" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         </is>
       </c>
       <c r="G90" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H90" s="28" t="inlineStr"/>
     </row>
@@ -12465,7 +12465,7 @@
         </is>
       </c>
       <c r="G91" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H91" s="28" t="inlineStr"/>
     </row>
@@ -12501,7 +12501,7 @@
         </is>
       </c>
       <c r="G92" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H92" s="28" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         </is>
       </c>
       <c r="G93" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H93" s="28" t="inlineStr"/>
     </row>
@@ -12573,7 +12573,7 @@
         </is>
       </c>
       <c r="G94" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H94" s="28" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         </is>
       </c>
       <c r="G95" s="28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H95" s="28" t="inlineStr"/>
     </row>
@@ -12645,7 +12645,7 @@
         </is>
       </c>
       <c r="G96" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H96" s="28" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         </is>
       </c>
       <c r="G97" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H97" s="28" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="G98" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H98" s="28" t="inlineStr">
         <is>
@@ -12765,7 +12765,7 @@
         </is>
       </c>
       <c r="G99" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H99" s="28" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         </is>
       </c>
       <c r="G100" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H100" s="28" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         </is>
       </c>
       <c r="G101" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H101" s="28" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         </is>
       </c>
       <c r="G102" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H102" s="28" t="inlineStr">
         <is>
@@ -12925,7 +12925,7 @@
         </is>
       </c>
       <c r="G103" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H103" s="28" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         </is>
       </c>
       <c r="G104" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H104" s="28" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         </is>
       </c>
       <c r="G105" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H105" s="28" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         </is>
       </c>
       <c r="G106" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H106" s="28" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         </is>
       </c>
       <c r="G107" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H107" s="28" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         </is>
       </c>
       <c r="G108" s="28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H108" s="28" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         </is>
       </c>
       <c r="G109" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H109" s="28" t="inlineStr">
         <is>
@@ -13205,7 +13205,7 @@
         </is>
       </c>
       <c r="G110" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H110" s="28" t="inlineStr">
         <is>
@@ -13245,7 +13245,7 @@
         </is>
       </c>
       <c r="G111" s="28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H111" s="28" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         </is>
       </c>
       <c r="G112" s="28" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H112" s="28" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         </is>
       </c>
       <c r="G113" s="28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H113" s="28" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         </is>
       </c>
       <c r="G114" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H114" s="28" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         </is>
       </c>
       <c r="G115" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H115" s="28" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         </is>
       </c>
       <c r="G116" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H116" s="28" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         </is>
       </c>
       <c r="G117" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H117" s="28" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         </is>
       </c>
       <c r="G118" s="28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H118" s="28" t="inlineStr"/>
     </row>
@@ -13553,7 +13553,7 @@
         </is>
       </c>
       <c r="G119" s="28" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H119" s="28" t="inlineStr"/>
     </row>
@@ -13589,7 +13589,7 @@
         </is>
       </c>
       <c r="G120" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H120" s="28" t="inlineStr">
         <is>
@@ -13629,7 +13629,7 @@
         </is>
       </c>
       <c r="G121" s="28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H121" s="28" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M264"/>
+  <dimension ref="A1:M271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -33270,17 +33270,17 @@
     <row r="2">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-008</t>
+          <t>WEB-GLOBAL-001</t>
         </is>
       </c>
       <c r="B2" s="28" t="inlineStr">
         <is>
-          <t>Global · No visible focus indicator — Open the accessibility option</t>
+          <t>Global · Automated accessibility violation — aria-valid-attr-value</t>
         </is>
       </c>
       <c r="C2" s="28" t="inlineStr">
         <is>
-          <t>Components &amp; States</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D2" s="28" t="inlineStr">
@@ -33290,18 +33290,18 @@
       </c>
       <c r="E2" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (2.4.7): every keyboard-focusable control shows a visible focus indicator. DBIM and UX4G both draw a 4px ring.  →  Live: Tab stop 1 (button#open-the-accessibility-menu, “Open the accessibility option”) shows no visible change when focused — outline, box-shadow, border, background and colour are identical focused and unfocused. Measured on 142 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: ARIA attributes must conform to valid values — &lt;th class="sorting sorting_asc" tabindex="0" aria-controls="dataTable1" rowspan="1" colspan="1" aria-sort="ascending" aria-label="#: activate to sort column des (aria-valid-attr-value, wcag2a, wcag412). Measured on 15 pages.</t>
         </is>
       </c>
       <c r="F2" s="28" t="inlineStr">
         <is>
-          <t>Give the control a visible focus style — the estate's 4px ring — and make sure it is not removed by an `outline: none` elsewhere in the stylesheet.</t>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
         </is>
       </c>
       <c r="G2" s="28" t="n"/>
       <c r="H2" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/about-the-division/</t>
+          <t>https://www.dosje.gov.in/about-the-division-social-defence/</t>
         </is>
       </c>
       <c r="I2" s="28" t="inlineStr">
@@ -33325,12 +33325,12 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-078</t>
+          <t>WEB-GLOBAL-007</t>
         </is>
       </c>
       <c r="B3" s="28" t="inlineStr">
         <is>
-          <t>Global · Non-text control below 3:1 — Language Translator</t>
+          <t>Global · Text contrast below AA — Single Access Mechanism for All Verticals o…</t>
         </is>
       </c>
       <c r="C3" s="28" t="inlineStr">
@@ -33345,18 +33345,18 @@
       </c>
       <c r="E3" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.11): the visible part of a control — its icon, its outline, its indicator — needs 3:1 against what is behind it.  →  Live: Text “Language Translator” (button.bhashini-dropdown-btn) renders #0373DF on #0373DF at 14px/400 — measured on the capture's pixels: #A3CCF3 on #0373DF is 2.76:1 against the 3.0:1 minimum. Measured on 129 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Single Access Mechanism for All Verticals of Empowerment &amp; Social Har…” (p.elementor-heading-title) renders #FFFFFF on #F97316 at 16px/400 — #FFFFFF on #F97316 as painted on the capture: 2.8:1 against the 4.5:1 minimum. Measured on 10 pages.</t>
         </is>
       </c>
       <c r="F3" s="28" t="inlineStr">
         <is>
-          <t>Darken the icon or its ground until the pair reaches 3:1. The control's accessible name is already correct; only what is drawn needs changing.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G3" s="28" t="n"/>
       <c r="H3" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/about-the-division/</t>
+          <t>https://www.dosje.gov.in/</t>
         </is>
       </c>
       <c r="I3" s="28" t="inlineStr">
@@ -33380,17 +33380,17 @@
     <row r="4">
       <c r="A4" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-001</t>
+          <t>WEB-GLOBAL-086</t>
         </is>
       </c>
       <c r="B4" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — aria-valid-attr-value</t>
+          <t>Global · No visible focus indicator — Pagination page numbers</t>
         </is>
       </c>
       <c r="C4" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Components &amp; States</t>
         </is>
       </c>
       <c r="D4" s="28" t="inlineStr">
@@ -33400,18 +33400,18 @@
       </c>
       <c r="E4" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: ARIA attributes must conform to valid values — &lt;th class="sorting sorting_asc" tabindex="0" aria-controls="dataTable1" rowspan="1" colspan="1" aria-sort="ascending" aria-label="#: activate to sort column des (aria-valid-attr-value, wcag2a, wcag412). Measured on 15 pages.</t>
+          <t>Figma: WCAG 2.2 AA (2.4.7): every keyboard-focusable control shows a visible focus indicator. DBIM and UX4G both draw a 4px ring.  →  Live: Pagination page numbers: screenshotted focused and then blurred, no pixel changes, so a keyboard user cannot see where focus is. Measured on 9 pages.</t>
         </is>
       </c>
       <c r="F4" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+          <t>Give the control a visible focus style — the estate's 4px ring — and make sure it is not removed by an `outline: none` elsewhere in the stylesheet.</t>
         </is>
       </c>
       <c r="G4" s="28" t="n"/>
       <c r="H4" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/about-the-division-social-defence/</t>
+          <t>https://www.dosje.gov.in/annual-reports/</t>
         </is>
       </c>
       <c r="I4" s="28" t="inlineStr">
@@ -33435,17 +33435,17 @@
     <row r="5">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-007</t>
+          <t>WEB-GLOBAL-085</t>
         </is>
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Single Access Mechanism for All Verticals o…</t>
+          <t>Global · No visible focus indicator — Pagination previous / next arrows</t>
         </is>
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Components &amp; States</t>
         </is>
       </c>
       <c r="D5" s="28" t="inlineStr">
@@ -33455,18 +33455,18 @@
       </c>
       <c r="E5" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Single Access Mechanism for All Verticals of Empowerment &amp; Social Har…” (p.elementor-heading-title) renders #FFFFFF on #F97316 at 16px/400 — measured on the capture's pixels: #FFFFFF on #F97316 is 2.8:1 against the 4.5:1 minimum. Measured on 11 pages.</t>
+          <t>Figma: WCAG 2.2 AA (2.4.7): every keyboard-focusable control shows a visible focus indicator. DBIM and UX4G both draw a 4px ring.  →  Live: Pagination previous / next arrows: screenshotted focused and then blurred, no pixel changes, so a keyboard user cannot see where focus is. Measured on 9 pages.</t>
         </is>
       </c>
       <c r="F5" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Give the control a visible focus style — the estate's 4px ring — and make sure it is not removed by an `outline: none` elsewhere in the stylesheet.</t>
         </is>
       </c>
       <c r="G5" s="28" t="n"/>
       <c r="H5" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/</t>
+          <t>https://www.dosje.gov.in/annual-reports/</t>
         </is>
       </c>
       <c r="I5" s="28" t="inlineStr">
@@ -33510,7 +33510,7 @@
       </c>
       <c r="E6" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.11): the visible part of a control — its icon, its outline, its indicator — needs 3:1 against what is behind it.  →  Live: Text “Previous slide” (div.ccps-nav-btn) renders #EEEEEE on #FFFFFF at 16px/400 — measured on the capture's pixels: #F1EFEA on #FBF3DC is 1.04:1 against the 3.0:1 minimum. Measured on 7 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.11): the visible part of a control — its icon, its outline, its indicator — needs 3:1 against what is behind it.  →  Live: Text “Previous slide” (div.ccps-nav-btn) renders #EEEEEE on #FFFFFF at 16px/400 — #F0EFED on #FCF9EA as painted on the capture: 1.09:1 against the 3.0:1 minimum.</t>
         </is>
       </c>
       <c r="F6" s="28" t="inlineStr">
@@ -33545,38 +33545,38 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-080</t>
+          <t>WEB-GLOBAL-025</t>
         </is>
       </c>
       <c r="B7" s="28" t="inlineStr">
         <is>
-          <t>Global · Non-text control below 3:1 — Go to slide 1</t>
+          <t>Global · Heading levels skip — Need Support?</t>
         </is>
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>Blocker</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.11): the visible part of a control — its icon, its outline, its indicator — needs 3:1 against what is behind it.  →  Live: Text “Go to slide 1” (span.swiper-pagination-bullet) renders #1F2937 on #373737 at 16px/400 — measured on the capture's pixels: #4A4A4A on #0F0F0F is 2.16:1 against the 3.0:1 minimum.</t>
+          <t>Figma: WCAG 2.2 A (1.3.1): heading levels descend without skipping, so the outline can be navigated.  →  Live: “Need Support?” is an &lt;h6&gt; directly after an &lt;h1&gt;, skipping h2. The outline cannot be navigated reliably by a screen reader. Measured on 138 pages.</t>
         </is>
       </c>
       <c r="F7" s="28" t="inlineStr">
         <is>
-          <t>Darken the icon or its ground until the pair reaches 3:1. The control's accessible name is already correct; only what is drawn needs changing.</t>
+          <t>Re-tag the heading so levels descend in order, or promote the heading above it. Where the markup is only for size, use CSS instead.</t>
         </is>
       </c>
       <c r="G7" s="28" t="n"/>
       <c r="H7" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/</t>
+          <t>https://www.dosje.gov.in/about-the-division/</t>
         </is>
       </c>
       <c r="I7" s="28" t="inlineStr">
@@ -33600,17 +33600,17 @@
     <row r="8">
       <c r="A8" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-025</t>
+          <t>WEB-GLOBAL-010</t>
         </is>
       </c>
       <c r="B8" s="28" t="inlineStr">
         <is>
-          <t>Global · Heading levels skip — Need Support?</t>
+          <t>Global · Automated accessibility violation — aria-command-name</t>
         </is>
       </c>
       <c r="C8" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D8" s="28" t="inlineStr">
@@ -33620,12 +33620,12 @@
       </c>
       <c r="E8" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 A (1.3.1): heading levels descend without skipping, so the outline can be navigated.  →  Live: “Need Support?” is an &lt;h6&gt; directly after an &lt;h1&gt;, skipping h2. The outline cannot be navigated reliably by a screen reader. Measured on 135 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: ARIA commands must have an accessible name — &lt;a class="elementor-button elementor-size-sm" role="button" id="accessibilityButton"&gt; (aria-command-name, wcag2a, wcag412). Measured on 146 pages.</t>
         </is>
       </c>
       <c r="F8" s="28" t="inlineStr">
         <is>
-          <t>Re-tag the heading so levels descend in order, or promote the heading above it. Where the markup is only for size, use CSS instead.</t>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
         </is>
       </c>
       <c r="G8" s="28" t="n"/>
@@ -33655,12 +33655,12 @@
     <row r="9">
       <c r="A9" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-010</t>
+          <t>WEB-GLOBAL-011</t>
         </is>
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — aria-command-name</t>
+          <t>Global · Automated accessibility violation — link-name</t>
         </is>
       </c>
       <c r="C9" s="28" t="inlineStr">
@@ -33675,7 +33675,8 @@
       </c>
       <c r="E9" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: ARIA commands must have an accessible name — &lt;a class="elementor-button elementor-size-sm" role="button" id="accessibilityButton"&gt; (aria-command-name, wcag2a, wcag412). Measured on 143 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Links must have discernible text — &lt;a href="https://www.digitalindia.gov.in/" target="_blank"&gt;
+							&lt;img loading="lazy" width="105" height="41" src="https://www.dosje.gov.in/wp-content/uploads/ (link-name, wcag2a, wcag244, wcag412). Measured on 146 pages.</t>
         </is>
       </c>
       <c r="F9" s="28" t="inlineStr">
@@ -33710,17 +33711,17 @@
     <row r="10">
       <c r="A10" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-011</t>
+          <t>WEB-GLOBAL-045</t>
         </is>
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — link-name</t>
+          <t>Global · Footer is missing a DBIM-mandated section — footer</t>
         </is>
       </c>
       <c r="C10" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D10" s="28" t="inlineStr">
@@ -33730,13 +33731,12 @@
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Links must have discernible text — &lt;a href="https://www.digitalindia.gov.in/" target="_blank"&gt;
-							&lt;img loading="lazy" width="105" height="41" src="https://www.dosje.gov.in/wp-content/uploads/ (link-name, wcag2a, wcag244, wcag412). Measured on 143 pages.</t>
+          <t>Figma: DBIM 3.0 §5.6: the footer carries Archives, Website Policy, Related Links and Feedback.  →  Live: DBIM 5.6 mandates four footer sections. This footer publishes 0 of them; missing: Archives, Website Policy, Related Links, Feedback. Measured on 146 pages.</t>
         </is>
       </c>
       <c r="F10" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+          <t>Add the missing sections to the footer. Archives and Website Policy need a page each; Related Links and Feedback can carry the existing ones.</t>
         </is>
       </c>
       <c r="G10" s="28" t="n"/>
@@ -33766,17 +33766,17 @@
     <row r="11">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-045</t>
+          <t>WEB-GLOBAL-046</t>
         </is>
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>Global · Footer is missing a DBIM-mandated section — footer</t>
+          <t>Global · UX4G violet leaks into the brand palette — a</t>
         </is>
       </c>
       <c r="C11" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D11" s="28" t="inlineStr">
@@ -33786,12 +33786,12 @@
       </c>
       <c r="E11" s="28" t="inlineStr">
         <is>
-          <t>Figma: DBIM 3.0 §5.6: the footer carries Archives, Website Policy, Related Links and Feedback.  →  Live: DBIM 5.6 mandates four footer sections. This footer publishes 0 of them; missing: Archives, Website Policy, Related Links, Feedback. Measured on 143 pages.</t>
+          <t>Figma: DBIM 3.0 §2.1: one colour group from the primary palette. UX4G's violet is its own brand layer, not the Department's.  →  Live: 9 element(s) render UX4G's violet primary rather than the Department's key colour. DBIM 2.1 allows one colour group from the primary palette. Measured on 145 pages.</t>
         </is>
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>Add the missing sections to the footer. Archives and Website Policy need a page each; Related Links and Feedback can carry the existing ones.</t>
+          <t>Override the inherited UX4G variables so the Department's key colour applies everywhere, including the skip link and the accessibility widget.</t>
         </is>
       </c>
       <c r="G11" s="28" t="n"/>
@@ -33821,17 +33821,17 @@
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-046</t>
+          <t>WEB-GLOBAL-063</t>
         </is>
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>Global · UX4G violet leaks into the brand palette — a</t>
+          <t>Global · Font size outside the UX4G type scale — 10px text</t>
         </is>
       </c>
       <c r="C12" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D12" s="28" t="inlineStr">
@@ -33841,12 +33841,12 @@
       </c>
       <c r="E12" s="28" t="inlineStr">
         <is>
-          <t>Figma: DBIM 3.0 §2.1: one colour group from the primary palette. UX4G's violet is its own brand layer, not the Department's.  →  Live: 9 element(s) render UX4G's violet primary rather than the Department's key colour. DBIM 2.1 allows one colour group from the primary palette. Measured on 142 pages.</t>
+          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 1 element(s) render at 10px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). It is also below Body/XS, the stated minimum usable size. Measured on 130 pages.</t>
         </is>
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
-          <t>Override the inherited UX4G variables so the Department's key colour applies everywhere, including the skip link and the accessibility widget.</t>
+          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
         </is>
       </c>
       <c r="G12" s="28" t="n"/>
@@ -33876,17 +33876,17 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-063</t>
+          <t>WEB-GLOBAL-019</t>
         </is>
       </c>
       <c r="B13" s="28" t="inlineStr">
         <is>
-          <t>Global · Font size outside the UX4G type scale — 10px text</t>
+          <t>Global · Text contrast below AA — About Ministry</t>
         </is>
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D13" s="28" t="inlineStr">
@@ -33896,12 +33896,12 @@
       </c>
       <c r="E13" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 1 element(s) render at 10px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). It is also below Body/XS, the stated minimum usable size. Measured on 127 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “About Ministry” (span.elementor-icon-list-text) renders #E2E6EA on #0373DF at 14px/400 — #E2E6EA on #0373DF as painted on the capture: 3.7:1 against the 4.5:1 minimum. Measured on 124 pages.</t>
         </is>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G13" s="28" t="n"/>
@@ -33931,17 +33931,17 @@
     <row r="14">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-019</t>
+          <t>WEB-GLOBAL-032</t>
         </is>
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — About Ministry</t>
+          <t>Global · Touch target below the minimum — Home</t>
         </is>
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D14" s="28" t="inlineStr">
@@ -33951,12 +33951,12 @@
       </c>
       <c r="E14" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “About Ministry” (span.elementor-icon-list-text) renders #E2E6EA on #0373DF at 14px/400 — measured on the capture's pixels: #E2E6EA on #0373DF is 3.7:1 against the 4.5:1 minimum. Measured on 121 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Home” is 41×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 41×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 144 pages.</t>
         </is>
       </c>
       <c r="F14" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
         </is>
       </c>
       <c r="G14" s="28" t="n"/>
@@ -33986,12 +33986,12 @@
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-026</t>
+          <t>WEB-GLOBAL-033</t>
         </is>
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Open Department</t>
+          <t>Global · Touch target below the minimum — Department</t>
         </is>
       </c>
       <c r="C15" s="28" t="inlineStr">
@@ -34006,7 +34006,7 @@
       </c>
       <c r="E15" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Open Department” is 14×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 14×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 141 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Department” is 83×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 83×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 144 pages.</t>
         </is>
       </c>
       <c r="F15" s="28" t="inlineStr">
@@ -34041,12 +34041,12 @@
     <row r="16">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-032</t>
+          <t>WEB-GLOBAL-026</t>
         </is>
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Home</t>
+          <t>Global · Touch target below the minimum — Open Department</t>
         </is>
       </c>
       <c r="C16" s="28" t="inlineStr">
@@ -34061,7 +34061,7 @@
       </c>
       <c r="E16" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Home” is 41×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 41×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 140 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Open Department” is 14×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 14×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 144 pages.</t>
         </is>
       </c>
       <c r="F16" s="28" t="inlineStr">
@@ -34096,12 +34096,12 @@
     <row r="17">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-033</t>
+          <t>WEB-GLOBAL-031</t>
         </is>
       </c>
       <c r="B17" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Department</t>
+          <t>Global · Touch target below the minimum — Associated Organisations</t>
         </is>
       </c>
       <c r="C17" s="28" t="inlineStr">
@@ -34116,7 +34116,7 @@
       </c>
       <c r="E17" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Department” is 83×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 83×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 140 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Associated Organisations” is 172×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 172×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 144 pages.</t>
         </is>
       </c>
       <c r="F17" s="28" t="inlineStr">
@@ -34151,17 +34151,17 @@
     <row r="18">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-031</t>
+          <t>WEB-GLOBAL-017</t>
         </is>
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Associated Organisations</t>
+          <t>Global · Text contrast below AA — Get in Touch</t>
         </is>
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D18" s="28" t="inlineStr">
@@ -34171,12 +34171,12 @@
       </c>
       <c r="E18" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Associated Organisations” is 172×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 172×21 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 140 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Get in Touch” (a.btn) renders #0373DF on #E5EFF9 at 16px/500 — #0373DF on #E5EFF9 as painted on the capture: 3.99:1 against the 4.5:1 minimum. Measured on 126 pages.</t>
         </is>
       </c>
       <c r="F18" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G18" s="28" t="n"/>
@@ -34206,17 +34206,17 @@
     <row r="19">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-017</t>
+          <t>WEB-GLOBAL-064</t>
         </is>
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Get in Touch</t>
+          <t>Global · Font size outside the UX4G type scale — 8px text</t>
         </is>
       </c>
       <c r="C19" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D19" s="28" t="inlineStr">
@@ -34226,12 +34226,12 @@
       </c>
       <c r="E19" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Get in Touch” (a.btn) renders #0373DF on #E5EFF9 at 16px/500 — measured on the capture's pixels: #0373DF on #E5EFF9 is 3.99:1 against the 4.5:1 minimum. Measured on 123 pages.</t>
+          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 2 element(s) render at 8px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). It is also below Body/XS, the stated minimum usable size. Measured on 117 pages.</t>
         </is>
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
         </is>
       </c>
       <c r="G19" s="28" t="n"/>
@@ -34261,17 +34261,17 @@
     <row r="20">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-064</t>
+          <t>WEB-GLOBAL-016</t>
         </is>
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>Global · Font size outside the UX4G type scale — 8px text</t>
+          <t>Global · Text contrast below AA — Get in Touch</t>
         </is>
       </c>
       <c r="C20" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D20" s="28" t="inlineStr">
@@ -34281,12 +34281,12 @@
       </c>
       <c r="E20" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 2 element(s) render at 8px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). It is also below Body/XS, the stated minimum usable size. Measured on 117 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Get in Touch” (a.btn) renders #0373DF on #E5EFF9 at 14px/500 — #0373DF on #E5EFF9 as painted on the capture: 3.99:1 against the 4.5:1 minimum. Measured on 116 pages.</t>
         </is>
       </c>
       <c r="F20" s="28" t="inlineStr">
         <is>
-          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G20" s="28" t="n"/>
@@ -34316,17 +34316,17 @@
     <row r="21">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-016</t>
+          <t>WEB-GLOBAL-027</t>
         </is>
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Get in Touch</t>
+          <t>Global · Touch target below the minimum — About Ministry</t>
         </is>
       </c>
       <c r="C21" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -34336,12 +34336,12 @@
       </c>
       <c r="E21" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Get in Touch” (a.btn) renders #0373DF on #E5EFF9 at 14px/500 — measured on the capture's pixels: #0373DF on #E5EFF9 is 3.99:1 against the 4.5:1 minimum. Measured on 116 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “About Ministry” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 110 pages.</t>
         </is>
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
         </is>
       </c>
       <c r="G21" s="28" t="n"/>
@@ -34371,12 +34371,12 @@
     <row r="22">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-027</t>
+          <t>WEB-GLOBAL-030</t>
         </is>
       </c>
       <c r="B22" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — About Ministry</t>
+          <t>Global · Touch target below the minimum — Vision &amp; Mission</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
@@ -34391,7 +34391,7 @@
       </c>
       <c r="E22" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “About Ministry” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 110 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Vision &amp; Mission” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 108 pages.</t>
         </is>
       </c>
       <c r="F22" s="28" t="inlineStr">
@@ -34426,12 +34426,12 @@
     <row r="23">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-030</t>
+          <t>WEB-GLOBAL-029</t>
         </is>
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Vision &amp; Mission</t>
+          <t>Global · Touch target below the minimum — Organisational Chart</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
@@ -34446,7 +34446,7 @@
       </c>
       <c r="E23" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Vision &amp; Mission” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 108 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Organisational Chart” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 106 pages.</t>
         </is>
       </c>
       <c r="F23" s="28" t="inlineStr">
@@ -34481,12 +34481,12 @@
     <row r="24">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-029</t>
+          <t>WEB-GLOBAL-028</t>
         </is>
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Organisational Chart</t>
+          <t>Global · Touch target below the minimum — Ministers &amp; Officials</t>
         </is>
       </c>
       <c r="C24" s="28" t="inlineStr">
@@ -34501,7 +34501,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Organisational Chart” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 106 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Ministers &amp; Officials” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 94 pages.</t>
         </is>
       </c>
       <c r="F24" s="28" t="inlineStr">
@@ -34536,17 +34536,17 @@
     <row r="25">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-028</t>
+          <t>WEB-GLOBAL-054</t>
         </is>
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Ministers &amp; Officials</t>
+          <t>Global · Built value differs from the design — login</t>
         </is>
       </c>
       <c r="C25" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D25" s="28" t="inlineStr">
@@ -34556,20 +34556,20 @@
       </c>
       <c r="E25" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Ministers &amp; Officials” is 151×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 151×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 94 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built #FFFFFF · design #0373DF  →  Live: “login” — colour #0373DF → #FFFFFF. Measured on 82 pages.</t>
         </is>
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G25" s="28" t="n"/>
-      <c r="H25" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/about-the-division/</t>
-        </is>
-      </c>
+          <t>Set the built value to the design's.</t>
+        </is>
+      </c>
+      <c r="G25" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
+        </is>
+      </c>
+      <c r="H25" s="28" t="n"/>
       <c r="I25" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -34591,17 +34591,17 @@
     <row r="26">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-054</t>
+          <t>WEB-GLOBAL-056</t>
         </is>
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — login</t>
+          <t>Global · Built value differs from the design — gov. of india</t>
         </is>
       </c>
       <c r="C26" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D26" s="28" t="inlineStr">
@@ -34611,7 +34611,7 @@
       </c>
       <c r="E26" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built #FFFFFF · design #0373DF  →  Live: “login” — colour #0373DF → #FFFFFF. Measured on 82 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 12px · design 14px · Built 400 weight · design 500  →  Live: “gov. of india” — size 14 → 12; weight 500 → 400. Measured on 72 pages.</t>
         </is>
       </c>
       <c r="F26" s="28" t="inlineStr">
@@ -34621,7 +34621,7 @@
       </c>
       <c r="G26" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-109359</t>
         </is>
       </c>
       <c r="H26" s="28" t="n"/>
@@ -34646,17 +34646,17 @@
     <row r="27">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-056</t>
+          <t>WEB-GLOBAL-024</t>
         </is>
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — gov. of india</t>
+          <t>Global · Page has no &lt;h1&gt; / more than one — page title</t>
         </is>
       </c>
       <c r="C27" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D27" s="28" t="inlineStr">
@@ -34666,20 +34666,20 @@
       </c>
       <c r="E27" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 12px · design 14px · Built 400 weight · design 500  →  Live: “gov. of india” — size 14 → 12; weight 500 → 400. Measured on 72 pages.</t>
+          <t>Figma: WCAG 2.2 A (1.3.1) and GIGW 3.0: one &lt;h1&gt; per page, naming the page.  →  Live: The page renders no &lt;h1&gt;. The first visible heading is &lt;h6&gt; “Need Support?”. Measured on 42 pages.</t>
         </is>
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
-        </is>
-      </c>
-      <c r="G27" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-109359</t>
-        </is>
-      </c>
-      <c r="H27" s="28" t="n"/>
+          <t>Render exactly one &lt;h1&gt; carrying the page's own title, above the content.</t>
+        </is>
+      </c>
+      <c r="G27" s="28" t="n"/>
+      <c r="H27" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/advertisement/</t>
+        </is>
+      </c>
       <c r="I27" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -34701,17 +34701,17 @@
     <row r="28">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-024</t>
+          <t>WEB-GLOBAL-055</t>
         </is>
       </c>
       <c r="B28" s="28" t="inlineStr">
         <is>
-          <t>Global · Page has no &lt;h1&gt; / more than one — page title</t>
+          <t>Global · Built value differs from the design — title</t>
         </is>
       </c>
       <c r="C28" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D28" s="28" t="inlineStr">
@@ -34721,20 +34721,20 @@
       </c>
       <c r="E28" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 A (1.3.1) and GIGW 3.0: one &lt;h1&gt; per page, naming the page.  →  Live: The page renders no &lt;h1&gt;. The first visible heading is &lt;h6&gt; “Need Support?”. Measured on 41 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built #1F2937 · design #1F2428  →  Live: “title” — colour #1F2428 → #1F2937. Measured on 42 pages.</t>
         </is>
       </c>
       <c r="F28" s="28" t="inlineStr">
         <is>
-          <t>Render exactly one &lt;h1&gt; carrying the page's own title, above the content.</t>
-        </is>
-      </c>
-      <c r="G28" s="28" t="n"/>
-      <c r="H28" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/advertisement/</t>
-        </is>
-      </c>
+          <t>Set the built value to the design's.</t>
+        </is>
+      </c>
+      <c r="G28" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
+        </is>
+      </c>
+      <c r="H28" s="28" t="n"/>
       <c r="I28" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -34756,12 +34756,12 @@
     <row r="29">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-055</t>
+          <t>WEB-GLOBAL-021</t>
         </is>
       </c>
       <c r="B29" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — title</t>
+          <t>Global · Text contrast below AA — View All Documents from MoSJE</t>
         </is>
       </c>
       <c r="C29" s="28" t="inlineStr">
@@ -34776,20 +34776,20 @@
       </c>
       <c r="E29" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built #1F2937 · design #1F2428  →  Live: “title” — colour #1F2428 → #1F2937. Measured on 42 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “View All Documents from MoSJE” (a.btn) renders #0373DF on #F9FAFB at 14px/500 — #0373DF on #F9FAFB as painted on the capture: 4.44:1 against the 4.5:1 minimum. Measured on 13 pages.</t>
         </is>
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
-        </is>
-      </c>
-      <c r="G29" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
-        </is>
-      </c>
-      <c r="H29" s="28" t="n"/>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+        </is>
+      </c>
+      <c r="G29" s="28" t="n"/>
+      <c r="H29" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/documents/corrigendum-to-pm-daksh-scheme-guidelines/</t>
+        </is>
+      </c>
       <c r="I29" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -34811,17 +34811,17 @@
     <row r="30">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-021</t>
+          <t>WEB-GLOBAL-015</t>
         </is>
       </c>
       <c r="B30" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — View All Documents from MoSJE</t>
+          <t>Global · Automated accessibility violation — frame-title</t>
         </is>
       </c>
       <c r="C30" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D30" s="28" t="inlineStr">
@@ -34831,18 +34831,18 @@
       </c>
       <c r="E30" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “View All Documents from MoSJE” (a.btn) renders #0373DF on #F9FAFB at 14px/500 — measured on the capture's pixels: #2E8AE4 on #F9FAFB is 3.42:1 against the 4.5:1 minimum. Measured on 13 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Frames must have an accessible name — &lt;iframe width="100%" height="300" style="border:0;" loading="lazy" allowfullscreen="" referrerpolicy="no-referrer-when-downgrade" src="https://www.google.com/ma (frame-title, wcag2a, wcag412). Measured on 19 pages.</t>
         </is>
       </c>
       <c r="F30" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
         </is>
       </c>
       <c r="G30" s="28" t="n"/>
       <c r="H30" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/documents/corrigendum-to-pm-daksh-scheme-guidelines/</t>
+          <t>https://www.dosje.gov.in/events/ek-ped-maa-ke-naam-6/</t>
         </is>
       </c>
       <c r="I30" s="28" t="inlineStr">
@@ -34866,17 +34866,17 @@
     <row r="31">
       <c r="A31" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-015</t>
+          <t>WEB-GLOBAL-020</t>
         </is>
       </c>
       <c r="B31" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — frame-title</t>
+          <t>Global · Text contrast below AA — Dr. Ambedkar Foundation Official</t>
         </is>
       </c>
       <c r="C31" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D31" s="28" t="inlineStr">
@@ -34886,18 +34886,18 @@
       </c>
       <c r="E31" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Frames must have an accessible name — &lt;iframe width="100%" height="300" style="border:0;" loading="lazy" allowfullscreen="" referrerpolicy="no-referrer-when-downgrade" src="https://www.google.com/ma (frame-title, wcag2a, wcag412). Measured on 19 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Dr. Ambedkar Foundation Official” (h4.text-center) renders #0373DF on #F9FAFB at 20px/600 — #0373DF on #F9FAFB as painted on the capture: 4.44:1 against the 4.5:1 minimum. Measured on 14 pages.</t>
         </is>
       </c>
       <c r="F31" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G31" s="28" t="n"/>
       <c r="H31" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/events/ek-ped-maa-ke-naam-6/</t>
+          <t>https://www.dosje.gov.in/daf-directory/</t>
         </is>
       </c>
       <c r="I31" s="28" t="inlineStr">
@@ -34921,17 +34921,17 @@
     <row r="32">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-020</t>
+          <t>WEB-GLOBAL-065</t>
         </is>
       </c>
       <c r="B32" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Chairperson's office</t>
+          <t>Global · Font size outside the UX4G type scale — 11px text</t>
         </is>
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D32" s="28" t="inlineStr">
@@ -34941,18 +34941,18 @@
       </c>
       <c r="E32" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Chairperson's office” (h4.text-center) renders #0373DF on #F9FAFB at 20px/600 — measured on the capture's pixels: #848586 on #FFFFFF is 3.7:1 against the 4.5:1 minimum. Measured on 14 pages.</t>
+          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 9 element(s) render at 11px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). It is also below Body/XS, the stated minimum usable size. Measured on 6 pages.</t>
         </is>
       </c>
       <c r="F32" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
         </is>
       </c>
       <c r="G32" s="28" t="n"/>
       <c r="H32" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/chairpersons-office/</t>
+          <t>https://www.dosje.gov.in/dashboard/</t>
         </is>
       </c>
       <c r="I32" s="28" t="inlineStr">
@@ -35031,17 +35031,17 @@
     <row r="34">
       <c r="A34" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-065</t>
+          <t>WEB-GLOBAL-009</t>
         </is>
       </c>
       <c r="B34" s="28" t="inlineStr">
         <is>
-          <t>Global · Font size outside the UX4G type scale — 11px text</t>
+          <t>Global · Image carries no alt attribute</t>
         </is>
       </c>
       <c r="C34" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D34" s="28" t="inlineStr">
@@ -35051,18 +35051,18 @@
       </c>
       <c r="E34" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 9 element(s) render at 11px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). It is also below Body/XS, the stated minimum usable size. Measured on 4 pages.</t>
+          <t>Figma: WCAG 2.2 A (1.1.1): every image carries an alt attribute — descriptive where it conveys meaning, empty where it is decorative.  →  Live: “g8203_6a017643c9e5a_5jbzbySbWZr2OwiYXBianYQzkv1kI7tVXaWbwldA.jpg” renders at 411px wide with no alt attribute. A screen reader announces the file name instead of the content. Measured on 6 pages.</t>
         </is>
       </c>
       <c r="F34" s="28" t="inlineStr">
         <is>
-          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
+          <t>Add an alt attribute: a description where the image carries meaning, alt="" where it is decorative.</t>
         </is>
       </c>
       <c r="G34" s="28" t="n"/>
       <c r="H34" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/dashboard/</t>
+          <t>https://www.dosje.gov.in/gallery/</t>
         </is>
       </c>
       <c r="I34" s="28" t="inlineStr">
@@ -35196,17 +35196,17 @@
     <row r="37">
       <c r="A37" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-059</t>
+          <t>WEB-GLOBAL-022</t>
         </is>
       </c>
       <c r="B37" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — dr. virendra kumar</t>
+          <t>Global · Text contrast below AA — Dr. Ambedkar International Centre (DAIC)</t>
         </is>
       </c>
       <c r="C37" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D37" s="28" t="inlineStr">
@@ -35216,20 +35216,20 @@
       </c>
       <c r="E37" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #0373DF · design #1F2428  →  Live: “dr. virendra kumar” — weight 500 → 400; colour #1F2428 → #0373DF. Measured on 6 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Dr. Ambedkar International Centre (DAIC)” (a.text-primary) renders #0373DF on #F9FAFB at 16px/400 — #0373DF on #F9FAFB as painted on the capture: 4.44:1 against the 4.5:1 minimum. Measured on 4 pages.</t>
         </is>
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
-        </is>
-      </c>
-      <c r="G37" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-89516</t>
-        </is>
-      </c>
-      <c r="H37" s="28" t="n"/>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+        </is>
+      </c>
+      <c r="G37" s="28" t="n"/>
+      <c r="H37" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/official/dr-swati-s-mishra/</t>
+        </is>
+      </c>
       <c r="I37" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -35251,17 +35251,17 @@
     <row r="38">
       <c r="A38" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-014</t>
+          <t>WEB-GLOBAL-059</t>
         </is>
       </c>
       <c r="B38" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — link-in-text-block</t>
+          <t>Global · Built value differs from the design — dr. virendra kumar</t>
         </is>
       </c>
       <c r="C38" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D38" s="28" t="inlineStr">
@@ -35271,20 +35271,20 @@
       </c>
       <c r="E38" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Links must be distinguishable without relying on color — &lt;a href="https://www.dosje.gov.in/organisation/national-portal-for-transgender-persons/" target="_blank" rel="noopener"&gt;https://www.dosje.gov.in/organisation/na (link-in-text-block, wcag2a, wcag141). Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #0373DF · design #1F2428  →  Live: “dr. virendra kumar” — weight 500 → 400; colour #1F2428 → #0373DF. Measured on 6 pages.</t>
         </is>
       </c>
       <c r="F38" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
-        </is>
-      </c>
-      <c r="G38" s="28" t="n"/>
-      <c r="H38" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/about-the-division-social-defence/</t>
-        </is>
-      </c>
+          <t>Set the built value to the design's.</t>
+        </is>
+      </c>
+      <c r="G38" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-89516</t>
+        </is>
+      </c>
+      <c r="H38" s="28" t="n"/>
       <c r="I38" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -35306,17 +35306,17 @@
     <row r="39">
       <c r="A39" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-022</t>
+          <t>WEB-GLOBAL-014</t>
         </is>
       </c>
       <c r="B39" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Dr. Ambedkar International Centre (DAIC)</t>
+          <t>Global · Automated accessibility violation — link-in-text-block</t>
         </is>
       </c>
       <c r="C39" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D39" s="28" t="inlineStr">
@@ -35326,18 +35326,18 @@
       </c>
       <c r="E39" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Dr. Ambedkar International Centre (DAIC)” (a.text-primary) renders #0373DF on #F9FAFB at 16px/400 — measured on the capture's pixels: #0373DF on #F9FAFB is 4.44:1 against the 4.5:1 minimum. Measured on 4 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Links must be distinguishable without relying on color — &lt;a href="https://www.dosje.gov.in/organisation/national-portal-for-transgender-persons/" target="_blank" rel="noopener"&gt;https://www.dosje.gov.in/organisation/na (link-in-text-block, wcag2a, wcag141). Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
         </is>
       </c>
       <c r="G39" s="28" t="n"/>
       <c r="H39" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/official/dr-swati-s-mishra/</t>
+          <t>https://www.dosje.gov.in/about-the-division-social-defence/</t>
         </is>
       </c>
       <c r="I39" s="28" t="inlineStr">
@@ -35526,12 +35526,12 @@
     <row r="43">
       <c r="A43" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-009</t>
+          <t>WEB-GLOBAL-052</t>
         </is>
       </c>
       <c r="B43" s="28" t="inlineStr">
         <is>
-          <t>Global · Image carries no alt attribute</t>
+          <t>Global · Content in the design is not in the build — search by name, designation, or organization</t>
         </is>
       </c>
       <c r="C43" s="28" t="inlineStr">
@@ -35546,20 +35546,20 @@
       </c>
       <c r="E43" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 A (1.1.1): every image carries an alt attribute — descriptive where it conveys meaning, empty where it is decorative.  →  Live: “g8203_6a017643c9e5a_5jbzbySbWZr2OwiYXBianYQzkv1kI7tVXaWbwldA.jpg” renders at 411px wide with no alt attribute. A screen reader announces the file name instead of the content. Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by name, designation, or organiza” · absent from the build  →  Live: The design frame carries “search by name, designation, or organization” (16px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>Add an alt attribute: a description where the image carries meaning, alt="" where it is decorative.</t>
-        </is>
-      </c>
-      <c r="G43" s="28" t="n"/>
-      <c r="H43" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/gallery/</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G43" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-9324</t>
+        </is>
+      </c>
+      <c r="H43" s="28" t="n"/>
       <c r="I43" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -35581,12 +35581,12 @@
     <row r="44">
       <c r="A44" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-052</t>
+          <t>WEB-GLOBAL-048</t>
         </is>
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — search by name, designation, or organization</t>
+          <t>Global · Content in the design is not in the build — of 1500 items</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
@@ -35601,7 +35601,7 @@
       </c>
       <c r="E44" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by name, designation, or organiza” · absent from the build  →  Live: The design frame carries “search by name, designation, or organization” (16px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “of 1500 items” · absent from the build  →  Live: The design frame carries “of 1500 items” (12px). Nothing with that text renders on the live page. Measured on 4 pages.</t>
         </is>
       </c>
       <c r="F44" s="28" t="inlineStr">
@@ -35611,7 +35611,7 @@
       </c>
       <c r="G44" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-9324</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
         </is>
       </c>
       <c r="H44" s="28" t="n"/>
@@ -35636,12 +35636,12 @@
     <row r="45">
       <c r="A45" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-048</t>
+          <t>WEB-GLOBAL-051</t>
         </is>
       </c>
       <c r="B45" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — of 1500 items</t>
+          <t>Global · Content in the design is not in the build</t>
         </is>
       </c>
       <c r="C45" s="28" t="inlineStr">
@@ -35656,7 +35656,7 @@
       </c>
       <c r="E45" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “of 1500 items” · absent from the build  →  Live: The design frame carries “of 1500 items” (12px). Nothing with that text renders on the live page. Measured on 4 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “empowering citizens with the right to in” · absent from the build  →  Live: The design frame carries “empowering citizens with the right to information access government data, decisi” (16px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F45" s="28" t="inlineStr">
@@ -35666,7 +35666,7 @@
       </c>
       <c r="G45" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
         </is>
       </c>
       <c r="H45" s="28" t="n"/>
@@ -35691,17 +35691,17 @@
     <row r="46">
       <c r="A46" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-051</t>
+          <t>WEB-GLOBAL-062</t>
         </is>
       </c>
       <c r="B46" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build</t>
+          <t>Global · Built value differs from the design — here's how the ministry empowers citizens like you</t>
         </is>
       </c>
       <c r="C46" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D46" s="28" t="inlineStr">
@@ -35711,17 +35711,17 @@
       </c>
       <c r="E46" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “empowering citizens with the right to in” · absent from the build  →  Live: The design frame carries “empowering citizens with the right to information access government data, decisi” (16px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 28px · design 22px · Built #1F2937 · design #1F2428  →  Live: “here's how the ministry empowers citizens like you” — size 22 → 28; colour #1F2428 → #1F2937. Measured on 4 pages.</t>
         </is>
       </c>
       <c r="F46" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+          <t>Set the built value to the design's.</t>
         </is>
       </c>
       <c r="G46" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-8477</t>
         </is>
       </c>
       <c r="H46" s="28" t="n"/>
@@ -35746,17 +35746,17 @@
     <row r="47">
       <c r="A47" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-062</t>
+          <t>WEB-GLOBAL-049</t>
         </is>
       </c>
       <c r="B47" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — here's how the ministry empowers citizens like you</t>
+          <t>Global · Content in the design is not in the build — search by title, keyword, or document number</t>
         </is>
       </c>
       <c r="C47" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D47" s="28" t="inlineStr">
@@ -35766,17 +35766,17 @@
       </c>
       <c r="E47" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 28px · design 22px · Built #1F2937 · design #1F2428  →  Live: “here's how the ministry empowers citizens like you” — size 22 → 28; colour #1F2428 → #1F2937. Measured on 4 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by title, keyword, or document nu” · absent from the build  →  Live: The design frame carries “search by title, keyword, or document number” (16px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
       <c r="G47" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-8477</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
         </is>
       </c>
       <c r="H47" s="28" t="n"/>
@@ -35801,17 +35801,17 @@
     <row r="48">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-049</t>
+          <t>WEB-GLOBAL-034</t>
         </is>
       </c>
       <c r="B48" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — search by title, keyword, or document number</t>
+          <t>Global · Touch target below the minimum — NCBC</t>
         </is>
       </c>
       <c r="C48" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D48" s="28" t="inlineStr">
@@ -35821,20 +35821,20 @@
       </c>
       <c r="E48" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by title, keyword, or document nu” · absent from the build  →  Live: The design frame carries “search by title, keyword, or document number” (16px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NCBC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F48" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G48" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
-        </is>
-      </c>
-      <c r="H48" s="28" t="n"/>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+        </is>
+      </c>
+      <c r="G48" s="28" t="n"/>
+      <c r="H48" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/acts-rules/</t>
+        </is>
+      </c>
       <c r="I48" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -35856,12 +35856,12 @@
     <row r="49">
       <c r="A49" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-034</t>
+          <t>WEB-GLOBAL-036</t>
         </is>
       </c>
       <c r="B49" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NCBC</t>
+          <t>Global · Touch target below the minimum — DAF</t>
         </is>
       </c>
       <c r="C49" s="28" t="inlineStr">
@@ -35876,7 +35876,7 @@
       </c>
       <c r="E49" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NCBC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DAF” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F49" s="28" t="inlineStr">
@@ -35887,7 +35887,7 @@
       <c r="G49" s="28" t="n"/>
       <c r="H49" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/acts-rules/</t>
+          <t>https://www.dosje.gov.in/advertisement/</t>
         </is>
       </c>
       <c r="I49" s="28" t="inlineStr">
@@ -35911,12 +35911,12 @@
     <row r="50">
       <c r="A50" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-036</t>
+          <t>WEB-GLOBAL-037</t>
         </is>
       </c>
       <c r="B50" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — DAF</t>
+          <t>Global · Touch target below the minimum — DAIC</t>
         </is>
       </c>
       <c r="C50" s="28" t="inlineStr">
@@ -35931,7 +35931,7 @@
       </c>
       <c r="E50" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DAF” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DAIC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F50" s="28" t="inlineStr">
@@ -35966,12 +35966,12 @@
     <row r="51">
       <c r="A51" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-037</t>
+          <t>WEB-GLOBAL-039</t>
         </is>
       </c>
       <c r="B51" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — DAIC</t>
+          <t>Global · Touch target below the minimum — NSFDC</t>
         </is>
       </c>
       <c r="C51" s="28" t="inlineStr">
@@ -35986,7 +35986,7 @@
       </c>
       <c r="E51" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DAIC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NSFDC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F51" s="28" t="inlineStr">
@@ -35997,7 +35997,7 @@
       <c r="G51" s="28" t="n"/>
       <c r="H51" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/advertisement/</t>
+          <t>https://www.dosje.gov.in/annual-reports/</t>
         </is>
       </c>
       <c r="I51" s="28" t="inlineStr">
@@ -36021,12 +36021,12 @@
     <row r="52">
       <c r="A52" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-039</t>
+          <t>WEB-GLOBAL-040</t>
         </is>
       </c>
       <c r="B52" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NSFDC</t>
+          <t>Global · Touch target below the minimum — NMBA</t>
         </is>
       </c>
       <c r="C52" s="28" t="inlineStr">
@@ -36041,7 +36041,7 @@
       </c>
       <c r="E52" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NSFDC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NMBA” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F52" s="28" t="inlineStr">
@@ -36052,7 +36052,7 @@
       <c r="G52" s="28" t="n"/>
       <c r="H52" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/annual-reports/</t>
+          <t>https://www.dosje.gov.in/circulars-notifications/</t>
         </is>
       </c>
       <c r="I52" s="28" t="inlineStr">
@@ -36076,12 +36076,12 @@
     <row r="53">
       <c r="A53" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-040</t>
+          <t>WEB-GLOBAL-043</t>
         </is>
       </c>
       <c r="B53" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NMBA</t>
+          <t>Global · Touch target below the minimum — SCW</t>
         </is>
       </c>
       <c r="C53" s="28" t="inlineStr">
@@ -36096,7 +36096,7 @@
       </c>
       <c r="E53" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NMBA” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “SCW” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F53" s="28" t="inlineStr">
@@ -36107,7 +36107,7 @@
       <c r="G53" s="28" t="n"/>
       <c r="H53" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/circulars-notifications/</t>
+          <t>https://www.dosje.gov.in/mou/</t>
         </is>
       </c>
       <c r="I53" s="28" t="inlineStr">
@@ -36131,12 +36131,12 @@
     <row r="54">
       <c r="A54" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-043</t>
+          <t>WEB-GLOBAL-042</t>
         </is>
       </c>
       <c r="B54" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — SCW</t>
+          <t>Global · Touch target below the minimum — NSKFDC</t>
         </is>
       </c>
       <c r="C54" s="28" t="inlineStr">
@@ -36151,7 +36151,7 @@
       </c>
       <c r="E54" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “SCW” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NSKFDC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F54" s="28" t="inlineStr">
@@ -36186,17 +36186,17 @@
     <row r="55">
       <c r="A55" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-042</t>
+          <t>WEB-GLOBAL-023</t>
         </is>
       </c>
       <c r="B55" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NSKFDC</t>
+          <t>Global · Text contrast below AA — Dr. Swati S. Mishra</t>
         </is>
       </c>
       <c r="C55" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D55" s="28" t="inlineStr">
@@ -36206,18 +36206,18 @@
       </c>
       <c r="E55" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NSKFDC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Dr. Swati S. Mishra” (h1.h3) renders #0373DF on #F9FAFB at 22px/500 — #0373DF on #F9FAFB as painted on the capture: 4.44:1 against the 4.5:1 minimum. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G55" s="28" t="n"/>
       <c r="H55" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/mou/</t>
+          <t>https://www.dosje.gov.in/official/dr-swati-s-mishra/</t>
         </is>
       </c>
       <c r="I55" s="28" t="inlineStr">
@@ -36241,17 +36241,17 @@
     <row r="56">
       <c r="A56" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-023</t>
+          <t>WEB-GLOBAL-044</t>
         </is>
       </c>
       <c r="B56" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Dr. Swati S. Mishra</t>
+          <t>Global · Touch target below the minimum — DAIC</t>
         </is>
       </c>
       <c r="C56" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D56" s="28" t="inlineStr">
@@ -36261,18 +36261,18 @@
       </c>
       <c r="E56" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Dr. Swati S. Mishra” (h1.h3) renders #0373DF on #F9FAFB at 22px/500 — measured on the capture's pixels: #0675DF on #F9FAFB is 4.35:1 against the 4.5:1 minimum. Measured on 3 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DAIC” is 35×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 35×19 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F56" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
         </is>
       </c>
       <c r="G56" s="28" t="n"/>
       <c r="H56" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/official/dr-swati-s-mishra/</t>
+          <t>https://www.dosje.gov.in/tender/investment-of-an-amount-of-rs-10-00-crore-in-fixed-reg-2/</t>
         </is>
       </c>
       <c r="I56" s="28" t="inlineStr">
@@ -36296,17 +36296,17 @@
     <row r="57">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-044</t>
+          <t>WEB-GLOBAL-060</t>
         </is>
       </c>
       <c r="B57" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — DAIC</t>
+          <t>Global · Built value differs from the design — union minister of social justice and empowerment</t>
         </is>
       </c>
       <c r="C57" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D57" s="28" t="inlineStr">
@@ -36316,20 +36316,20 @@
       </c>
       <c r="E57" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DAIC” is 35×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 35×19 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 12px · Built #1F2937 · design #343A40  →  Live: “union minister of social justice and empowerment” — size 12 → 14; colour #343A40 → #1F2937. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F57" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G57" s="28" t="n"/>
-      <c r="H57" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/tender/investment-of-an-amount-of-rs-10-00-crore-in-fixed-reg-2/</t>
-        </is>
-      </c>
+          <t>Set the built value to the design's.</t>
+        </is>
+      </c>
+      <c r="G57" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-89516</t>
+        </is>
+      </c>
+      <c r="H57" s="28" t="n"/>
       <c r="I57" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -36351,12 +36351,12 @@
     <row r="58">
       <c r="A58" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-060</t>
+          <t>WEB-GLOBAL-061</t>
         </is>
       </c>
       <c r="B58" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — union minister of social justice and empowerment</t>
+          <t>Global · Built value differs from the design — mos3-msje[at]gov[dot]in</t>
         </is>
       </c>
       <c r="C58" s="28" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="E58" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 12px · Built #1F2937 · design #343A40  →  Live: “union minister of social justice and empowerment” — size 12 → 14; colour #343A40 → #1F2937. Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 12px · Built 400 weight · design 500 · Built #1F2937 · design #1F2428  →  Live: “mos3-msje[at]gov[dot]in” — size 12 → 14; weight 500 → 400; colour #1F2428 → #1F2937. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F58" s="28" t="inlineStr">
@@ -36406,17 +36406,17 @@
     <row r="59">
       <c r="A59" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-061</t>
+          <t>WEB-GLOBAL-053</t>
         </is>
       </c>
       <c r="B59" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — mos3-msje[at]gov[dot]in</t>
+          <t>Global · Content in the design is not in the build — target group</t>
         </is>
       </c>
       <c r="C59" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D59" s="28" t="inlineStr">
@@ -36426,17 +36426,17 @@
       </c>
       <c r="E59" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 12px · Built 400 weight · design 500 · Built #1F2937 · design #1F2428  →  Live: “mos3-msje[at]gov[dot]in” — size 12 → 14; weight 500 → 400; colour #1F2428 → #1F2937. Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “target group” · absent from the build  →  Live: The design frame carries “target group” (14px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F59" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
       <c r="G59" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-89516</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
         </is>
       </c>
       <c r="H59" s="28" t="n"/>
@@ -36461,12 +36461,12 @@
     <row r="60">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-053</t>
+          <t>WEB-GLOBAL-050</t>
         </is>
       </c>
       <c r="B60" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — target group</t>
+          <t>Global · Content in the design is not in the build — sort by recently added</t>
         </is>
       </c>
       <c r="C60" s="28" t="inlineStr">
@@ -36481,7 +36481,7 @@
       </c>
       <c r="E60" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “target group” · absent from the build  →  Live: The design frame carries “target group” (14px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “sort by recently added” · absent from the build  →  Live: The design frame carries “sort by recently added” (14px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
         </is>
       </c>
       <c r="F60" s="28" t="inlineStr">
@@ -36491,7 +36491,7 @@
       </c>
       <c r="G60" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
         </is>
       </c>
       <c r="H60" s="28" t="n"/>
@@ -36516,12 +36516,12 @@
     <row r="61">
       <c r="A61" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-050</t>
+          <t>WEB-GLOBAL-069</t>
         </is>
       </c>
       <c r="B61" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — sort by recently added</t>
+          <t>Global · Page language is not en-IN — html lang</t>
         </is>
       </c>
       <c r="C61" s="28" t="inlineStr">
@@ -36531,25 +36531,25 @@
       </c>
       <c r="D61" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E61" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “sort by recently added” · absent from the build  →  Live: The design frame carries “sort by recently added” (14px). Nothing with that text renders on the live page. Measured on 3 pages.</t>
+          <t>Figma: GIGW 3.0 and WCAG 3.1.1: the page declares its language; en-IN on a Government of India property.  →  Live: The document declares lang="en-US" on a Government of India property; en-IN is the correct locale. Measured on 146 pages.</t>
         </is>
       </c>
       <c r="F61" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G61" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12795</t>
-        </is>
-      </c>
-      <c r="H61" s="28" t="n"/>
+          <t>Set lang="en-IN" on &lt;html&gt;, and lang on any block in another language.</t>
+        </is>
+      </c>
+      <c r="G61" s="28" t="n"/>
+      <c r="H61" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/about-the-division/</t>
+        </is>
+      </c>
       <c r="I61" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -36571,17 +36571,17 @@
     <row r="62">
       <c r="A62" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-069</t>
+          <t>WEB-GLOBAL-070</t>
         </is>
       </c>
       <c r="B62" s="28" t="inlineStr">
         <is>
-          <t>Global · Page language is not en-IN — html lang</t>
+          <t>Global · JavaScript errors in the console — console</t>
         </is>
       </c>
       <c r="C62" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="D62" s="28" t="inlineStr">
@@ -36591,12 +36591,12 @@
       </c>
       <c r="E62" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 and WCAG 3.1.1: the page declares its language; en-IN on a Government of India property.  →  Live: The document declares lang="en-US" on a Government of India property; en-IN is the correct locale. Measured on 143 pages.</t>
+          <t>Figma: GIGW 3.0 quality: a page loads without scripting errors.  →  Live: The page logs 21 JavaScript errors on load. First: Loading the font 'https://fonts.gstatic.com/s/notosans/v42/o-0ZIpQlx3QUlC5A4PNr4C5OaxRsfNNlKbCePevttHOmHS91ixg0.woff2' violates the following Content Security Policy directive: "fo Measured on 146 pages.</t>
         </is>
       </c>
       <c r="F62" s="28" t="inlineStr">
         <is>
-          <t>Set lang="en-IN" on &lt;html&gt;, and lang on any block in another language.</t>
+          <t>Fix the scripting errors, starting with the first — later ones are often consequences.</t>
         </is>
       </c>
       <c r="G62" s="28" t="n"/>
@@ -36626,17 +36626,17 @@
     <row r="63">
       <c r="A63" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-070</t>
+          <t>WEB-GLOBAL-067</t>
         </is>
       </c>
       <c r="B63" s="28" t="inlineStr">
         <is>
-          <t>Global · JavaScript errors in the console — console</t>
+          <t>Global · Automated accessibility violation — landmark-contentinfo-is-top-level</t>
         </is>
       </c>
       <c r="C63" s="28" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D63" s="28" t="inlineStr">
@@ -36646,12 +36646,14 @@
       </c>
       <c r="E63" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 quality: a page loads without scripting errors.  →  Live: The page logs 21 JavaScript errors on load. First: Error: &lt;svg&gt; attribute height: Expected length, "undefined". Measured on 143 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Contentinfo landmark should not be contained in another landmark — &lt;div class="mosje-visitor-counter mosje-visitor-counter-total" role="contentinfo" aria-label="Total site visits"&gt;
+					&lt;span class="mvc-item mvc-total"&gt;
+			&lt;spa (landmark-contentinfo-is-top-level, ). Measured on 145 pages.</t>
         </is>
       </c>
       <c r="F63" s="28" t="inlineStr">
         <is>
-          <t>Fix the scripting errors, starting with the first — later ones are often consequences.</t>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
         </is>
       </c>
       <c r="G63" s="28" t="n"/>
@@ -36681,12 +36683,12 @@
     <row r="64">
       <c r="A64" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-067</t>
+          <t>WEB-GLOBAL-068</t>
         </is>
       </c>
       <c r="B64" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — landmark-contentinfo-is-top-level</t>
+          <t>Global · Automated accessibility violation — landmark-no-duplicate-contentinfo</t>
         </is>
       </c>
       <c r="C64" s="28" t="inlineStr">
@@ -36701,9 +36703,7 @@
       </c>
       <c r="E64" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Contentinfo landmark should not be contained in another landmark — &lt;div class="mosje-visitor-counter mosje-visitor-counter-total" role="contentinfo" aria-label="Total site visits"&gt;
-					&lt;span class="mvc-item mvc-total"&gt;
-			&lt;spa (landmark-contentinfo-is-top-level, ). Measured on 142 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Document should not have more than one contentinfo landmark — &lt;footer data-elementor-type="footer" data-elementor-id="370" class="elementor elementor-370 elementor-location-footer" data-elementor-post-type="elementor_libra (landmark-no-duplicate-contentinfo, ). Measured on 144 pages.</t>
         </is>
       </c>
       <c r="F64" s="28" t="inlineStr">
@@ -36738,12 +36738,12 @@
     <row r="65">
       <c r="A65" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-068</t>
+          <t>WEB-GLOBAL-066</t>
         </is>
       </c>
       <c r="B65" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — landmark-no-duplicate-contentinfo</t>
+          <t>Global · Automated accessibility violation — heading-order</t>
         </is>
       </c>
       <c r="C65" s="28" t="inlineStr">
@@ -36758,7 +36758,7 @@
       </c>
       <c r="E65" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Document should not have more than one contentinfo landmark — &lt;footer data-elementor-type="footer" data-elementor-id="370" class="elementor elementor-370 elementor-location-footer" data-elementor-post-type="elementor_libra (landmark-no-duplicate-contentinfo, ). Measured on 141 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Heading levels should only increase by one — &lt;h6 class="elementor-heading-title elementor-size-default"&gt;Need Support?&lt;/h6&gt; (heading-order, ). Measured on 138 pages.</t>
         </is>
       </c>
       <c r="F65" s="28" t="inlineStr">
@@ -36793,12 +36793,12 @@
     <row r="66">
       <c r="A66" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-066</t>
+          <t>WEB-GLOBAL-081</t>
         </is>
       </c>
       <c r="B66" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — heading-order</t>
+          <t>Global · Automated accessibility violation — region</t>
         </is>
       </c>
       <c r="C66" s="28" t="inlineStr">
@@ -36813,7 +36813,7 @@
       </c>
       <c r="E66" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Heading levels should only increase by one — &lt;h6 class="elementor-heading-title elementor-size-default"&gt;Need Support?&lt;/h6&gt; (heading-order, ). Measured on 135 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: All page content should be contained by landmarks — &lt;a class="skip-link screen-reader-text" href="#content"&gt;Skip to content&lt;/a&gt; (region, ). Measured on 70 pages.</t>
         </is>
       </c>
       <c r="F66" s="28" t="inlineStr">
@@ -36824,7 +36824,7 @@
       <c r="G66" s="28" t="n"/>
       <c r="H66" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/about-the-division/</t>
+          <t>https://www.dosje.gov.in/acts-rules/</t>
         </is>
       </c>
       <c r="I66" s="28" t="inlineStr">
@@ -36848,17 +36848,17 @@
     <row r="67">
       <c r="A67" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-081</t>
+          <t>WEB-GLOBAL-071</t>
         </is>
       </c>
       <c r="B67" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — region</t>
+          <t>Global · Page title or description missing — meta description</t>
         </is>
       </c>
       <c r="C67" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D67" s="28" t="inlineStr">
@@ -36868,18 +36868,18 @@
       </c>
       <c r="E67" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: All page content should be contained by landmarks — &lt;a class="skip-link screen-reader-text" href="#content"&gt;Skip to content&lt;/a&gt; (region, ). Measured on 69 pages.</t>
+          <t>Figma: GIGW 3.0: every page publishes a descriptive title and meta description.  →  Live: The page publishes no meta description. Measured on 56 pages.</t>
         </is>
       </c>
       <c r="F67" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+          <t>Publish a page-specific title and meta description.</t>
         </is>
       </c>
       <c r="G67" s="28" t="n"/>
       <c r="H67" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/acts-rules/</t>
+          <t>https://www.dosje.gov.in/advertisement/</t>
         </is>
       </c>
       <c r="I67" s="28" t="inlineStr">
@@ -36903,12 +36903,12 @@
     <row r="68">
       <c r="A68" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-071</t>
+          <t>WEB-GLOBAL-072</t>
         </is>
       </c>
       <c r="B68" s="28" t="inlineStr">
         <is>
-          <t>Global · Page title or description missing — meta description</t>
+          <t>Global · Icon size outside the DBIM set — Icon-Container.svg</t>
         </is>
       </c>
       <c r="C68" s="28" t="inlineStr">
@@ -36923,18 +36923,18 @@
       </c>
       <c r="E68" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0: every page publishes a descriptive title and meta description.  →  Live: The page publishes no meta description. Measured on 55 pages.</t>
+          <t>Figma: DBIM 3.0 §3.7: icons are drawn at 24, 32, 48 or 64px, in proportion.  →  Live: 6 icon(s) render at sizes outside DBIM 3.7's set (24/32/48/64 px) — the first is Icon-Container.svg at 35×35px. Measured on 20 pages.</t>
         </is>
       </c>
       <c r="F68" s="28" t="inlineStr">
         <is>
-          <t>Publish a page-specific title and meta description.</t>
+          <t>Redraw or re-export the icon at 24, 32, 48 or 64px, keeping its proportion.</t>
         </is>
       </c>
       <c r="G68" s="28" t="n"/>
       <c r="H68" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/advertisement/</t>
+          <t>https://www.dosje.gov.in/home-page/for-beneficiary/</t>
         </is>
       </c>
       <c r="I68" s="28" t="inlineStr">
@@ -36958,17 +36958,17 @@
     <row r="69">
       <c r="A69" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-072</t>
+          <t>WEB-GLOBAL-076</t>
         </is>
       </c>
       <c r="B69" s="28" t="inlineStr">
         <is>
-          <t>Global · Icon size outside the DBIM set — Icon-Container.svg</t>
+          <t>Global · Font size outside the UX4G type scale — 15px text</t>
         </is>
       </c>
       <c r="C69" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D69" s="28" t="inlineStr">
@@ -36978,18 +36978,18 @@
       </c>
       <c r="E69" s="28" t="inlineStr">
         <is>
-          <t>Figma: DBIM 3.0 §3.7: icons are drawn at 24, 32, 48 or 64px, in proportion.  →  Live: 6 icon(s) render at sizes outside DBIM 3.7's set (24/32/48/64 px) — the first is Icon-Container.svg at 35×35px. Measured on 20 pages.</t>
+          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 19 element(s) render at 15px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). Measured on 19 pages.</t>
         </is>
       </c>
       <c r="F69" s="28" t="inlineStr">
         <is>
-          <t>Redraw or re-export the icon at 24, 32, 48 or 64px, keeping its proportion.</t>
+          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
         </is>
       </c>
       <c r="G69" s="28" t="n"/>
       <c r="H69" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/home-page/for-beneficiary/</t>
+          <t>https://www.dosje.gov.in/contact-us/</t>
         </is>
       </c>
       <c r="I69" s="28" t="inlineStr">
@@ -37013,12 +37013,12 @@
     <row r="70">
       <c r="A70" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-076</t>
+          <t>WEB-GLOBAL-077</t>
         </is>
       </c>
       <c r="B70" s="28" t="inlineStr">
         <is>
-          <t>Global · Font size outside the UX4G type scale — 15px text</t>
+          <t>Global · Font size outside the UX4G type scale — 22px text</t>
         </is>
       </c>
       <c r="C70" s="28" t="inlineStr">
@@ -37033,7 +37033,7 @@
       </c>
       <c r="E70" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 19 element(s) render at 15px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). Measured on 19 pages.</t>
+          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 5 element(s) render at 22px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). Measured on 19 pages.</t>
         </is>
       </c>
       <c r="F70" s="28" t="inlineStr">
@@ -37044,7 +37044,7 @@
       <c r="G70" s="28" t="n"/>
       <c r="H70" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/contact-us/</t>
+          <t>https://www.dosje.gov.in/</t>
         </is>
       </c>
       <c r="I70" s="28" t="inlineStr">
@@ -37068,17 +37068,17 @@
     <row r="71">
       <c r="A71" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-077</t>
+          <t>WEB-GLOBAL-082</t>
         </is>
       </c>
       <c r="B71" s="28" t="inlineStr">
         <is>
-          <t>Global · Font size outside the UX4G type scale — 22px text</t>
+          <t>Global · Automated accessibility violation — skip-link</t>
         </is>
       </c>
       <c r="C71" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D71" s="28" t="inlineStr">
@@ -37088,18 +37088,18 @@
       </c>
       <c r="E71" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 5 element(s) render at 22px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). Measured on 19 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: The skip-link target should exist and be focusable — &lt;a class="skip-link screen-reader-text" href="#content"&gt;Skip to content&lt;/a&gt; (skip-link, ). Measured on 7 pages.</t>
         </is>
       </c>
       <c r="F71" s="28" t="inlineStr">
         <is>
-          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
         </is>
       </c>
       <c r="G71" s="28" t="n"/>
       <c r="H71" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/</t>
+          <t>https://www.dosje.gov.in/advertisement/</t>
         </is>
       </c>
       <c r="I71" s="28" t="inlineStr">
@@ -37123,17 +37123,17 @@
     <row r="72">
       <c r="A72" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-082</t>
+          <t>WEB-GLOBAL-087</t>
         </is>
       </c>
       <c r="B72" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — skip-link</t>
+          <t>Global · Focus indicator too faint to find — Pagination page numbers</t>
         </is>
       </c>
       <c r="C72" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Components &amp; States</t>
         </is>
       </c>
       <c r="D72" s="28" t="inlineStr">
@@ -37143,18 +37143,18 @@
       </c>
       <c r="E72" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: The skip-link target should exist and be focusable — &lt;a class="skip-link screen-reader-text" href="#content"&gt;Skip to content&lt;/a&gt; (skip-link, ). Measured on 7 pages.</t>
+          <t>Figma: WCAG 2.2 AA (2.4.7): every keyboard-focusable control shows a visible focus indicator. DBIM and UX4G both draw a 4px ring.  →  Live: Pagination page numbers: screenshotted focused and then blurred, only 1.3% of the region changes — the digit turns from grey to black, with no ring or fill, which is hard to find on a page. Measured on 8 pages.</t>
         </is>
       </c>
       <c r="F72" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+          <t>Give the control a visible focus style — the estate's 4px ring — and make sure it is not removed by an `outline: none` elsewhere in the stylesheet.</t>
         </is>
       </c>
       <c r="G72" s="28" t="n"/>
       <c r="H72" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/advertisement/</t>
+          <t>https://www.dosje.gov.in/annual-reports/</t>
         </is>
       </c>
       <c r="I72" s="28" t="inlineStr">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="E108" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.11): the visible part of a control — its icon, its outline, its indicator — needs 3:1 against what is behind it.  →  Live: Text “Session Cookies always active” (input.form-check-input) renders #545454 on #0373DF at 16px/400 — measured on the capture's pixels: #FFFFFF on #90BFEC is 1.94:1 against the 3.0:1 minimum. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.11): the visible part of a control — its icon, its outline, its indicator — needs 3:1 against what is behind it.  →  Live: Text “Session Cookies always active” (input.form-check-input) renders #545454 on #0373DF at 16px/400 — #FFFFFF on #90BFEC as painted on the capture: 1.94:1 against the 3.0:1 minimum. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F108" s="28" t="inlineStr">
@@ -39178,7 +39178,7 @@
       </c>
       <c r="E109" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Ensures user session persistence, allowing seamless navigation on the…” (p.small) renders #938BB6 on #FFFFFF at 12px/400 — measured on the capture's pixels: #9A92BA on #FFFFFF is 2.92:1 against the 4.5:1 minimum. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Ensures user session persistence, allowing seamless navigation on the…” (p.small) renders #938BB6 on #FFFFFF at 12px/400 — #938BB6 on #FFFFFF as painted on the capture: 3.18:1 against the 4.5:1 minimum. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F109" s="28" t="inlineStr">
@@ -39673,7 +39673,7 @@
       </c>
       <c r="E118" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Pre-Matric (SCs &amp; Others)” (span.mosje-cat-metric-label) renders #6B6F78 on #EAF2FB at 12px/500 — measured on the capture's pixels: #999FA8 on #EAF2FB is 2.36:1 against the 4.5:1 minimum.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Pre-Matric (SCs &amp; Others)” (span.mosje-cat-metric-label) renders #6B6F78 on #EAF2FB at 12px/500 — #6B6F78 on #EAF2FB as painted on the capture: 4.46:1 against the 4.5:1 minimum.</t>
         </is>
       </c>
       <c r="F118" s="28" t="inlineStr">
@@ -40003,7 +40003,7 @@
       </c>
       <c r="E124" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “29,015” (div.mosje-hostel-num) renders #2BA84A on #FFFFFF at 20px/600 — measured on the capture's pixels: #B0DFBB on #FFFFFF is 1.49:1 against the 4.5:1 minimum.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “29,015” (div.mosje-hostel-num) renders #2BA84A on #FFFFFF at 20px/600 — #2BA84A on #FFFFFF as painted on the capture: 3.09:1 against the 4.5:1 minimum.</t>
         </is>
       </c>
       <c r="F124" s="28" t="inlineStr">
@@ -40443,7 +40443,7 @@
       </c>
       <c r="E132" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Declared” (span.badge) renders #FFFFFF on #3C9718 at 12px/500 — measured on the capture's pixels: #F9FCF7 on #3C9718 is 3.6:1 against the 4.5:1 minimum. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Declared” (span.badge) renders #FFFFFF on #3C9718 at 12px/500 — #FFFFFF on #3C9718 as painted on the capture: 3.73:1 against the 4.5:1 minimum. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F132" s="28" t="inlineStr">
@@ -40663,7 +40663,7 @@
       </c>
       <c r="E136" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Declared” (span.badge) renders #FFFFFF on #3C9718 at 12px/500 — measured on the capture's pixels: #F9FCF7 on #3C9718 is 3.6:1 against the 4.5:1 minimum. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Declared” (span.badge) renders #FFFFFF on #3C9718 at 12px/500 — #FFFFFF on #3C9718 as painted on the capture: 3.73:1 against the 4.5:1 minimum. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F136" s="28" t="inlineStr">
@@ -41578,7 +41578,7 @@
     <row r="153">
       <c r="A153" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-152</t>
+          <t>WEB-SCREEN-326</t>
         </is>
       </c>
       <c r="B153" s="28" t="inlineStr">
@@ -41588,30 +41588,30 @@
       </c>
       <c r="C153" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Components &amp; States</t>
         </is>
       </c>
       <c r="D153" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E153" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “empowering india, every day” · absent from the build  →  Live: The design frame carries “empowering india, every day” (56px). Nothing with that text renders on the live page.</t>
+          <t>Figma: WCAG 2.2 AA (2.4.7): every keyboard-focusable control shows a visible focus indicator. DBIM and UX4G both draw a 4px ring.  →  Live: Home hero banner (an unlabelled link): screenshotted focused and then blurred, no pixel changes, so a keyboard user cannot see where focus is.</t>
         </is>
       </c>
       <c r="F153" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G153" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-7805</t>
-        </is>
-      </c>
-      <c r="H153" s="28" t="n"/>
+          <t>Give the control a visible focus style — the estate's 4px ring — and make sure it is not removed by an `outline: none` elsewhere in the stylesheet.</t>
+        </is>
+      </c>
+      <c r="G153" s="28" t="n"/>
+      <c r="H153" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I153" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -41633,7 +41633,7 @@
     <row r="154">
       <c r="A154" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-150</t>
+          <t>WEB-SCREEN-152</t>
         </is>
       </c>
       <c r="B154" s="28" t="inlineStr">
@@ -41653,7 +41653,7 @@
       </c>
       <c r="E154" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “bringing social justice to every doorste” · absent from the build  →  Live: The design frame carries “bringing social justice to every doorstep through digital access” (22px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “empowering india, every day” · absent from the build  →  Live: The design frame carries “empowering india, every day” (56px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F154" s="28" t="inlineStr">
@@ -41661,12 +41661,12 @@
           <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
-      <c r="G154" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-7805</t>
-        </is>
-      </c>
-      <c r="H154" s="28" t="n"/>
+      <c r="G154" s="28" t="n"/>
+      <c r="H154" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I154" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -41688,7 +41688,7 @@
     <row r="155">
       <c r="A155" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-153</t>
+          <t>WEB-SCREEN-150</t>
         </is>
       </c>
       <c r="B155" s="28" t="inlineStr">
@@ -41708,7 +41708,7 @@
       </c>
       <c r="E155" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “explore opportunities” · absent from the build  →  Live: The design frame carries “explore opportunities” (16px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “bringing social justice to every doorste” · absent from the build  →  Live: The design frame carries “bringing social justice to every doorstep through digital access” (22px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F155" s="28" t="inlineStr">
@@ -41716,12 +41716,12 @@
           <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
-      <c r="G155" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-7805</t>
-        </is>
-      </c>
-      <c r="H155" s="28" t="n"/>
+      <c r="G155" s="28" t="n"/>
+      <c r="H155" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I155" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -41743,7 +41743,7 @@
     <row r="156">
       <c r="A156" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-169</t>
+          <t>WEB-SCREEN-153</t>
         </is>
       </c>
       <c r="B156" s="28" t="inlineStr">
@@ -41763,7 +41763,7 @@
       </c>
       <c r="E156" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “view schemes” · absent from the build  →  Live: The design frame carries “view schemes” (16px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “explore opportunities” · absent from the build  →  Live: The design frame carries “explore opportunities” (16px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F156" s="28" t="inlineStr">
@@ -41771,12 +41771,12 @@
           <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
-      <c r="G156" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-7805</t>
-        </is>
-      </c>
-      <c r="H156" s="28" t="n"/>
+      <c r="G156" s="28" t="n"/>
+      <c r="H156" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I156" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -41798,7 +41798,7 @@
     <row r="157">
       <c r="A157" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-157</t>
+          <t>WEB-SCREEN-169</t>
         </is>
       </c>
       <c r="B157" s="28" t="inlineStr">
@@ -41818,7 +41818,7 @@
       </c>
       <c r="E157" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “latest updates” · absent from the build  →  Live: The design frame carries “latest updates” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “view schemes” · absent from the build  →  Live: The design frame carries “view schemes” (16px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F157" s="28" t="inlineStr">
@@ -41826,12 +41826,12 @@
           <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
-      <c r="G157" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-7805</t>
-        </is>
-      </c>
-      <c r="H157" s="28" t="n"/>
+      <c r="G157" s="28" t="n"/>
+      <c r="H157" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I157" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -41853,7 +41853,7 @@
     <row r="158">
       <c r="A158" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-158</t>
+          <t>WEB-SCREEN-157</t>
         </is>
       </c>
       <c r="B158" s="28" t="inlineStr">
@@ -41873,7 +41873,7 @@
       </c>
       <c r="E158" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “new funding alert!” · absent from the build  →  Live: The design frame carries “new funding alert!” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “latest updates” · absent from the build  →  Live: The design frame carries “latest updates” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F158" s="28" t="inlineStr">
@@ -41881,12 +41881,12 @@
           <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
-      <c r="G158" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-7805</t>
-        </is>
-      </c>
-      <c r="H158" s="28" t="n"/>
+      <c r="G158" s="28" t="n"/>
+      <c r="H158" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I158" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -41908,7 +41908,7 @@
     <row r="159">
       <c r="A159" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-033</t>
+          <t>WEB-SCREEN-317</t>
         </is>
       </c>
       <c r="B159" s="28" t="inlineStr">
@@ -41928,7 +41928,7 @@
       </c>
       <c r="E159" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 1” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 1” is 40×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 40×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F159" s="28" t="inlineStr">
@@ -41963,7 +41963,7 @@
     <row r="160">
       <c r="A160" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-036</t>
+          <t>WEB-SCREEN-316</t>
         </is>
       </c>
       <c r="B160" s="28" t="inlineStr">
@@ -41983,7 +41983,7 @@
       </c>
       <c r="E160" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 2” is 40×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 40×12 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 2” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F160" s="28" t="inlineStr">
@@ -43448,12 +43448,12 @@
     <row r="187">
       <c r="A187" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-041</t>
+          <t>WEB-SCREEN-043</t>
         </is>
       </c>
       <c r="B187" s="28" t="inlineStr">
         <is>
-          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop</t>
+          <t>Resources · mobile</t>
         </is>
       </c>
       <c r="C187" s="28" t="inlineStr">
@@ -43468,7 +43468,7 @@
       </c>
       <c r="E187" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Home” is 38×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 38×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DWBDNC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F187" s="28" t="inlineStr">
@@ -43479,7 +43479,7 @@
       <c r="G187" s="28" t="n"/>
       <c r="H187" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/procedure-for-processing-grant-in-aid-cases-in-respect-of-voluntary-organisations/</t>
+          <t>https://www.dosje.gov.in/resources/</t>
         </is>
       </c>
       <c r="I187" s="28" t="inlineStr">
@@ -43503,17 +43503,17 @@
     <row r="188">
       <c r="A188" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-042</t>
+          <t>WEB-SCREEN-194</t>
         </is>
       </c>
       <c r="B188" s="28" t="inlineStr">
         <is>
-          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop</t>
+          <t>Rti · desktop</t>
         </is>
       </c>
       <c r="C188" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D188" s="28" t="inlineStr">
@@ -43523,20 +43523,20 @@
       </c>
       <c r="E188" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Department” is 74×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 74×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “suo-moto disclosure” · absent from the build  →  Live: The design frame carries “suo-moto disclosure” (14px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F188" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G188" s="28" t="n"/>
-      <c r="H188" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/procedure-for-processing-grant-in-aid-cases-in-respect-of-voluntary-organisations/</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G188" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
+        </is>
+      </c>
+      <c r="H188" s="28" t="n"/>
       <c r="I188" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -43558,17 +43558,17 @@
     <row r="189">
       <c r="A189" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-040</t>
+          <t>WEB-SCREEN-193</t>
         </is>
       </c>
       <c r="B189" s="28" t="inlineStr">
         <is>
-          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop</t>
+          <t>Rti · desktop</t>
         </is>
       </c>
       <c r="C189" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D189" s="28" t="inlineStr">
@@ -43578,20 +43578,20 @@
       </c>
       <c r="E189" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Associated Organisations” is 161×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 161×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “right to information act 2005” · absent from the build  →  Live: The design frame carries “right to information act 2005” (28px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F189" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G189" s="28" t="n"/>
-      <c r="H189" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/procedure-for-processing-grant-in-aid-cases-in-respect-of-voluntary-organisations/</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G189" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
+        </is>
+      </c>
+      <c r="H189" s="28" t="n"/>
       <c r="I189" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -43613,17 +43613,17 @@
     <row r="190">
       <c r="A190" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-043</t>
+          <t>WEB-SCREEN-195</t>
         </is>
       </c>
       <c r="B190" s="28" t="inlineStr">
         <is>
-          <t>Resources · mobile</t>
+          <t>Rti · desktop</t>
         </is>
       </c>
       <c r="C190" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D190" s="28" t="inlineStr">
@@ -43633,20 +43633,20 @@
       </c>
       <c r="E190" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “DWBDNC” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “the national commission for scheduled ca” · absent from the build  →  Live: The design frame carries “the national commission for scheduled castes (ncsc) is a constitutional body est” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F190" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G190" s="28" t="n"/>
-      <c r="H190" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/resources/</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G190" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
+        </is>
+      </c>
+      <c r="H190" s="28" t="n"/>
       <c r="I190" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -43668,17 +43668,17 @@
     <row r="191">
       <c r="A191" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-194</t>
+          <t>WEB-SCREEN-270</t>
         </is>
       </c>
       <c r="B191" s="28" t="inlineStr">
         <is>
-          <t>Rti · desktop</t>
+          <t>Samavesh Admin Portals · desktop</t>
         </is>
       </c>
       <c r="C191" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D191" s="28" t="inlineStr">
@@ -43688,17 +43688,17 @@
       </c>
       <c r="E191" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “suo-moto disclosure” · absent from the build  →  Live: The design frame carries “suo-moto disclosure” (14px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 700 weight · design 500 · Built #FF671F · design #1F2428  →  Live: “smile - transgender” — weight 500 → 700; colour #1F2428 → #FF671F. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F191" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+          <t>Set the built value to the design's.</t>
         </is>
       </c>
       <c r="G191" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=7298-28616</t>
         </is>
       </c>
       <c r="H191" s="28" t="n"/>
@@ -43723,17 +43723,17 @@
     <row r="192">
       <c r="A192" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-193</t>
+          <t>WEB-SCREEN-271</t>
         </is>
       </c>
       <c r="B192" s="28" t="inlineStr">
         <is>
-          <t>Rti · desktop</t>
+          <t>Samavesh Citizen Portals · desktop</t>
         </is>
       </c>
       <c r="C192" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D192" s="28" t="inlineStr">
@@ -43743,17 +43743,17 @@
       </c>
       <c r="E192" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “right to information act 2005” · absent from the build  →  Live: The design frame carries “right to information act 2005” (28px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 700 weight · design 500 · Built #FF671F · design #1F2428  →  Live: “smile - transgender” — weight 500 → 700; colour #1F2428 → #FF671F. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F192" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+          <t>Set the built value to the design's.</t>
         </is>
       </c>
       <c r="G192" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=7116-34665</t>
         </is>
       </c>
       <c r="H192" s="28" t="n"/>
@@ -43778,40 +43778,40 @@
     <row r="193">
       <c r="A193" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-195</t>
+          <t>WEB-SCREEN-009</t>
         </is>
       </c>
       <c r="B193" s="28" t="inlineStr">
         <is>
-          <t>Rti · desktop</t>
+          <t>Scheme Documents  Dr Ambedkar National Merit Award Scheme  · desktop</t>
         </is>
       </c>
       <c r="C193" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D193" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E193" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “the national commission for scheduled ca” · absent from the build  →  Live: The design frame carries “the national commission for scheduled castes (ncsc) is a constitutional body est” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Scheme: Dr. Ambedkar National Merit Award Scheme for meritorious stud…” (p.mb-0) renders #938BB6 on #F9FAFB at 16px/400 — #938BB6 on #F9FAFB as painted on the capture: 3.04:1 against the 4.5:1 minimum. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F193" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G193" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14221</t>
-        </is>
-      </c>
-      <c r="H193" s="28" t="n"/>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+        </is>
+      </c>
+      <c r="G193" s="28" t="n"/>
+      <c r="H193" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/scheme-documents/dr-ambedkar-national-merit-award-scheme-for-scs-students-for-class-12th-level/</t>
+        </is>
+      </c>
       <c r="I193" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -43833,40 +43833,40 @@
     <row r="194">
       <c r="A194" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-270</t>
+          <t>WEB-SCREEN-010</t>
         </is>
       </c>
       <c r="B194" s="28" t="inlineStr">
         <is>
-          <t>Samavesh Admin Portals · desktop</t>
+          <t>Scheme Documents  Merger Order · desktop</t>
         </is>
       </c>
       <c r="C194" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D194" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="E194" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 700 weight · design 500 · Built #FF671F · design #1F2428  →  Live: “smile - transgender” — weight 500 → 700; colour #1F2428 → #FF671F. Measured on 2 pages.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Scheme: Dr. Ambedkar Scheme for Social Integration through Inter-Cast…” (p.mb-0) renders #938BB6 on #F9FAFB at 16px/400 — #938BB6 on #F9FAFB as painted on the capture: 3.04:1 against the 4.5:1 minimum. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F194" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
-        </is>
-      </c>
-      <c r="G194" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=7298-28616</t>
-        </is>
-      </c>
-      <c r="H194" s="28" t="n"/>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+        </is>
+      </c>
+      <c r="G194" s="28" t="n"/>
+      <c r="H194" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/scheme-documents/merger-order/</t>
+        </is>
+      </c>
       <c r="I194" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -43888,17 +43888,17 @@
     <row r="195">
       <c r="A195" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-271</t>
+          <t>WEB-SCREEN-044</t>
         </is>
       </c>
       <c r="B195" s="28" t="inlineStr">
         <is>
-          <t>Samavesh Citizen Portals · desktop</t>
+          <t>Schemes And Services  Geriatric Caregivers Training · mobile</t>
         </is>
       </c>
       <c r="C195" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D195" s="28" t="inlineStr">
@@ -43908,20 +43908,20 @@
       </c>
       <c r="E195" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 700 weight · design 500 · Built #FF671F · design #1F2428  →  Live: “smile - transgender” — weight 500 → 700; colour #1F2428 → #FF671F. Measured on 2 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Senior Citizens Welfare(SCW)” is 203×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 203×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F195" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
-        </is>
-      </c>
-      <c r="G195" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=7116-34665</t>
-        </is>
-      </c>
-      <c r="H195" s="28" t="n"/>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+        </is>
+      </c>
+      <c r="G195" s="28" t="n"/>
+      <c r="H195" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/schemes-and-services/geriatric-caregivers-training/</t>
+        </is>
+      </c>
       <c r="I195" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -43943,38 +43943,38 @@
     <row r="196">
       <c r="A196" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-009</t>
+          <t>WEB-SCREEN-272</t>
         </is>
       </c>
       <c r="B196" s="28" t="inlineStr">
         <is>
-          <t>Scheme Documents  Dr Ambedkar National Merit Award Scheme  · desktop</t>
+          <t>Schemes And Services  Geriatric Caregivers Training · mobile</t>
         </is>
       </c>
       <c r="C196" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D196" s="28" t="inlineStr">
         <is>
-          <t>Blocker</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E196" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Scheme: Dr. Ambedkar National Merit Award Scheme for meritorious stud…” (p.mb-0) renders #938BB6 on #F9FAFB at 16px/400 — measured on the capture's pixels: #0373DF on #F9FAFB is 4.44:1 against the 4.5:1 minimum. Measured on 2 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 28px · design 20px · Built 500 weight · design 600  →  Live: “about the scheme” — size 20 → 28; weight 600 → 500.</t>
         </is>
       </c>
       <c r="F196" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+          <t>Set the built value to the design's.</t>
         </is>
       </c>
       <c r="G196" s="28" t="n"/>
       <c r="H196" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/scheme-documents/dr-ambedkar-national-merit-award-scheme-for-scs-students-for-class-12th-level/</t>
+          <t>https://www.dosje.gov.in/schemes-and-services/geriatric-caregivers-training/</t>
         </is>
       </c>
       <c r="I196" s="28" t="inlineStr">
@@ -43998,40 +43998,40 @@
     <row r="197">
       <c r="A197" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-010</t>
+          <t>WEB-SCREEN-275</t>
         </is>
       </c>
       <c r="B197" s="28" t="inlineStr">
         <is>
-          <t>Scheme Documents  Merger Order · desktop</t>
+          <t>Schemes And Services  Top Class Education In Colllege For Obc  · desktop</t>
         </is>
       </c>
       <c r="C197" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D197" s="28" t="inlineStr">
         <is>
-          <t>Blocker</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E197" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Scheme: Dr. Ambedkar Scheme for Social Integration through Inter-Cast…” (p.mb-0) renders #938BB6 on #F9FAFB at 16px/400 — measured on the capture's pixels: #2787E3 on #F9FAFB is 3.55:1 against the 4.5:1 minimum. Measured on 2 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #FFFFFF · design #1F2937  →  Live: “active” — weight 500 → 400; colour #1F2937 → #FFFFFF.</t>
         </is>
       </c>
       <c r="F197" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
-        </is>
-      </c>
-      <c r="G197" s="28" t="n"/>
-      <c r="H197" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/scheme-documents/merger-order/</t>
-        </is>
-      </c>
+          <t>Set the built value to the design's.</t>
+        </is>
+      </c>
+      <c r="G197" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-11885</t>
+        </is>
+      </c>
+      <c r="H197" s="28" t="n"/>
       <c r="I197" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -44053,40 +44053,40 @@
     <row r="198">
       <c r="A198" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-044</t>
+          <t>WEB-SCREEN-281</t>
         </is>
       </c>
       <c r="B198" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Geriatric Caregivers Training · mobile</t>
+          <t>Schemes And Services  Top Class Education In Colllege For Obc  · desktop</t>
         </is>
       </c>
       <c r="C198" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D198" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E198" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Senior Citizens Welfare(SCW)” is 203×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 203×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500  →  Live: “scheme” — weight 500 → 400.</t>
         </is>
       </c>
       <c r="F198" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G198" s="28" t="n"/>
-      <c r="H198" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/schemes-and-services/geriatric-caregivers-training/</t>
-        </is>
-      </c>
+          <t>Set the built value to the design's.</t>
+        </is>
+      </c>
+      <c r="G198" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-11885</t>
+        </is>
+      </c>
+      <c r="H198" s="28" t="n"/>
       <c r="I198" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -44108,12 +44108,12 @@
     <row r="199">
       <c r="A199" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-272</t>
+          <t>WEB-SCREEN-274</t>
         </is>
       </c>
       <c r="B199" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Geriatric Caregivers Training · mobile</t>
+          <t>Schemes And Services  Top Class Education In Colllege For Obc  · mobile</t>
         </is>
       </c>
       <c r="C199" s="28" t="inlineStr">
@@ -44128,7 +44128,7 @@
       </c>
       <c r="E199" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 28px · design 20px · Built 500 weight · design 600  →  Live: “about the scheme” — size 20 → 28; weight 600 → 500.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #FFFFFF · design #1F2428  →  Live: “active” — weight 500 → 400; colour #1F2428 → #FFFFFF.</t>
         </is>
       </c>
       <c r="F199" s="28" t="inlineStr">
@@ -44136,12 +44136,12 @@
           <t>Set the built value to the design's.</t>
         </is>
       </c>
-      <c r="G199" s="28" t="n"/>
-      <c r="H199" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/schemes-and-services/geriatric-caregivers-training/</t>
-        </is>
-      </c>
+      <c r="G199" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105399</t>
+        </is>
+      </c>
+      <c r="H199" s="28" t="n"/>
       <c r="I199" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -44163,12 +44163,12 @@
     <row r="200">
       <c r="A200" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-275</t>
+          <t>WEB-SCREEN-276</t>
         </is>
       </c>
       <c r="B200" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Top Class Education In Colllege For Obc  · desktop</t>
+          <t>Schemes And Services  Top Class Education In Colllege For Obc  · mobile</t>
         </is>
       </c>
       <c r="C200" s="28" t="inlineStr">
@@ -44183,7 +44183,7 @@
       </c>
       <c r="E200" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #FFFFFF · design #1F2937  →  Live: “active” — weight 500 → 400; colour #1F2937 → #FFFFFF.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #374151 · design #343A40  →  Live: “archived” — weight 500 → 400; colour #343A40 → #374151.</t>
         </is>
       </c>
       <c r="F200" s="28" t="inlineStr">
@@ -44193,7 +44193,7 @@
       </c>
       <c r="G200" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-11885</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105399</t>
         </is>
       </c>
       <c r="H200" s="28" t="n"/>
@@ -44218,12 +44218,12 @@
     <row r="201">
       <c r="A201" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-281</t>
+          <t>WEB-SCREEN-273</t>
         </is>
       </c>
       <c r="B201" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Top Class Education In Colllege For Obc  · desktop</t>
+          <t>Schemes And Services  Top Class Education In Colllege For Obc  · mobile</t>
         </is>
       </c>
       <c r="C201" s="28" t="inlineStr">
@@ -44233,12 +44233,12 @@
       </c>
       <c r="D201" s="28" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E201" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500  →  Live: “scheme” — weight 500 → 400.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 12px · Built 500 weight · design 400 · Built #1F2937 · design #343A40  →  Live: “start publish date” — size 12 → 14; weight 400 → 500; colour #343A40 → #1F2937.</t>
         </is>
       </c>
       <c r="F201" s="28" t="inlineStr">
@@ -44248,7 +44248,7 @@
       </c>
       <c r="G201" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-11885</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105399</t>
         </is>
       </c>
       <c r="H201" s="28" t="n"/>
@@ -44273,17 +44273,17 @@
     <row r="202">
       <c r="A202" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-274</t>
+          <t>WEB-SCREEN-204</t>
         </is>
       </c>
       <c r="B202" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Top Class Education In Colllege For Obc  · mobile</t>
+          <t>Schemes Services · desktop</t>
         </is>
       </c>
       <c r="C202" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D202" s="28" t="inlineStr">
@@ -44293,17 +44293,17 @@
       </c>
       <c r="E202" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #FFFFFF · design #1F2428  →  Live: “active” — weight 500 → 400; colour #1F2428 → #FFFFFF.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “schemes and services” · absent from the build  →  Live: The design frame carries “schemes and services” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F202" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
       <c r="G202" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105399</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
         </is>
       </c>
       <c r="H202" s="28" t="n"/>
@@ -44328,17 +44328,17 @@
     <row r="203">
       <c r="A203" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-276</t>
+          <t>WEB-SCREEN-199</t>
         </is>
       </c>
       <c r="B203" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Top Class Education In Colllege For Obc  · mobile</t>
+          <t>Schemes Services · desktop</t>
         </is>
       </c>
       <c r="C203" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D203" s="28" t="inlineStr">
@@ -44348,17 +44348,17 @@
       </c>
       <c r="E203" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 400 weight · design 500 · Built #374151 · design #343A40  →  Live: “archived” — weight 500 → 400; colour #343A40 → #374151.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “explore welfare schemes, social empowerm” · absent from the build  →  Live: The design frame carries “explore welfare schemes, social empowerment programs, and citizen services offer” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F203" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
       <c r="G203" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105399</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
         </is>
       </c>
       <c r="H203" s="28" t="n"/>
@@ -44383,17 +44383,17 @@
     <row r="204">
       <c r="A204" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-273</t>
+          <t>WEB-SCREEN-205</t>
         </is>
       </c>
       <c r="B204" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Top Class Education In Colllege For Obc  · mobile</t>
+          <t>Schemes Services · desktop</t>
         </is>
       </c>
       <c r="C204" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D204" s="28" t="inlineStr">
@@ -44403,17 +44403,17 @@
       </c>
       <c r="E204" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 12px · Built 500 weight · design 400 · Built #1F2937 · design #343A40  →  Live: “start publish date” — size 12 → 14; weight 400 → 500; colour #343A40 → #1F2937.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by scheme name or keyword” · absent from the build  →  Live: The design frame carries “search by scheme name or keyword” (16px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F204" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
       <c r="G204" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105399</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
         </is>
       </c>
       <c r="H204" s="28" t="n"/>
@@ -44438,7 +44438,7 @@
     <row r="205">
       <c r="A205" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-204</t>
+          <t>WEB-SCREEN-207</t>
         </is>
       </c>
       <c r="B205" s="28" t="inlineStr">
@@ -44458,7 +44458,7 @@
       </c>
       <c r="E205" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “schemes and services” · absent from the build  →  Live: The design frame carries “schemes and services” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “smile - support for marginalised individ” · absent from the build  →  Live: The design frame carries “smile - support for marginalised individuals for livelihood &amp; enterprise” (16px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F205" s="28" t="inlineStr">
@@ -44493,7 +44493,7 @@
     <row r="206">
       <c r="A206" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-199</t>
+          <t>WEB-SCREEN-200</t>
         </is>
       </c>
       <c r="B206" s="28" t="inlineStr">
@@ -44513,7 +44513,7 @@
       </c>
       <c r="E206" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “explore welfare schemes, social empowerm” · absent from the build  →  Live: The design frame carries “explore welfare schemes, social empowerment programs, and citizen services offer” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “integrated rehabilitation, skills traini” · absent from the build  →  Live: The design frame carries “integrated rehabilitation, skills training and livelihood support for marginalis” (14px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F206" s="28" t="inlineStr">
@@ -44548,7 +44548,7 @@
     <row r="207">
       <c r="A207" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-205</t>
+          <t>WEB-SCREEN-203</t>
         </is>
       </c>
       <c r="B207" s="28" t="inlineStr">
@@ -44568,7 +44568,7 @@
       </c>
       <c r="E207" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by scheme name or keyword” · absent from the build  →  Live: The design frame carries “search by scheme name or keyword” (16px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “scheme for economic empowerment of dnts ” · absent from the build  →  Live: The design frame carries “scheme for economic empowerment of dnts (seed)” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F207" s="28" t="inlineStr">
@@ -44603,12 +44603,12 @@
     <row r="208">
       <c r="A208" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-207</t>
+          <t>WEB-SCREEN-209</t>
         </is>
       </c>
       <c r="B208" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop</t>
+          <t>Schemes Services · mobile</t>
         </is>
       </c>
       <c r="C208" s="28" t="inlineStr">
@@ -44623,7 +44623,7 @@
       </c>
       <c r="E208" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “smile - support for marginalised individ” · absent from the build  →  Live: The design frame carries “smile - support for marginalised individuals for livelihood &amp; enterprise” (16px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “venture capital fund for scs &amp; obcs” · absent from the build  →  Live: The design frame carries “venture capital fund for scs &amp; obcs” (16px). Nothing with that text renders on the live page. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F208" s="28" t="inlineStr">
@@ -44633,7 +44633,7 @@
       </c>
       <c r="G208" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105022</t>
         </is>
       </c>
       <c r="H208" s="28" t="n"/>
@@ -44658,17 +44658,17 @@
     <row r="209">
       <c r="A209" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-200</t>
+          <t>WEB-SCREEN-277</t>
         </is>
       </c>
       <c r="B209" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop</t>
+          <t>Sitemap · desktop</t>
         </is>
       </c>
       <c r="C209" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D209" s="28" t="inlineStr">
@@ -44678,17 +44678,17 @@
       </c>
       <c r="E209" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “integrated rehabilitation, skills traini” · absent from the build  →  Live: The design frame carries “integrated rehabilitation, skills training and livelihood support for marginalis” (14px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 16px · Built #0373DF · design #014B92  →  Live: “dashboard” — size 16 → 14; colour #014B92 → #0373DF.</t>
         </is>
       </c>
       <c r="F209" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+          <t>Set the built value to the design's.</t>
         </is>
       </c>
       <c r="G209" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=5243-134590</t>
         </is>
       </c>
       <c r="H209" s="28" t="n"/>
@@ -44713,17 +44713,17 @@
     <row r="210">
       <c r="A210" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-203</t>
+          <t>WEB-SCREEN-286</t>
         </is>
       </c>
       <c r="B210" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop</t>
+          <t>State · Accessibility Panel Open · desktop</t>
         </is>
       </c>
       <c r="C210" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D210" s="28" t="inlineStr">
@@ -44733,20 +44733,20 @@
       </c>
       <c r="E210" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “scheme for economic empowerment of dnts ” · absent from the build  →  Live: The design frame carries “scheme for economic empowerment of dnts (seed)” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Interactive controls must not be nested — &lt;button aria-label="Light Dark Theme" aria-pressed="false" tabindex="9" id="dark-btn" class="uwaw-features__item__i"&gt; (nested-interactive, wcag2a, wcag412).</t>
         </is>
       </c>
       <c r="F210" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G210" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12250</t>
-        </is>
-      </c>
-      <c r="H210" s="28" t="n"/>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+        </is>
+      </c>
+      <c r="G210" s="28" t="n"/>
+      <c r="H210" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I210" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -44768,17 +44768,17 @@
     <row r="211">
       <c r="A211" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-209</t>
+          <t>WEB-SCREEN-287</t>
         </is>
       </c>
       <c r="B211" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · mobile</t>
+          <t>State · Accessibility Panel Open · desktop</t>
         </is>
       </c>
       <c r="C211" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D211" s="28" t="inlineStr">
@@ -44788,20 +44788,20 @@
       </c>
       <c r="E211" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “venture capital fund for scs &amp; obcs” · absent from the build  →  Live: The design frame carries “venture capital fund for scs &amp; obcs” (16px). Nothing with that text renders on the live page. Measured on 2 pages.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Elements should not have tabindex greater than zero — &lt;button type="button" aria-label="Close main navigation panel" class="uwaw-close" tabindex="1"&gt;&lt;/button&gt; (tabindex, ).</t>
         </is>
       </c>
       <c r="F211" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G211" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105022</t>
-        </is>
-      </c>
-      <c r="H211" s="28" t="n"/>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+        </is>
+      </c>
+      <c r="G211" s="28" t="n"/>
+      <c r="H211" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I211" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -44823,12 +44823,12 @@
     <row r="212">
       <c r="A212" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-277</t>
+          <t>WEB-SCREEN-291</t>
         </is>
       </c>
       <c r="B212" s="28" t="inlineStr">
         <is>
-          <t>Sitemap · desktop</t>
+          <t>State · Accessibility Panel Open · desktop</t>
         </is>
       </c>
       <c r="C212" s="28" t="inlineStr">
@@ -44838,25 +44838,25 @@
       </c>
       <c r="D212" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E212" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 14px · design 16px · Built #0373DF · design #014B92  →  Live: “dashboard” — size 16 → 14; colour #014B92 → #0373DF.</t>
+          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 14 element(s) render at 13px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F212" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
-        </is>
-      </c>
-      <c r="G212" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=5243-134590</t>
-        </is>
-      </c>
-      <c r="H212" s="28" t="n"/>
+          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
+        </is>
+      </c>
+      <c r="G212" s="28" t="n"/>
+      <c r="H212" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/</t>
+        </is>
+      </c>
       <c r="I212" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -44878,12 +44878,12 @@
     <row r="213">
       <c r="A213" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-286</t>
+          <t>WEB-SCREEN-315</t>
         </is>
       </c>
       <c r="B213" s="28" t="inlineStr">
         <is>
-          <t>State · Accessibility Panel Open · desktop</t>
+          <t>State · Gallery Card Opens · desktop</t>
         </is>
       </c>
       <c r="C213" s="28" t="inlineStr">
@@ -44898,7 +44898,7 @@
       </c>
       <c r="E213" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Interactive controls must not be nested — &lt;button aria-label="Light Dark Theme" aria-pressed="false" tabindex="9" id="dark-btn" class="uwaw-features__item__i"&gt; (nested-interactive, wcag2a, wcag412).</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: &lt;svg&gt; elements with an img role must have an alternative text — &lt;svg viewBox="0 0 24 24" role="img" tabindex="-1" xmlns="http://www.w3.org/2000/svg"&gt;&lt;circle cx="10" cy="10" r="7"&gt;&lt;/circle&gt;&lt;path d="M16 16 L21 21"&gt;&lt;/path&gt;&lt;/svg (svg-img-alt, wcag2a, wcag111). Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F213" s="28" t="inlineStr">
@@ -44909,7 +44909,7 @@
       <c r="G213" s="28" t="n"/>
       <c r="H213" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/</t>
+          <t>https://www.dosje.gov.in/gallery/</t>
         </is>
       </c>
       <c r="I213" s="28" t="inlineStr">
@@ -44933,12 +44933,12 @@
     <row r="214">
       <c r="A214" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-287</t>
+          <t>WEB-SCREEN-016</t>
         </is>
       </c>
       <c r="B214" s="28" t="inlineStr">
         <is>
-          <t>State · Accessibility Panel Open · desktop</t>
+          <t>State · Gallery Lightbox · desktop</t>
         </is>
       </c>
       <c r="C214" s="28" t="inlineStr">
@@ -44953,7 +44953,7 @@
       </c>
       <c r="E214" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: Elements should not have tabindex greater than zero — &lt;button type="button" aria-label="Close main navigation panel" class="uwaw-close" tabindex="1"&gt;&lt;/button&gt; (tabindex, ).</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: &lt;svg&gt; elements with an img role must have an alternative text — &lt;svg viewBox="0 0 24 24" role="img" tabindex="-1" xmlns="http://www.w3.org/2000/svg"&gt;&lt;circle cx="10" cy="10" r="7"&gt;&lt;/circle&gt;&lt;path d="M16 16 L21 21"&gt;&lt;/path&gt;&lt;/svg (svg-img-alt, wcag2a, wcag111). Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F214" s="28" t="inlineStr">
@@ -44964,7 +44964,7 @@
       <c r="G214" s="28" t="n"/>
       <c r="H214" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/</t>
+          <t>https://www.dosje.gov.in/gallery/</t>
         </is>
       </c>
       <c r="I214" s="28" t="inlineStr">
@@ -44988,32 +44988,32 @@
     <row r="215">
       <c r="A215" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-291</t>
+          <t>WEB-SCREEN-048</t>
         </is>
       </c>
       <c r="B215" s="28" t="inlineStr">
         <is>
-          <t>State · Accessibility Panel Open · desktop</t>
+          <t>State · Home 320 · mobile320</t>
         </is>
       </c>
       <c r="C215" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D215" s="28" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E215" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §2.3: font sizes come from the published type scale (12/14/16/18/20/24/28/32/36/40/52/60), and Body/XS 12px is the minimum.  →  Live: 14 element(s) render at 13px, which is not on the UX4G type scale (12/14/16/18/20/24/28/32/36/40/52/60). Measured on 2 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 1” is 40×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 40×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F215" s="28" t="inlineStr">
         <is>
-          <t>Move the size to the nearest step on the UX4G scale, and never below 12px.</t>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
         </is>
       </c>
       <c r="G215" s="28" t="n"/>
@@ -45043,17 +45043,17 @@
     <row r="216">
       <c r="A216" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-016</t>
+          <t>WEB-SCREEN-045</t>
         </is>
       </c>
       <c r="B216" s="28" t="inlineStr">
         <is>
-          <t>State · Gallery Lightbox · desktop</t>
+          <t>State · Home 320 · mobile320</t>
         </is>
       </c>
       <c r="C216" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D216" s="28" t="inlineStr">
@@ -45063,18 +45063,18 @@
       </c>
       <c r="E216" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: &lt;svg&gt; elements with an img role must have an alternative text — &lt;svg viewBox="0 0 24 24" role="img" tabindex="-1" xmlns="http://www.w3.org/2000/svg"&gt;&lt;circle cx="10" cy="10" r="7"&gt;&lt;/circle&gt;&lt;path d="M16 16 L21 21"&gt;&lt;/path&gt;&lt;/svg (svg-img-alt, wcag2a, wcag111).</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 2” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F216" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
         </is>
       </c>
       <c r="G216" s="28" t="n"/>
       <c r="H216" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/gallery/</t>
+          <t>https://www.dosje.gov.in/</t>
         </is>
       </c>
       <c r="I216" s="28" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="217">
       <c r="A217" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-048</t>
+          <t>WEB-SCREEN-046</t>
         </is>
       </c>
       <c r="B217" s="28" t="inlineStr">
@@ -45118,7 +45118,7 @@
       </c>
       <c r="E217" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 1” is 40×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 40×12 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 3” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F217" s="28" t="inlineStr">
@@ -45153,7 +45153,7 @@
     <row r="218">
       <c r="A218" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-045</t>
+          <t>WEB-SCREEN-047</t>
         </is>
       </c>
       <c r="B218" s="28" t="inlineStr">
@@ -45173,7 +45173,7 @@
       </c>
       <c r="E218" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 2” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 4” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F218" s="28" t="inlineStr">
@@ -45208,12 +45208,12 @@
     <row r="219">
       <c r="A219" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-046</t>
+          <t>WEB-SCREEN-049</t>
         </is>
       </c>
       <c r="B219" s="28" t="inlineStr">
         <is>
-          <t>State · Home 320 · mobile320</t>
+          <t>State · Home Hindi · desktop</t>
         </is>
       </c>
       <c r="C219" s="28" t="inlineStr">
@@ -45228,7 +45228,7 @@
       </c>
       <c r="E219" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 3” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “घर” is 15×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 15×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F219" s="28" t="inlineStr">
@@ -45263,12 +45263,12 @@
     <row r="220">
       <c r="A220" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-047</t>
+          <t>WEB-SCREEN-050</t>
         </is>
       </c>
       <c r="B220" s="28" t="inlineStr">
         <is>
-          <t>State · Home 320 · mobile320</t>
+          <t>State · Home Hindi · desktop</t>
         </is>
       </c>
       <c r="C220" s="28" t="inlineStr">
@@ -45283,7 +45283,7 @@
       </c>
       <c r="E220" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Go to slide 4” is 12×12px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 12×12 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “विभाग” is 34×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 34×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F220" s="28" t="inlineStr">
@@ -45318,7 +45318,7 @@
     <row r="221">
       <c r="A221" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-049</t>
+          <t>WEB-SCREEN-051</t>
         </is>
       </c>
       <c r="B221" s="28" t="inlineStr">
@@ -45338,7 +45338,7 @@
       </c>
       <c r="E221" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “घर” is 15×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 15×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “संबद्ध संगठन” is 68×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 68×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F221" s="28" t="inlineStr">
@@ -45373,17 +45373,17 @@
     <row r="222">
       <c r="A222" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-050</t>
+          <t>WEB-SCREEN-017</t>
         </is>
       </c>
       <c r="B222" s="28" t="inlineStr">
         <is>
-          <t>State · Home Hindi · desktop</t>
+          <t>State · Important Links Modal · desktop</t>
         </is>
       </c>
       <c r="C222" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="D222" s="28" t="inlineStr">
@@ -45393,12 +45393,12 @@
       </c>
       <c r="E222" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “विभाग” is 34×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 34×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: ARIA dialog and alertdialog nodes should have an accessible name — &lt;div class="modal fade modal-links show" id="exampleModal" tabindex="-1" aria-labelledby="exampleModalLabel" aria-modal="true" role="dialog" style="display: blo (aria-dialog-name, ).</t>
         </is>
       </c>
       <c r="F222" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
         </is>
       </c>
       <c r="G222" s="28" t="n"/>
@@ -45428,12 +45428,12 @@
     <row r="223">
       <c r="A223" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-051</t>
+          <t>WEB-SCREEN-052</t>
         </is>
       </c>
       <c r="B223" s="28" t="inlineStr">
         <is>
-          <t>State · Home Hindi · desktop</t>
+          <t>State · Mega Menu Department · desktop</t>
         </is>
       </c>
       <c r="C223" s="28" t="inlineStr">
@@ -45448,7 +45448,7 @@
       </c>
       <c r="E223" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “संबद्ध संगठन” is 68×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 68×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Close Department” is 14×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 14×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F223" s="28" t="inlineStr">
@@ -45483,17 +45483,17 @@
     <row r="224">
       <c r="A224" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-017</t>
+          <t>WEB-SCREEN-022</t>
         </is>
       </c>
       <c r="B224" s="28" t="inlineStr">
         <is>
-          <t>State · Important Links Modal · desktop</t>
+          <t>State · Search Scholarship · desktop</t>
         </is>
       </c>
       <c r="C224" s="28" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D224" s="28" t="inlineStr">
@@ -45503,18 +45503,18 @@
       </c>
       <c r="E224" s="28" t="inlineStr">
         <is>
-          <t>Figma: GIGW 3.0 mandates WCAG 2.2 AA conformance; axe-core tests a subset of it programmatically.  →  Live: ARIA dialog and alertdialog nodes should have an accessible name — &lt;div class="modal fade modal-links show" id="exampleModal" tabindex="-1" aria-labelledby="exampleModalLabel" aria-modal="true" role="dialog" style="display: blo (aria-dialog-name, ).</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Scholarship” (mark) renders #0373DF on #FFF3CD at 16px/600 — #0373DF on #FFF3CD as painted on the capture: 4.19:1 against the 4.5:1 minimum.</t>
         </is>
       </c>
       <c r="F224" s="28" t="inlineStr">
         <is>
-          <t>Correct the markup the rule names; the rule's help page states the accepted fixes.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G224" s="28" t="n"/>
       <c r="H224" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/</t>
+          <t>https://www.dosje.gov.in/?s=scholarship</t>
         </is>
       </c>
       <c r="I224" s="28" t="inlineStr">
@@ -45538,17 +45538,17 @@
     <row r="225">
       <c r="A225" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-052</t>
+          <t>WEB-SCREEN-023</t>
         </is>
       </c>
       <c r="B225" s="28" t="inlineStr">
         <is>
-          <t>State · Mega Menu Department · desktop</t>
+          <t>State · Search Scholarship · desktop</t>
         </is>
       </c>
       <c r="C225" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D225" s="28" t="inlineStr">
@@ -45558,18 +45558,18 @@
       </c>
       <c r="E225" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Close Department” is 14×21px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 14×21 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “…” (span.page-link) renders #938BB6 on #FFFFFF at 14px/400 — #938BB6 on #FFFFFF as painted on the capture: 3.18:1 against the 4.5:1 minimum.</t>
         </is>
       </c>
       <c r="F225" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
         </is>
       </c>
       <c r="G225" s="28" t="n"/>
       <c r="H225" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/</t>
+          <t>https://www.dosje.gov.in/?s=scholarship</t>
         </is>
       </c>
       <c r="I225" s="28" t="inlineStr">
@@ -45593,17 +45593,17 @@
     <row r="226">
       <c r="A226" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-022</t>
+          <t>WEB-SCREEN-212</t>
         </is>
       </c>
       <c r="B226" s="28" t="inlineStr">
         <is>
-          <t>State · Search Scholarship · desktop</t>
+          <t>Suo Moto Disclosure · desktop</t>
         </is>
       </c>
       <c r="C226" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D226" s="28" t="inlineStr">
@@ -45613,20 +45613,20 @@
       </c>
       <c r="E226" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Scholarship” (mark) renders #0373DF on #FFF3CD at 16px/600 — measured on the capture's pixels: #0373DF on #FFF3CD is 4.19:1 against the 4.5:1 minimum.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “government's proactive release of key in” · absent from the build  →  Live: The design frame carries “government's proactive release of key information to ensure transparency without” (16px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F226" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
-        </is>
-      </c>
-      <c r="G226" s="28" t="n"/>
-      <c r="H226" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/?s=scholarship</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G226" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14426</t>
+        </is>
+      </c>
+      <c r="H226" s="28" t="n"/>
       <c r="I226" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -45648,17 +45648,17 @@
     <row r="227">
       <c r="A227" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-023</t>
+          <t>WEB-SCREEN-221</t>
         </is>
       </c>
       <c r="B227" s="28" t="inlineStr">
         <is>
-          <t>State · Search Scholarship · desktop</t>
+          <t>Suo Moto Disclosure · desktop</t>
         </is>
       </c>
       <c r="C227" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D227" s="28" t="inlineStr">
@@ -45668,20 +45668,20 @@
       </c>
       <c r="E227" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “…” (span.page-link) renders #938BB6 on #FFFFFF at 14px/400 — measured on the capture's pixels: #DEE2E6 on #FFFFFF is 1.3:1 against the 4.5:1 minimum.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “sort by recently updated” · absent from the build  →  Live: The design frame carries “sort by recently updated” (14px). Nothing with that text renders on the live page. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F227" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
-        </is>
-      </c>
-      <c r="G227" s="28" t="n"/>
-      <c r="H227" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/?s=scholarship</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G227" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14426</t>
+        </is>
+      </c>
+      <c r="H227" s="28" t="n"/>
       <c r="I227" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -45703,7 +45703,7 @@
     <row r="228">
       <c r="A228" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-212</t>
+          <t>WEB-SCREEN-218</t>
         </is>
       </c>
       <c r="B228" s="28" t="inlineStr">
@@ -45723,7 +45723,7 @@
       </c>
       <c r="E228" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “government's proactive release of key in” · absent from the build  →  Live: The design frame carries “government's proactive release of key information to ensure transparency without” (16px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of faa” · absent from the build  →  Live: The design frame carries “list of faa” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F228" s="28" t="inlineStr">
@@ -45758,7 +45758,7 @@
     <row r="229">
       <c r="A229" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-221</t>
+          <t>WEB-SCREEN-215</t>
         </is>
       </c>
       <c r="B229" s="28" t="inlineStr">
@@ -45778,7 +45778,7 @@
       </c>
       <c r="E229" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “sort by recently updated” · absent from the build  →  Live: The design frame carries “sort by recently updated” (14px). Nothing with that text renders on the live page. Measured on 2 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of cpio” · absent from the build  →  Live: The design frame carries “list of cpio” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F229" s="28" t="inlineStr">
@@ -45813,7 +45813,7 @@
     <row r="230">
       <c r="A230" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-218</t>
+          <t>WEB-SCREEN-216</t>
         </is>
       </c>
       <c r="B230" s="28" t="inlineStr">
@@ -45833,7 +45833,7 @@
       </c>
       <c r="E230" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of faa” · absent from the build  →  Live: The design frame carries “list of faa” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of cpio and faa” · absent from the build  →  Live: The design frame carries “list of cpio and faa” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F230" s="28" t="inlineStr">
@@ -45868,7 +45868,7 @@
     <row r="231">
       <c r="A231" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-215</t>
+          <t>WEB-SCREEN-217</t>
         </is>
       </c>
       <c r="B231" s="28" t="inlineStr">
@@ -45888,7 +45888,7 @@
       </c>
       <c r="E231" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of cpio” · absent from the build  →  Live: The design frame carries “list of cpio” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of cpios and faas” · absent from the build  →  Live: The design frame carries “list of cpios and faas” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F231" s="28" t="inlineStr">
@@ -45923,17 +45923,17 @@
     <row r="232">
       <c r="A232" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-216</t>
+          <t>WEB-SCREEN-053</t>
         </is>
       </c>
       <c r="B232" s="28" t="inlineStr">
         <is>
-          <t>Suo Moto Disclosure · desktop</t>
+          <t>Supreme Court Judgement · mobile</t>
         </is>
       </c>
       <c r="C232" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D232" s="28" t="inlineStr">
@@ -45943,20 +45943,20 @@
       </c>
       <c r="E232" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of cpio and faa” · absent from the build  →  Live: The design frame carries “list of cpio and faa” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NCSK” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F232" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G232" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14426</t>
-        </is>
-      </c>
-      <c r="H232" s="28" t="n"/>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+        </is>
+      </c>
+      <c r="G232" s="28" t="n"/>
+      <c r="H232" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/supreme-court-judgement/</t>
+        </is>
+      </c>
       <c r="I232" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -45978,12 +45978,12 @@
     <row r="233">
       <c r="A233" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-217</t>
+          <t>WEB-SCREEN-222</t>
         </is>
       </c>
       <c r="B233" s="28" t="inlineStr">
         <is>
-          <t>Suo Moto Disclosure · desktop</t>
+          <t>Tenders · desktop</t>
         </is>
       </c>
       <c r="C233" s="28" t="inlineStr">
@@ -45998,7 +45998,7 @@
       </c>
       <c r="E233" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “list of cpios and faas” · absent from the build  →  Live: The design frame carries “list of cpios and faas” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by tender name or keyword” · absent from the build  →  Live: The design frame carries “search by tender name or keyword” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F233" s="28" t="inlineStr">
@@ -46008,7 +46008,7 @@
       </c>
       <c r="G233" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-14426</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12568</t>
         </is>
       </c>
       <c r="H233" s="28" t="n"/>
@@ -46033,17 +46033,17 @@
     <row r="234">
       <c r="A234" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-053</t>
+          <t>WEB-SCREEN-278</t>
         </is>
       </c>
       <c r="B234" s="28" t="inlineStr">
         <is>
-          <t>Supreme Court Judgement · mobile</t>
+          <t>Tenders · desktop</t>
         </is>
       </c>
       <c r="C234" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D234" s="28" t="inlineStr">
@@ -46053,20 +46053,20 @@
       </c>
       <c r="E234" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NCSK” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built #374151 · design #343A40  →  Live: “archived” — colour #343A40 → #374151. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F234" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G234" s="28" t="n"/>
-      <c r="H234" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/supreme-court-judgement/</t>
-        </is>
-      </c>
+          <t>Set the built value to the design's.</t>
+        </is>
+      </c>
+      <c r="G234" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12568</t>
+        </is>
+      </c>
+      <c r="H234" s="28" t="n"/>
       <c r="I234" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -46088,17 +46088,17 @@
     <row r="235">
       <c r="A235" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-222</t>
+          <t>WEB-SCREEN-054</t>
         </is>
       </c>
       <c r="B235" s="28" t="inlineStr">
         <is>
-          <t>Tenders · desktop</t>
+          <t>Tenders · mobile</t>
         </is>
       </c>
       <c r="C235" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D235" s="28" t="inlineStr">
@@ -46108,20 +46108,20 @@
       </c>
       <c r="E235" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by tender name or keyword” · absent from the build  →  Live: The design frame carries “search by tender name or keyword” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NSFDC” is 47×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 47×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F235" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G235" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12568</t>
-        </is>
-      </c>
-      <c r="H235" s="28" t="n"/>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+        </is>
+      </c>
+      <c r="G235" s="28" t="n"/>
+      <c r="H235" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/tenders/</t>
+        </is>
+      </c>
       <c r="I235" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -46143,27 +46143,27 @@
     <row r="236">
       <c r="A236" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-278</t>
+          <t>WEB-SCREEN-282</t>
         </is>
       </c>
       <c r="B236" s="28" t="inlineStr">
         <is>
-          <t>Tenders · desktop</t>
+          <t>Tenders · mobile</t>
         </is>
       </c>
       <c r="C236" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D236" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E236" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built #374151 · design #343A40  →  Live: “archived” — colour #343A40 → #374151. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 16px · design 14px  →  Live: “explore current tender notices, eligibility details, and submission gu” — size 14 → 16. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F236" s="28" t="inlineStr">
@@ -46171,12 +46171,12 @@
           <t>Set the built value to the design's.</t>
         </is>
       </c>
-      <c r="G236" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12568</t>
-        </is>
-      </c>
-      <c r="H236" s="28" t="n"/>
+      <c r="G236" s="28" t="n"/>
+      <c r="H236" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/tenders/</t>
+        </is>
+      </c>
       <c r="I236" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -46198,7 +46198,7 @@
     <row r="237">
       <c r="A237" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-054</t>
+          <t>WEB-SCREEN-283</t>
         </is>
       </c>
       <c r="B237" s="28" t="inlineStr">
@@ -46208,22 +46208,22 @@
       </c>
       <c r="C237" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Typography</t>
         </is>
       </c>
       <c r="D237" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E237" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NSFDC” is 47×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 47×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Built 22px · design 20px  →  Live: “active tenders” — size 20 → 22.</t>
         </is>
       </c>
       <c r="F237" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+          <t>Set the built value to the design's.</t>
         </is>
       </c>
       <c r="G237" s="28" t="n"/>
@@ -46253,38 +46253,38 @@
     <row r="238">
       <c r="A238" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-282</t>
+          <t>WEB-SCREEN-055</t>
         </is>
       </c>
       <c r="B238" s="28" t="inlineStr">
         <is>
-          <t>Tenders · mobile</t>
+          <t>Updates · mobile</t>
         </is>
       </c>
       <c r="C238" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D238" s="28" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E238" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 16px · design 14px  →  Live: “explore current tender notices, eligibility details, and submission gu” — size 14 → 16. Measured on 2 pages.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NOS” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F238" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
         </is>
       </c>
       <c r="G238" s="28" t="n"/>
       <c r="H238" s="28" t="inlineStr">
         <is>
-          <t>https://www.dosje.gov.in/tenders/</t>
+          <t>https://www.dosje.gov.in/updates/</t>
         </is>
       </c>
       <c r="I238" s="28" t="inlineStr">
@@ -46308,40 +46308,40 @@
     <row r="239">
       <c r="A239" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-283</t>
+          <t>WEB-SCREEN-230</t>
         </is>
       </c>
       <c r="B239" s="28" t="inlineStr">
         <is>
-          <t>Tenders · mobile</t>
+          <t>Vacancies · desktop</t>
         </is>
       </c>
       <c r="C239" s="28" t="inlineStr">
         <is>
-          <t>Typography</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D239" s="28" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E239" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Built 22px · design 20px  →  Live: “active tenders” — size 20 → 22.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by vacancy name or keyword” · absent from the build  →  Live: The design frame carries “search by vacancy name or keyword” (16px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F239" s="28" t="inlineStr">
         <is>
-          <t>Set the built value to the design's.</t>
-        </is>
-      </c>
-      <c r="G239" s="28" t="n"/>
-      <c r="H239" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/tenders/</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G239" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12427</t>
+        </is>
+      </c>
+      <c r="H239" s="28" t="n"/>
       <c r="I239" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -46363,17 +46363,17 @@
     <row r="240">
       <c r="A240" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-055</t>
+          <t>WEB-SCREEN-225</t>
         </is>
       </c>
       <c r="B240" s="28" t="inlineStr">
         <is>
-          <t>Updates · mobile</t>
+          <t>Vacancies · desktop</t>
         </is>
       </c>
       <c r="C240" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D240" s="28" t="inlineStr">
@@ -46383,20 +46383,20 @@
       </c>
       <c r="E240" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “NOS” is 147×20px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 147×20 it is also below the WCAG 2.5.8 AA floor of 24×24. Measured on 2 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “engagement of supervisor/consultant (con” · absent from the build  →  Live: The design frame carries “engagement of supervisor/consultant (contract)” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F240" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
-        </is>
-      </c>
-      <c r="G240" s="28" t="n"/>
-      <c r="H240" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/updates/</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G240" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12427</t>
+        </is>
+      </c>
+      <c r="H240" s="28" t="n"/>
       <c r="I240" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -46418,7 +46418,7 @@
     <row r="241">
       <c r="A241" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-230</t>
+          <t>WEB-SCREEN-227</t>
         </is>
       </c>
       <c r="B241" s="28" t="inlineStr">
@@ -46438,7 +46438,7 @@
       </c>
       <c r="E241" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by vacancy name or keyword” · absent from the build  →  Live: The design frame carries “search by vacancy name or keyword” (16px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “new delhi · contract · apply by 30 nov 2” · absent from the build  →  Live: The design frame carries “new delhi · contract · apply by 30 nov 2025” (12px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F241" s="28" t="inlineStr">
@@ -46473,7 +46473,7 @@
     <row r="242">
       <c r="A242" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-225</t>
+          <t>WEB-SCREEN-233</t>
         </is>
       </c>
       <c r="B242" s="28" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="E242" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “engagement of supervisor/consultant (con” · absent from the build  →  Live: The design frame carries “engagement of supervisor/consultant (contract)” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “supervisory and consultant roles for pro” · absent from the build  →  Live: The design frame carries “supervisory and consultant roles for project implementation and monitoring” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F242" s="28" t="inlineStr">
@@ -46528,7 +46528,7 @@
     <row r="243">
       <c r="A243" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-227</t>
+          <t>WEB-SCREEN-234</t>
         </is>
       </c>
       <c r="B243" s="28" t="inlineStr">
@@ -46548,7 +46548,7 @@
       </c>
       <c r="E243" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “new delhi · contract · apply by 30 nov 2” · absent from the build  →  Live: The design frame carries “new delhi · contract · apply by 30 nov 2025” (12px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “temporary / short-term consultants” · absent from the build  →  Live: The design frame carries “temporary / short-term consultants” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F243" s="28" t="inlineStr">
@@ -46583,7 +46583,7 @@
     <row r="244">
       <c r="A244" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-233</t>
+          <t>WEB-SCREEN-226</t>
         </is>
       </c>
       <c r="B244" s="28" t="inlineStr">
@@ -46603,7 +46603,7 @@
       </c>
       <c r="E244" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “supervisory and consultant roles for pro” · absent from the build  →  Live: The design frame carries “supervisory and consultant roles for project implementation and monitoring” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “multiple locations · contract · ongoing” · absent from the build  →  Live: The design frame carries “multiple locations · contract · ongoing” (12px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F244" s="28" t="inlineStr">
@@ -46638,12 +46638,12 @@
     <row r="245">
       <c r="A245" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-234</t>
+          <t>WEB-SCREEN-229</t>
         </is>
       </c>
       <c r="B245" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · desktop</t>
+          <t>Vacancies · mobile</t>
         </is>
       </c>
       <c r="C245" s="28" t="inlineStr">
@@ -46658,7 +46658,7 @@
       </c>
       <c r="E245" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “temporary / short-term consultants” · absent from the build  →  Live: The design frame carries “temporary / short-term consultants” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by scheme name or keyword” · absent from the build  →  Live: The design frame carries “search by scheme name or keyword” (14px). Nothing with that text renders on the live page. Measured on 2 pages.</t>
         </is>
       </c>
       <c r="F245" s="28" t="inlineStr">
@@ -46668,7 +46668,7 @@
       </c>
       <c r="G245" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12427</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105929</t>
         </is>
       </c>
       <c r="H245" s="28" t="n"/>
@@ -46693,12 +46693,12 @@
     <row r="246">
       <c r="A246" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-226</t>
+          <t>WEB-SCREEN-224</t>
         </is>
       </c>
       <c r="B246" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · desktop</t>
+          <t>Vacancies · mobile</t>
         </is>
       </c>
       <c r="C246" s="28" t="inlineStr">
@@ -46713,7 +46713,7 @@
       </c>
       <c r="E246" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “multiple locations · contract · ongoing” · absent from the build  →  Live: The design frame carries “multiple locations · contract · ongoing” (12px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “contact &amp; support” · absent from the build  →  Live: The design frame carries “contact &amp; support” (20px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F246" s="28" t="inlineStr">
@@ -46723,7 +46723,7 @@
       </c>
       <c r="G246" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-12427</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105929</t>
         </is>
       </c>
       <c r="H246" s="28" t="n"/>
@@ -46748,7 +46748,7 @@
     <row r="247">
       <c r="A247" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-229</t>
+          <t>WEB-SCREEN-228</t>
         </is>
       </c>
       <c r="B247" s="28" t="inlineStr">
@@ -46768,7 +46768,7 @@
       </c>
       <c r="E247" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “search by scheme name or keyword” · absent from the build  →  Live: The design frame carries “search by scheme name or keyword” (14px). Nothing with that text renders on the live page. Measured on 2 pages.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “nodal ministry” · absent from the build  →  Live: The design frame carries “nodal ministry” (14px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F247" s="28" t="inlineStr">
@@ -46803,7 +46803,7 @@
     <row r="248">
       <c r="A248" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-224</t>
+          <t>WEB-SCREEN-232</t>
         </is>
       </c>
       <c r="B248" s="28" t="inlineStr">
@@ -46823,7 +46823,7 @@
       </c>
       <c r="E248" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “contact &amp; support” · absent from the build  →  Live: The design frame carries “contact &amp; support” (20px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “shreshta@dosje.gov.in” · absent from the build  →  Live: The design frame carries “shreshta@dosje.gov.in” (12px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F248" s="28" t="inlineStr">
@@ -46858,7 +46858,7 @@
     <row r="249">
       <c r="A249" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-228</t>
+          <t>WEB-SCREEN-223</t>
         </is>
       </c>
       <c r="B249" s="28" t="inlineStr">
@@ -46878,7 +46878,7 @@
       </c>
       <c r="E249" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “nodal ministry” · absent from the build  →  Live: The design frame carries “nodal ministry” (14px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “5th floor, lok nayak bhawan, khan market” · absent from the build  →  Live: The design frame carries “5th floor, lok nayak bhawan, khan market, new delhi - 110003” (12px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F249" s="28" t="inlineStr">
@@ -46913,17 +46913,17 @@
     <row r="250">
       <c r="A250" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-232</t>
+          <t>WEB-SCREEN-024</t>
         </is>
       </c>
       <c r="B250" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · mobile</t>
+          <t>Visitor Analytics · desktop</t>
         </is>
       </c>
       <c r="C250" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Color &amp; Token</t>
         </is>
       </c>
       <c r="D250" s="28" t="inlineStr">
@@ -46933,20 +46933,20 @@
       </c>
       <c r="E250" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “shreshta@dosje.gov.in” · absent from the build  →  Live: The design frame carries “shreshta@dosje.gov.in” (12px). Nothing with that text renders on the live page.</t>
+          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Previous” (a.page-link) renders #938BB6 on #FFFFFF at 16px/400 — #938BB6 on #FFFFFF as painted on the capture: 3.18:1 against the 4.5:1 minimum. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F250" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G250" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105929</t>
-        </is>
-      </c>
-      <c r="H250" s="28" t="n"/>
+          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
+        </is>
+      </c>
+      <c r="G250" s="28" t="n"/>
+      <c r="H250" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/visitor-analytics/</t>
+        </is>
+      </c>
       <c r="I250" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -46968,12 +46968,12 @@
     <row r="251">
       <c r="A251" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-223</t>
+          <t>WEB-SCREEN-240</t>
         </is>
       </c>
       <c r="B251" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · mobile</t>
+          <t>Whos Who · desktop</t>
         </is>
       </c>
       <c r="C251" s="28" t="inlineStr">
@@ -46988,7 +46988,7 @@
       </c>
       <c r="E251" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “5th floor, lok nayak bhawan, khan market” · absent from the build  →  Live: The design frame carries “5th floor, lok nayak bhawan, khan market, new delhi - 110003” (12px). Nothing with that text renders on the live page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “discover the commissions, corporations, ” · absent from the build  →  Live: The design frame carries “discover the commissions, corporations, institutes and foundations that work col” (16px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F251" s="28" t="inlineStr">
@@ -46998,7 +46998,7 @@
       </c>
       <c r="G251" s="28" t="inlineStr">
         <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=4571-105929</t>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-8801</t>
         </is>
       </c>
       <c r="H251" s="28" t="n"/>
@@ -47023,17 +47023,17 @@
     <row r="252">
       <c r="A252" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-024</t>
+          <t>WEB-SCREEN-245</t>
         </is>
       </c>
       <c r="B252" s="28" t="inlineStr">
         <is>
-          <t>Visitor Analytics · desktop</t>
+          <t>Whos Who · desktop</t>
         </is>
       </c>
       <c r="C252" s="28" t="inlineStr">
         <is>
-          <t>Color &amp; Token</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D252" s="28" t="inlineStr">
@@ -47043,20 +47043,20 @@
       </c>
       <c r="E252" s="28" t="inlineStr">
         <is>
-          <t>Figma: WCAG 2.2 AA (1.4.3), carried into GIGW 3.0: text needs 4.5:1 against its background, or 3:1 at 24px+ / 18.66px+ bold.  →  Live: Text “Previous” (a.page-link) renders #938BB6 on #FFFFFF at 16px/400 — measured on the capture's pixels: #B2ACCB on #FFFFFF is 2.17:1 against the 4.5:1 minimum. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “mosje officials” · absent from the build  →  Live: The design frame carries “mosje officials” (28px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F252" s="28" t="inlineStr">
         <is>
-          <t>Darken the text or lighten its ground until the pair measures at least the required ratio, then re-check every place the pair is used.</t>
-        </is>
-      </c>
-      <c r="G252" s="28" t="n"/>
-      <c r="H252" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/visitor-analytics/</t>
-        </is>
-      </c>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+        </is>
+      </c>
+      <c r="G252" s="28" t="inlineStr">
+        <is>
+          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-8801</t>
+        </is>
+      </c>
+      <c r="H252" s="28" t="n"/>
       <c r="I252" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -47078,7 +47078,7 @@
     <row r="253">
       <c r="A253" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-240</t>
+          <t>WEB-SCREEN-243</t>
         </is>
       </c>
       <c r="B253" s="28" t="inlineStr">
@@ -47098,7 +47098,7 @@
       </c>
       <c r="E253" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “discover the commissions, corporations, ” · absent from the build  →  Live: The design frame carries “discover the commissions, corporations, institutes and foundations that work col” (16px). Nothing with that text renders on the live page. Measured on 2 pages. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “min-sje@nic.in” · absent from the build  →  Live: The design frame carries “min-sje@nic.in” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F253" s="28" t="inlineStr">
@@ -47133,7 +47133,7 @@
     <row r="254">
       <c r="A254" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-245</t>
+          <t>WEB-SCREEN-236</t>
         </is>
       </c>
       <c r="B254" s="28" t="inlineStr">
@@ -47153,7 +47153,7 @@
       </c>
       <c r="E254" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “mosje officials” · absent from the build  →  Live: The design frame carries “mosje officials” (28px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “201 c-wing, shastri bhawan, new delhi” · absent from the build  →  Live: The design frame carries “201 c-wing, shastri bhawan, new delhi” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F254" s="28" t="inlineStr">
@@ -47188,7 +47188,7 @@
     <row r="255">
       <c r="A255" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-243</t>
+          <t>WEB-SCREEN-244</t>
         </is>
       </c>
       <c r="B255" s="28" t="inlineStr">
@@ -47208,7 +47208,7 @@
       </c>
       <c r="E255" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “min-sje@nic.in” · absent from the build  →  Live: The design frame carries “min-sje@nic.in” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “mosathawale@gmail.com” · absent from the build  →  Live: The design frame carries “mosathawale@gmail.com” (14px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F255" s="28" t="inlineStr">
@@ -47243,7 +47243,7 @@
     <row r="256">
       <c r="A256" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-236</t>
+          <t>WEB-SCREEN-250</t>
         </is>
       </c>
       <c r="B256" s="28" t="inlineStr">
@@ -47263,7 +47263,7 @@
       </c>
       <c r="E256" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “201 c-wing, shastri bhawan, new delhi” · absent from the build  →  Live: The design frame carries “201 c-wing, shastri bhawan, new delhi” (14px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “shri b l verma” · absent from the build  →  Live: The design frame carries “shri b l verma” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
         </is>
       </c>
       <c r="F256" s="28" t="inlineStr">
@@ -47298,17 +47298,17 @@
     <row r="257">
       <c r="A257" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-244</t>
+          <t>WEB-SCREEN-057</t>
         </is>
       </c>
       <c r="B257" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop</t>
+          <t>Whos Who · mobile</t>
         </is>
       </c>
       <c r="C257" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D257" s="28" t="inlineStr">
@@ -47318,20 +47318,20 @@
       </c>
       <c r="E257" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “mosathawale@gmail.com” · absent from the build  →  Live: The design frame carries “mosathawale@gmail.com” (14px). Nothing with that text renders on the live page.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Dr. Virendra Kumar” is 130×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 130×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F257" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G257" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-8801</t>
-        </is>
-      </c>
-      <c r="H257" s="28" t="n"/>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+        </is>
+      </c>
+      <c r="G257" s="28" t="n"/>
+      <c r="H257" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/whos-who/</t>
+        </is>
+      </c>
       <c r="I257" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -47353,17 +47353,17 @@
     <row r="258">
       <c r="A258" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-250</t>
+          <t>WEB-SCREEN-058</t>
         </is>
       </c>
       <c r="B258" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop</t>
+          <t>Whos Who · mobile</t>
         </is>
       </c>
       <c r="C258" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>Layout &amp; Spacing</t>
         </is>
       </c>
       <c r="D258" s="28" t="inlineStr">
@@ -47373,20 +47373,20 @@
       </c>
       <c r="E258" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “shri b l verma” · absent from the build  →  Live: The design frame carries “shri b l verma” (16px). Nothing with that text renders on the live page. Also measured on the 375px capture of the same page.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Shri Kishor Makwana” is 144×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 144×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F258" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
-        </is>
-      </c>
-      <c r="G258" s="28" t="inlineStr">
-        <is>
-          <t>https://www.figma.com/design/Ds5qx61QsI0ZkYSrLKxo0A/MoSJE--Handoff-?node-id=3453-8801</t>
-        </is>
-      </c>
-      <c r="H258" s="28" t="n"/>
+          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+        </is>
+      </c>
+      <c r="G258" s="28" t="n"/>
+      <c r="H258" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/whos-who/</t>
+        </is>
+      </c>
       <c r="I258" s="28" t="inlineStr">
         <is>
           <t>Open</t>
@@ -47408,7 +47408,7 @@
     <row r="259">
       <c r="A259" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-057</t>
+          <t>WEB-SCREEN-288</t>
         </is>
       </c>
       <c r="B259" s="28" t="inlineStr">
@@ -47428,7 +47428,7 @@
       </c>
       <c r="E259" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Dr. Virendra Kumar” is 130×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 130×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Shri Kaishab Bihari” is 129×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 129×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F259" s="28" t="inlineStr">
@@ -47463,7 +47463,7 @@
     <row r="260">
       <c r="A260" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-058</t>
+          <t>WEB-SCREEN-289</t>
         </is>
       </c>
       <c r="B260" s="28" t="inlineStr">
@@ -47483,7 +47483,7 @@
       </c>
       <c r="E260" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Shri Kishor Makwana” is 144×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 144×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Sadhvi Niranjan Jyoti” is 142×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 142×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
         </is>
       </c>
       <c r="F260" s="28" t="inlineStr">
@@ -47518,7 +47518,7 @@
     <row r="261">
       <c r="A261" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-288</t>
+          <t>WEB-SCREEN-235</t>
         </is>
       </c>
       <c r="B261" s="28" t="inlineStr">
@@ -47528,7 +47528,7 @@
       </c>
       <c r="C261" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D261" s="28" t="inlineStr">
@@ -47538,12 +47538,12 @@
       </c>
       <c r="E261" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Shri Kaishab Bihari” is 129×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 129×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “101c-wing, shastri bhawan, new delhi” · absent from the build  →  Live: The design frame carries “101c-wing, shastri bhawan, new delhi” (14px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F261" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
       <c r="G261" s="28" t="n"/>
@@ -47573,7 +47573,7 @@
     <row r="262">
       <c r="A262" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-289</t>
+          <t>WEB-SCREEN-249</t>
         </is>
       </c>
       <c r="B262" s="28" t="inlineStr">
@@ -47583,7 +47583,7 @@
       </c>
       <c r="C262" s="28" t="inlineStr">
         <is>
-          <t>Layout &amp; Spacing</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D262" s="28" t="inlineStr">
@@ -47593,12 +47593,12 @@
       </c>
       <c r="E262" s="28" t="inlineStr">
         <is>
-          <t>Figma: UX4G 3.0 §6: interactive targets are at least 44×44px with 8px between them. WCAG 2.5.8 AA sets an absolute floor of 24×24.  →  Live: “Sadhvi Niranjan Jyoti” is 142×19px. UX4G 3.0 §6 sets 44×44px as the minimum interactive size; at 142×19 it is also below the WCAG 2.5.8 AA floor of 24×24.</t>
+          <t>Figma: The approved Figma handoff frame for this screen. Design: “room no. 623, a-wing, shastri bhawan” · absent from the build  →  Live: The design frame carries “room no. 623, a-wing, shastri bhawan” (14px). Nothing with that text renders on the live page.</t>
         </is>
       </c>
       <c r="F262" s="28" t="inlineStr">
         <is>
-          <t>Grow the control, or add transparent padding around it, until it measures 44×44px with 8px clear of its neighbours.</t>
+          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
         </is>
       </c>
       <c r="G262" s="28" t="n"/>
@@ -47628,115 +47628,464 @@
     <row r="263">
       <c r="A263" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-235</t>
+          <t>WEB-GLOBAL-008</t>
         </is>
       </c>
       <c r="B263" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C263" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D263" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E263" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “101c-wing, shastri bhawan, new delhi” · absent from the build  →  Live: The design frame carries “101c-wing, shastri bhawan, new delhi” (14px). Nothing with that text renders on the live page.</t>
+          <t>Global · No visible focus indicator — Open the accessibility option — Open the accessibility option</t>
         </is>
       </c>
       <c r="F263" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+          <t>No fix required — this finding was withdrawn.</t>
         </is>
       </c>
       <c r="G263" s="28" t="n"/>
-      <c r="H263" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/whos-who/</t>
-        </is>
-      </c>
+      <c r="H263" s="28" t="n"/>
       <c r="I263" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="J263" s="28" t="n"/>
       <c r="K263" s="28" t="n"/>
       <c r="L263" s="28" t="inlineStr">
         <is>
-          <t>env: live</t>
+          <t>WITHDRAWN: Re-measured on pixels: the control is invisible until focused and then shows a visible ring. The first version compared styles, not what a keyboard user sees.</t>
         </is>
       </c>
       <c r="M263" s="28" t="inlineStr">
         <is>
-          <t>Screen</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-249</t>
+          <t>WEB-GLOBAL-078</t>
         </is>
       </c>
       <c r="B264" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C264" s="28" t="inlineStr">
         <is>
-          <t>Content &amp; Iconography</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D264" s="28" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E264" s="28" t="inlineStr">
         <is>
-          <t>Figma: The approved Figma handoff frame for this screen. Design: “room no. 623, a-wing, shastri bhawan” · absent from the build  →  Live: The design frame carries “room no. 623, a-wing, shastri bhawan” (14px). Nothing with that text renders on the live page.</t>
+          <t>Global · Non-text control below 3:1 — Language Translator — Language Translator</t>
         </is>
       </c>
       <c r="F264" s="28" t="inlineStr">
         <is>
-          <t>Add the content the design carries, or confirm with the design team that it was dropped deliberately.</t>
+          <t>No fix required — this finding was withdrawn.</t>
         </is>
       </c>
       <c r="G264" s="28" t="n"/>
-      <c r="H264" s="28" t="inlineStr">
-        <is>
-          <t>https://www.dosje.gov.in/whos-who/</t>
-        </is>
-      </c>
+      <c r="H264" s="28" t="n"/>
       <c r="I264" s="28" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Withdrawn</t>
         </is>
       </c>
       <c r="J264" s="28" t="n"/>
       <c r="K264" s="28" t="n"/>
       <c r="L264" s="28" t="inlineStr">
         <is>
-          <t>env: live</t>
+          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
         </is>
       </c>
       <c r="M264" s="28" t="inlineStr">
         <is>
-          <t>Screen</t>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="27" t="inlineStr">
+        <is>
+          <t>WEB-GLOBAL-080</t>
+        </is>
+      </c>
+      <c r="B265" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C265" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D265" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E265" s="28" t="inlineStr">
+        <is>
+          <t>Global · Non-text control below 3:1 — Go to slide 1 — Go to slide 1</t>
+        </is>
+      </c>
+      <c r="F265" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G265" s="28" t="n"/>
+      <c r="H265" s="28" t="n"/>
+      <c r="I265" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J265" s="28" t="n"/>
+      <c r="K265" s="28" t="n"/>
+      <c r="L265" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
+        </is>
+      </c>
+      <c r="M265" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-158</t>
+        </is>
+      </c>
+      <c r="B266" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C266" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D266" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E266" s="28" t="inlineStr">
+        <is>
+          <t>Home · desktop — new funding alert!</t>
+        </is>
+      </c>
+      <c r="F266" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G266" s="28" t="n"/>
+      <c r="H266" s="28" t="n"/>
+      <c r="I266" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J266" s="28" t="n"/>
+      <c r="K266" s="28" t="n"/>
+      <c r="L266" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
+        </is>
+      </c>
+      <c r="M266" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-033</t>
+        </is>
+      </c>
+      <c r="B267" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C267" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D267" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E267" s="28" t="inlineStr">
+        <is>
+          <t>Home · mobile — Go to slide 1</t>
+        </is>
+      </c>
+      <c r="F267" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G267" s="28" t="n"/>
+      <c r="H267" s="28" t="n"/>
+      <c r="I267" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J267" s="28" t="n"/>
+      <c r="K267" s="28" t="n"/>
+      <c r="L267" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
+        </is>
+      </c>
+      <c r="M267" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-036</t>
+        </is>
+      </c>
+      <c r="B268" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C268" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D268" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E268" s="28" t="inlineStr">
+        <is>
+          <t>Home · mobile — Go to slide 2</t>
+        </is>
+      </c>
+      <c r="F268" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G268" s="28" t="n"/>
+      <c r="H268" s="28" t="n"/>
+      <c r="I268" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J268" s="28" t="n"/>
+      <c r="K268" s="28" t="n"/>
+      <c r="L268" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
+        </is>
+      </c>
+      <c r="M268" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-041</t>
+        </is>
+      </c>
+      <c r="B269" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C269" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D269" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E269" s="28" t="inlineStr">
+        <is>
+          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Home</t>
+        </is>
+      </c>
+      <c r="F269" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G269" s="28" t="n"/>
+      <c r="H269" s="28" t="n"/>
+      <c r="I269" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J269" s="28" t="n"/>
+      <c r="K269" s="28" t="n"/>
+      <c r="L269" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
+        </is>
+      </c>
+      <c r="M269" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-042</t>
+        </is>
+      </c>
+      <c r="B270" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C270" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D270" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E270" s="28" t="inlineStr">
+        <is>
+          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Department</t>
+        </is>
+      </c>
+      <c r="F270" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G270" s="28" t="n"/>
+      <c r="H270" s="28" t="n"/>
+      <c r="I270" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J270" s="28" t="n"/>
+      <c r="K270" s="28" t="n"/>
+      <c r="L270" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
+        </is>
+      </c>
+      <c r="M270" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-040</t>
+        </is>
+      </c>
+      <c r="B271" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C271" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D271" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E271" s="28" t="inlineStr">
+        <is>
+          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Associated Organisations</t>
+        </is>
+      </c>
+      <c r="F271" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G271" s="28" t="n"/>
+      <c r="H271" s="28" t="n"/>
+      <c r="I271" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J271" s="28" t="n"/>
+      <c r="K271" s="28" t="n"/>
+      <c r="L271" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
+        </is>
+      </c>
+      <c r="M271" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M264"/>
+  <autoFilter ref="A1:M271"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/qc/MoSJE-Portal-QC-Tracker.xlsx
+++ b/docs/qc/MoSJE-Portal-QC-Tracker.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Coverage – SMILE Beggary'!$A$1:$H$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'NMBA'!$A$1:$M$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Coverage – NMBA'!$A$1:$H$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MoSJE Website'!$A$1:$M$342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MoSJE Website'!$A$1:$M$347</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'NHAPOA'!$A$1:$M$152</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Coverage – NHAPOA'!$A$1:$H$81</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TG'!$A$1:$M$34</definedName>
@@ -33182,7 +33182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M342"/>
+  <dimension ref="A1:M347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -41474,262 +41474,282 @@
     <row r="149">
       <c r="A149" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-008</t>
+          <t>WEB-SCREEN-428</t>
         </is>
       </c>
       <c r="B149" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Official  Shri Shailendra Kumar · desktop · content accuracy</t>
         </is>
       </c>
       <c r="C149" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D149" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E149" s="28" t="inlineStr">
         <is>
-          <t>Global · No visible focus indicator — Open the accessibility option — Open the accessibility option</t>
+          <t>Figma: GIGW 3.0: page content is accurate, specific to the page, and in the Department's own register.  →  Live: [Confirmed error] Observed on 21 Sep 2026. When an officer changes, the record is edited in place, so the web address keeps the predecessor's name: this page for Shri Parveen Kumar Thind (DAIC Member Secretary) is /official/shri-shailendra-kumar/. The same holds for the DAF Member Secretary (/official/shri-v-appa-rao-3/), the DAF Director (/official/shri-sudhanshu-kumar-pandey-2/), the NCSK Chairperson (/official/vacant-cp/) and the NCSK Vice-Chairperson (/official/shri-hardeep-singh-gill-2/). One officer is also held as several records: Shri Parveen Kumar Thind has four (four photographs, three titles, three addresses), and Dr. Virendra Kumar and both Ministers of State have several each. A shared or bookmarked link names the wrong person, and search engines index the old names.</t>
         </is>
       </c>
       <c r="F149" s="28" t="inlineStr">
         <is>
-          <t>No fix required — this finding was withdrawn.</t>
+          <t>Create a new record for a new officer instead of editing the predecessor's, and redirect the old address; keep one record per person and attach each post to it.</t>
         </is>
       </c>
       <c r="G149" s="28" t="n"/>
-      <c r="H149" s="28" t="n"/>
+      <c r="H149" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/official/shri-shailendra-kumar/</t>
+        </is>
+      </c>
       <c r="I149" s="28" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J149" s="28" t="n"/>
       <c r="K149" s="28" t="n"/>
       <c r="L149" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Re-measured on pixels: the control is invisible until focused and then shows a visible ring. The first version compared styles, not what a keyboard user sees.</t>
+          <t>env: live</t>
         </is>
       </c>
       <c r="M149" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Screen</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-078</t>
+          <t>WEB-SCREEN-430</t>
         </is>
       </c>
       <c r="B150" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Whos Who · desktop · content accuracy</t>
         </is>
       </c>
       <c r="C150" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D150" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E150" s="28" t="inlineStr">
         <is>
-          <t>Global · Non-text control below 3:1 — Language Translator — Language Translator</t>
+          <t>Figma: GIGW 3.0: page content is accurate, specific to the page, and in the Department's own register.  →  Live: [To confirm with the Department] Not provable as errors from public sources; each needs the Department's decision. (1) Shri Ramdas Athawale's card lists mosathawale@gmail.com beside mos3-msje@gov.in. Parliament's member record (sansad.in, Rajya Sabha) gives ramdas@sansad.nic.in; the two telephone numbers on the card match that record. (2) The NCBC team omits its Secretary, Mr. Sudhansh Pant, I.A.S. (NCBC contact page: Room 104, 011-26183190, secy-ncbc@nic.in), while the NCSK team lists its Secretary. (3) The NISD team shows only the three Ministers and no officer of NISD.</t>
         </is>
       </c>
       <c r="F150" s="28" t="inlineStr">
         <is>
-          <t>No fix required — this finding was withdrawn.</t>
+          <t>Decide whether a personal address belongs on an official page, whether every team lists its Secretary, and who represents NISD on this page; record each decision so the page stays consistent.</t>
         </is>
       </c>
       <c r="G150" s="28" t="n"/>
-      <c r="H150" s="28" t="n"/>
+      <c r="H150" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/whos-who/</t>
+        </is>
+      </c>
       <c r="I150" s="28" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J150" s="28" t="n"/>
       <c r="K150" s="28" t="n"/>
       <c r="L150" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
+          <t>env: live</t>
         </is>
       </c>
       <c r="M150" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Screen</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-007</t>
+          <t>WEB-SCREEN-427</t>
         </is>
       </c>
       <c r="B151" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Whos Who · desktop · content accuracy</t>
         </is>
       </c>
       <c r="C151" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D151" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E151" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Single Access Mechanism for All Verticals o… — Single Access Mechanism for All Verticals o…</t>
+          <t>Figma: GIGW 3.0: page content is accurate, specific to the page, and in the Department's own register.  →  Live: [Confirmed error] Checked against NCSC's own directory (ncsc.nic.in/who-is-who) on 21 Sep 2026. Both Members are shown with the Chairperson's telephone, 011-24620435, on the card and again in the address line; NCSC lists Shri Love Kush Kumar on 011-24623266 and Shri Vaddepalli Ramchander on 011-24624801. Shri Vaddepalli Ramchander's email is also the Chairperson's (chairman-ncsc@nic.in); NCSC lists vaddepalli.ncsc@ncsc.gov.in. The posts read “Member's office (LKK)” and “Member's office (VDR)” — the section headings of NCSC's directory, carried into the post field; NCSC gives the post as Member. A citizen who rings either Member reaches the Chairperson's office.</t>
         </is>
       </c>
       <c r="F151" s="28" t="inlineStr">
         <is>
-          <t>No fix required — this finding was withdrawn.</t>
+          <t>Correct the two officer records: Shri Love Kush Kumar — 011-24623266; Shri Vaddepalli Ramchander — 011-24624801 and vaddepalli.ncsc@ncsc.gov.in; post “Member” for both; remove “Phone: 011-24620435” from their address lines. Leave unchanged, checked correct: the Chairperson's number and email, Shri Love Kush Kumar's email, and Dr. Partha Biswas's details.</t>
         </is>
       </c>
       <c r="G151" s="28" t="n"/>
-      <c r="H151" s="28" t="n"/>
+      <c r="H151" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/whos-who/</t>
+        </is>
+      </c>
       <c r="I151" s="28" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J151" s="28" t="n"/>
       <c r="K151" s="28" t="n"/>
       <c r="L151" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-088, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>env: live</t>
         </is>
       </c>
       <c r="M151" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Screen</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-079</t>
+          <t>WEB-SCREEN-426</t>
         </is>
       </c>
       <c r="B152" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Whos Who · desktop · content accuracy</t>
         </is>
       </c>
       <c r="C152" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D152" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="E152" s="28" t="inlineStr">
         <is>
-          <t>Global · Non-text control below 3:1 — Previous slide — Previous slide</t>
+          <t>Figma: GIGW 3.0: page content is accurate, specific to the page, and in the Department's own register.  →  Live: [Confirmed error] Checked against NCBC's own website (ncbc.nic.in — Present Commission and Contact pages) on 21 Sep 2026. The Member is shown as “Shri Kiran Umesh Mahalle”; NCBC names her Mrs. Kiran Umesh Mahalle (“Ms.” in its contact table). The photograph is correct; the title is not. Her card shows no contact details although NCBC publishes them: intercom 103, Room 113, 1st Floor, 011-26185478, member-office@ncbc.nic.in. The Chairperson's card shows only her email; NCBC also publishes intercom 101, Room 7, and 011-26183152, 011-26182388.</t>
         </is>
       </c>
       <c r="F152" s="28" t="inlineStr">
         <is>
-          <t>No fix required — this finding was withdrawn.</t>
+          <t>Change the Member's title to “Mrs.”, as NCBC's Present Commission page gives it, and add her contact details; add the Chairperson's telephone numbers. Keep the photograph — it is correct.</t>
         </is>
       </c>
       <c r="G152" s="28" t="n"/>
-      <c r="H152" s="28" t="n"/>
+      <c r="H152" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/whos-who/</t>
+        </is>
+      </c>
       <c r="I152" s="28" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J152" s="28" t="n"/>
       <c r="K152" s="28" t="n"/>
       <c r="L152" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-355, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>env: live</t>
         </is>
       </c>
       <c r="M152" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Screen</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-080</t>
+          <t>WEB-SCREEN-429</t>
         </is>
       </c>
       <c r="B153" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Whos Who · desktop · content accuracy</t>
         </is>
       </c>
       <c r="C153" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Content &amp; Iconography</t>
         </is>
       </c>
       <c r="D153" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Minor</t>
         </is>
       </c>
       <c r="E153" s="28" t="inlineStr">
         <is>
-          <t>Global · Non-text control below 3:1 — Go to slide 1 — Go to slide 1</t>
+          <t>Figma: GIGW 3.0: page content is accurate, specific to the page, and in the Department's own register.  →  Live: [Confirmed error] Observed on the live page, 21 Sep 2026. (1) Sh. Suresh Kumar, Chief Manager (Admin), NSKFDC, has a grey placeholder silhouette, not a photograph. (2) “Shashtri Bhawan” and “Shashtri Bhavan” — the building is Shastri Bhawan. (3) Spacing: “Executive Vice-President , BJRNF”, “Director , BJRNF”, “Vice-Chairperson(Rank of…”, “Joint Secretary(BC)”. (4) The honorific is written both “Sh.” and “Shri”. (5) DAIC gives the Minister's post as “Chairman Union Minister of Social Justice and Empowerment O/o Minister SJE”. (6) Five email addresses are printed plainly and the rest as [at]/[dot]; jsbcd-msje appears both ways. (7) Telephone formats differ: “01145854410”; “23072192, 23072193” without the 011 code. (8) The designation filter's 86 options include office sections (“CASH SECTION”, “HINDI SECTION”), organisation names, a commission of inquiry and near-duplicates (“BJRNF Member” / “BJRNF/ Member”, three spellings of Minister of State); the organisation filter lists portals and schemes (E-Anudaan, E-UTTHAAN, NMBA, NOS, Smile Beggary, Transgender) as organisations. (9) The standfirst describes “initiatives”, not the officers the page lists.</t>
         </is>
       </c>
       <c r="F153" s="28" t="inlineStr">
         <is>
-          <t>No fix required — this finding was withdrawn.</t>
+          <t>Upload the officer's photograph; correct the spelling and spacing in the officer records; use one honorific form; give the Minister's DAIC post in words; publish every email address the same way; write telephone numbers with the STD code; limit the designation filter to posts and the organisation filter to organisations; replace the standfirst with a description of who the page lists.</t>
         </is>
       </c>
       <c r="G153" s="28" t="n"/>
-      <c r="H153" s="28" t="n"/>
+      <c r="H153" s="28" t="inlineStr">
+        <is>
+          <t>https://www.dosje.gov.in/whos-who/</t>
+        </is>
+      </c>
       <c r="I153" s="28" t="inlineStr">
         <is>
-          <t>Withdrawn</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="J153" s="28" t="n"/>
       <c r="K153" s="28" t="n"/>
       <c r="L153" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
+          <t>env: live</t>
         </is>
       </c>
       <c r="M153" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Screen</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-019</t>
+          <t>WEB-GLOBAL-008</t>
         </is>
       </c>
       <c r="B154" s="28" t="inlineStr">
@@ -41749,7 +41769,7 @@
       </c>
       <c r="E154" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — About Ministry — About Ministry</t>
+          <t>Global · No visible focus indicator — Open the accessibility option — Open the accessibility option</t>
         </is>
       </c>
       <c r="F154" s="28" t="inlineStr">
@@ -41768,7 +41788,7 @@
       <c r="K154" s="28" t="n"/>
       <c r="L154" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-091, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Re-measured on pixels: the control is invisible until focused and then shows a visible ring. The first version compared styles, not what a keyboard user sees.</t>
         </is>
       </c>
       <c r="M154" s="28" t="inlineStr">
@@ -41780,7 +41800,7 @@
     <row r="155">
       <c r="A155" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-026</t>
+          <t>WEB-GLOBAL-078</t>
         </is>
       </c>
       <c r="B155" s="28" t="inlineStr">
@@ -41800,7 +41820,7 @@
       </c>
       <c r="E155" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Open Department — Open Department</t>
+          <t>Global · Non-text control below 3:1 — Language Translator — Language Translator</t>
         </is>
       </c>
       <c r="F155" s="28" t="inlineStr">
@@ -41819,7 +41839,7 @@
       <c r="K155" s="28" t="n"/>
       <c r="L155" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
         </is>
       </c>
       <c r="M155" s="28" t="inlineStr">
@@ -41831,7 +41851,7 @@
     <row r="156">
       <c r="A156" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-032</t>
+          <t>WEB-GLOBAL-007</t>
         </is>
       </c>
       <c r="B156" s="28" t="inlineStr">
@@ -41851,7 +41871,7 @@
       </c>
       <c r="E156" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Home — Home</t>
+          <t>Global · Text contrast below AA — Single Access Mechanism for All Verticals o… — Single Access Mechanism for All Verticals o…</t>
         </is>
       </c>
       <c r="F156" s="28" t="inlineStr">
@@ -41870,7 +41890,7 @@
       <c r="K156" s="28" t="n"/>
       <c r="L156" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-088, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M156" s="28" t="inlineStr">
@@ -41882,7 +41902,7 @@
     <row r="157">
       <c r="A157" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-033</t>
+          <t>WEB-GLOBAL-079</t>
         </is>
       </c>
       <c r="B157" s="28" t="inlineStr">
@@ -41902,7 +41922,7 @@
       </c>
       <c r="E157" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Department — Department</t>
+          <t>Global · Non-text control below 3:1 — Previous slide — Previous slide</t>
         </is>
       </c>
       <c r="F157" s="28" t="inlineStr">
@@ -41921,7 +41941,7 @@
       <c r="K157" s="28" t="n"/>
       <c r="L157" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-355, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M157" s="28" t="inlineStr">
@@ -41933,7 +41953,7 @@
     <row r="158">
       <c r="A158" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-031</t>
+          <t>WEB-GLOBAL-080</t>
         </is>
       </c>
       <c r="B158" s="28" t="inlineStr">
@@ -41953,7 +41973,7 @@
       </c>
       <c r="E158" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Associated Organisations — Associated Organisations</t>
+          <t>Global · Non-text control below 3:1 — Go to slide 1 — Go to slide 1</t>
         </is>
       </c>
       <c r="F158" s="28" t="inlineStr">
@@ -41972,7 +41992,7 @@
       <c r="K158" s="28" t="n"/>
       <c r="L158" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
         </is>
       </c>
       <c r="M158" s="28" t="inlineStr">
@@ -41984,7 +42004,7 @@
     <row r="159">
       <c r="A159" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-017</t>
+          <t>WEB-GLOBAL-019</t>
         </is>
       </c>
       <c r="B159" s="28" t="inlineStr">
@@ -42004,7 +42024,7 @@
       </c>
       <c r="E159" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Get in Touch — Get in Touch</t>
+          <t>Global · Text contrast below AA — About Ministry — About Ministry</t>
         </is>
       </c>
       <c r="F159" s="28" t="inlineStr">
@@ -42023,7 +42043,7 @@
       <c r="K159" s="28" t="n"/>
       <c r="L159" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-090, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-091, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M159" s="28" t="inlineStr">
@@ -42035,7 +42055,7 @@
     <row r="160">
       <c r="A160" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-016</t>
+          <t>WEB-GLOBAL-026</t>
         </is>
       </c>
       <c r="B160" s="28" t="inlineStr">
@@ -42055,7 +42075,7 @@
       </c>
       <c r="E160" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Get in Touch — Get in Touch</t>
+          <t>Global · Touch target below the minimum — Open Department — Open Department</t>
         </is>
       </c>
       <c r="F160" s="28" t="inlineStr">
@@ -42074,7 +42094,7 @@
       <c r="K160" s="28" t="n"/>
       <c r="L160" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-090, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M160" s="28" t="inlineStr">
@@ -42086,7 +42106,7 @@
     <row r="161">
       <c r="A161" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-027</t>
+          <t>WEB-GLOBAL-032</t>
         </is>
       </c>
       <c r="B161" s="28" t="inlineStr">
@@ -42106,7 +42126,7 @@
       </c>
       <c r="E161" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — About Ministry — About Ministry</t>
+          <t>Global · Touch target below the minimum — Home — Home</t>
         </is>
       </c>
       <c r="F161" s="28" t="inlineStr">
@@ -42125,7 +42145,7 @@
       <c r="K161" s="28" t="n"/>
       <c r="L161" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-110, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M161" s="28" t="inlineStr">
@@ -42137,7 +42157,7 @@
     <row r="162">
       <c r="A162" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-030</t>
+          <t>WEB-GLOBAL-033</t>
         </is>
       </c>
       <c r="B162" s="28" t="inlineStr">
@@ -42157,7 +42177,7 @@
       </c>
       <c r="E162" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Vision &amp; Mission — Vision &amp; Mission</t>
+          <t>Global · Touch target below the minimum — Department — Department</t>
         </is>
       </c>
       <c r="F162" s="28" t="inlineStr">
@@ -42188,7 +42208,7 @@
     <row r="163">
       <c r="A163" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-029</t>
+          <t>WEB-GLOBAL-031</t>
         </is>
       </c>
       <c r="B163" s="28" t="inlineStr">
@@ -42208,7 +42228,7 @@
       </c>
       <c r="E163" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Organisational Chart — Organisational Chart</t>
+          <t>Global · Touch target below the minimum — Associated Organisations — Associated Organisations</t>
         </is>
       </c>
       <c r="F163" s="28" t="inlineStr">
@@ -42239,7 +42259,7 @@
     <row r="164">
       <c r="A164" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-028</t>
+          <t>WEB-GLOBAL-017</t>
         </is>
       </c>
       <c r="B164" s="28" t="inlineStr">
@@ -42259,7 +42279,7 @@
       </c>
       <c r="E164" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Ministers &amp; Officials — Ministers &amp; Officials</t>
+          <t>Global · Text contrast below AA — Get in Touch — Get in Touch</t>
         </is>
       </c>
       <c r="F164" s="28" t="inlineStr">
@@ -42278,7 +42298,7 @@
       <c r="K164" s="28" t="n"/>
       <c r="L164" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-090, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M164" s="28" t="inlineStr">
@@ -42290,7 +42310,7 @@
     <row r="165">
       <c r="A165" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-021</t>
+          <t>WEB-GLOBAL-016</t>
         </is>
       </c>
       <c r="B165" s="28" t="inlineStr">
@@ -42310,7 +42330,7 @@
       </c>
       <c r="E165" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — View All Documents from MoSJE — View All Documents from MoSJE</t>
+          <t>Global · Text contrast below AA — Get in Touch — Get in Touch</t>
         </is>
       </c>
       <c r="F165" s="28" t="inlineStr">
@@ -42329,7 +42349,7 @@
       <c r="K165" s="28" t="n"/>
       <c r="L165" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-092, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-090, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M165" s="28" t="inlineStr">
@@ -42341,7 +42361,7 @@
     <row r="166">
       <c r="A166" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-020</t>
+          <t>WEB-GLOBAL-027</t>
         </is>
       </c>
       <c r="B166" s="28" t="inlineStr">
@@ -42361,7 +42381,7 @@
       </c>
       <c r="E166" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Chairperson's office — Chairperson's office</t>
+          <t>Global · Touch target below the minimum — About Ministry — About Ministry</t>
         </is>
       </c>
       <c r="F166" s="28" t="inlineStr">
@@ -42380,7 +42400,7 @@
       <c r="K166" s="28" t="n"/>
       <c r="L166" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-092, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-110, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M166" s="28" t="inlineStr">
@@ -42392,7 +42412,7 @@
     <row r="167">
       <c r="A167" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-047</t>
+          <t>WEB-GLOBAL-030</t>
         </is>
       </c>
       <c r="B167" s="28" t="inlineStr">
@@ -42412,7 +42432,7 @@
       </c>
       <c r="E167" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — last updated on — last updated on</t>
+          <t>Global · Touch target below the minimum — Vision &amp; Mission — Vision &amp; Mission</t>
         </is>
       </c>
       <c r="F167" s="28" t="inlineStr">
@@ -42431,7 +42451,7 @@
       <c r="K167" s="28" t="n"/>
       <c r="L167" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M167" s="28" t="inlineStr">
@@ -42443,7 +42463,7 @@
     <row r="168">
       <c r="A168" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-038</t>
+          <t>WEB-GLOBAL-029</t>
         </is>
       </c>
       <c r="B168" s="28" t="inlineStr">
@@ -42463,7 +42483,7 @@
       </c>
       <c r="E168" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — MoSJE — MoSJE</t>
+          <t>Global · Touch target below the minimum — Organisational Chart — Organisational Chart</t>
         </is>
       </c>
       <c r="F168" s="28" t="inlineStr">
@@ -42494,7 +42514,7 @@
     <row r="169">
       <c r="A169" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-059</t>
+          <t>WEB-GLOBAL-028</t>
         </is>
       </c>
       <c r="B169" s="28" t="inlineStr">
@@ -42514,7 +42534,7 @@
       </c>
       <c r="E169" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — dr. virendra kumar — dr. virendra kumar</t>
+          <t>Global · Touch target below the minimum — Ministers &amp; Officials — Ministers &amp; Officials</t>
         </is>
       </c>
       <c r="F169" s="28" t="inlineStr">
@@ -42533,7 +42553,7 @@
       <c r="K169" s="28" t="n"/>
       <c r="L169" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M169" s="28" t="inlineStr">
@@ -42545,7 +42565,7 @@
     <row r="170">
       <c r="A170" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-022</t>
+          <t>WEB-GLOBAL-021</t>
         </is>
       </c>
       <c r="B170" s="28" t="inlineStr">
@@ -42565,7 +42585,7 @@
       </c>
       <c r="E170" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Dr. Ambedkar International Centre (DAIC) — Dr. Ambedkar International Centre (DAIC)</t>
+          <t>Global · Text contrast below AA — View All Documents from MoSJE — View All Documents from MoSJE</t>
         </is>
       </c>
       <c r="F170" s="28" t="inlineStr">
@@ -42596,7 +42616,7 @@
     <row r="171">
       <c r="A171" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-057</t>
+          <t>WEB-GLOBAL-020</t>
         </is>
       </c>
       <c r="B171" s="28" t="inlineStr">
@@ -42616,7 +42636,7 @@
       </c>
       <c r="E171" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — dr. virendra kumar — dr. virendra kumar</t>
+          <t>Global · Text contrast below AA — Chairperson's office — Chairperson's office</t>
         </is>
       </c>
       <c r="F171" s="28" t="inlineStr">
@@ -42635,7 +42655,7 @@
       <c r="K171" s="28" t="n"/>
       <c r="L171" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-092, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M171" s="28" t="inlineStr">
@@ -42647,7 +42667,7 @@
     <row r="172">
       <c r="A172" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-035</t>
+          <t>WEB-GLOBAL-047</t>
         </is>
       </c>
       <c r="B172" s="28" t="inlineStr">
@@ -42667,7 +42687,7 @@
       </c>
       <c r="E172" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — Transgender — Transgender</t>
+          <t>Global · Content in the design is not in the build — last updated on — last updated on</t>
         </is>
       </c>
       <c r="F172" s="28" t="inlineStr">
@@ -42686,7 +42706,7 @@
       <c r="K172" s="28" t="n"/>
       <c r="L172" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M172" s="28" t="inlineStr">
@@ -42698,7 +42718,7 @@
     <row r="173">
       <c r="A173" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-041</t>
+          <t>WEB-GLOBAL-038</t>
         </is>
       </c>
       <c r="B173" s="28" t="inlineStr">
@@ -42718,7 +42738,7 @@
       </c>
       <c r="E173" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NBCFDC — NBCFDC</t>
+          <t>Global · Touch target below the minimum — MoSJE — MoSJE</t>
         </is>
       </c>
       <c r="F173" s="28" t="inlineStr">
@@ -42749,7 +42769,7 @@
     <row r="174">
       <c r="A174" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-034</t>
+          <t>WEB-GLOBAL-059</t>
         </is>
       </c>
       <c r="B174" s="28" t="inlineStr">
@@ -42769,7 +42789,7 @@
       </c>
       <c r="E174" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NCBC — NCBC</t>
+          <t>Global · Built value differs from the design — dr. virendra kumar — dr. virendra kumar</t>
         </is>
       </c>
       <c r="F174" s="28" t="inlineStr">
@@ -42788,7 +42808,7 @@
       <c r="K174" s="28" t="n"/>
       <c r="L174" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
         </is>
       </c>
       <c r="M174" s="28" t="inlineStr">
@@ -42800,7 +42820,7 @@
     <row r="175">
       <c r="A175" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-036</t>
+          <t>WEB-GLOBAL-022</t>
         </is>
       </c>
       <c r="B175" s="28" t="inlineStr">
@@ -42820,7 +42840,7 @@
       </c>
       <c r="E175" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — DAF — DAF</t>
+          <t>Global · Text contrast below AA — Dr. Ambedkar International Centre (DAIC) — Dr. Ambedkar International Centre (DAIC)</t>
         </is>
       </c>
       <c r="F175" s="28" t="inlineStr">
@@ -42839,7 +42859,7 @@
       <c r="K175" s="28" t="n"/>
       <c r="L175" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-092, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M175" s="28" t="inlineStr">
@@ -42851,7 +42871,7 @@
     <row r="176">
       <c r="A176" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-037</t>
+          <t>WEB-GLOBAL-057</t>
         </is>
       </c>
       <c r="B176" s="28" t="inlineStr">
@@ -42871,7 +42891,7 @@
       </c>
       <c r="E176" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — DAIC — DAIC</t>
+          <t>Global · Built value differs from the design — dr. virendra kumar — dr. virendra kumar</t>
         </is>
       </c>
       <c r="F176" s="28" t="inlineStr">
@@ -42890,7 +42910,7 @@
       <c r="K176" s="28" t="n"/>
       <c r="L176" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
         </is>
       </c>
       <c r="M176" s="28" t="inlineStr">
@@ -42902,7 +42922,7 @@
     <row r="177">
       <c r="A177" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-039</t>
+          <t>WEB-GLOBAL-035</t>
         </is>
       </c>
       <c r="B177" s="28" t="inlineStr">
@@ -42922,7 +42942,7 @@
       </c>
       <c r="E177" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NSFDC — NSFDC</t>
+          <t>Global · Touch target below the minimum — Transgender — Transgender</t>
         </is>
       </c>
       <c r="F177" s="28" t="inlineStr">
@@ -42953,7 +42973,7 @@
     <row r="178">
       <c r="A178" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-040</t>
+          <t>WEB-GLOBAL-041</t>
         </is>
       </c>
       <c r="B178" s="28" t="inlineStr">
@@ -42973,7 +42993,7 @@
       </c>
       <c r="E178" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NMBA — NMBA</t>
+          <t>Global · Touch target below the minimum — NBCFDC — NBCFDC</t>
         </is>
       </c>
       <c r="F178" s="28" t="inlineStr">
@@ -43004,7 +43024,7 @@
     <row r="179">
       <c r="A179" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-043</t>
+          <t>WEB-GLOBAL-034</t>
         </is>
       </c>
       <c r="B179" s="28" t="inlineStr">
@@ -43024,7 +43044,7 @@
       </c>
       <c r="E179" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — SCW — SCW</t>
+          <t>Global · Touch target below the minimum — NCBC — NCBC</t>
         </is>
       </c>
       <c r="F179" s="28" t="inlineStr">
@@ -43055,7 +43075,7 @@
     <row r="180">
       <c r="A180" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-042</t>
+          <t>WEB-GLOBAL-036</t>
         </is>
       </c>
       <c r="B180" s="28" t="inlineStr">
@@ -43075,7 +43095,7 @@
       </c>
       <c r="E180" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — NSKFDC — NSKFDC</t>
+          <t>Global · Touch target below the minimum — DAF — DAF</t>
         </is>
       </c>
       <c r="F180" s="28" t="inlineStr">
@@ -43106,7 +43126,7 @@
     <row r="181">
       <c r="A181" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-023</t>
+          <t>WEB-GLOBAL-037</t>
         </is>
       </c>
       <c r="B181" s="28" t="inlineStr">
@@ -43126,7 +43146,7 @@
       </c>
       <c r="E181" s="28" t="inlineStr">
         <is>
-          <t>Global · Text contrast below AA — Dr. Swati S. Mishra — Dr. Swati S. Mishra</t>
+          <t>Global · Touch target below the minimum — DAIC — DAIC</t>
         </is>
       </c>
       <c r="F181" s="28" t="inlineStr">
@@ -43145,7 +43165,7 @@
       <c r="K181" s="28" t="n"/>
       <c r="L181" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-092, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M181" s="28" t="inlineStr">
@@ -43157,7 +43177,7 @@
     <row r="182">
       <c r="A182" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-044</t>
+          <t>WEB-GLOBAL-039</t>
         </is>
       </c>
       <c r="B182" s="28" t="inlineStr">
@@ -43177,7 +43197,7 @@
       </c>
       <c r="E182" s="28" t="inlineStr">
         <is>
-          <t>Global · Touch target below the minimum — DAIC — DAIC</t>
+          <t>Global · Touch target below the minimum — NSFDC — NSFDC</t>
         </is>
       </c>
       <c r="F182" s="28" t="inlineStr">
@@ -43208,7 +43228,7 @@
     <row r="183">
       <c r="A183" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-061</t>
+          <t>WEB-GLOBAL-040</t>
         </is>
       </c>
       <c r="B183" s="28" t="inlineStr">
@@ -43228,7 +43248,7 @@
       </c>
       <c r="E183" s="28" t="inlineStr">
         <is>
-          <t>Global · Built value differs from the design — mos3-msje[at]gov[dot]in — mos3-msje[at]gov[dot]in</t>
+          <t>Global · Touch target below the minimum — NMBA — NMBA</t>
         </is>
       </c>
       <c r="F183" s="28" t="inlineStr">
@@ -43247,7 +43267,7 @@
       <c r="K183" s="28" t="n"/>
       <c r="L183" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M183" s="28" t="inlineStr">
@@ -43259,7 +43279,7 @@
     <row r="184">
       <c r="A184" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-053</t>
+          <t>WEB-GLOBAL-043</t>
         </is>
       </c>
       <c r="B184" s="28" t="inlineStr">
@@ -43279,7 +43299,7 @@
       </c>
       <c r="E184" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — target group — target group</t>
+          <t>Global · Touch target below the minimum — SCW — SCW</t>
         </is>
       </c>
       <c r="F184" s="28" t="inlineStr">
@@ -43298,7 +43318,7 @@
       <c r="K184" s="28" t="n"/>
       <c r="L184" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M184" s="28" t="inlineStr">
@@ -43310,7 +43330,7 @@
     <row r="185">
       <c r="A185" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-050</t>
+          <t>WEB-GLOBAL-042</t>
         </is>
       </c>
       <c r="B185" s="28" t="inlineStr">
@@ -43330,7 +43350,7 @@
       </c>
       <c r="E185" s="28" t="inlineStr">
         <is>
-          <t>Global · Content in the design is not in the build — sort by recently added — sort by recently added</t>
+          <t>Global · Touch target below the minimum — NSKFDC — NSKFDC</t>
         </is>
       </c>
       <c r="F185" s="28" t="inlineStr">
@@ -43349,7 +43369,7 @@
       <c r="K185" s="28" t="n"/>
       <c r="L185" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M185" s="28" t="inlineStr">
@@ -43361,7 +43381,7 @@
     <row r="186">
       <c r="A186" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-066</t>
+          <t>WEB-GLOBAL-023</t>
         </is>
       </c>
       <c r="B186" s="28" t="inlineStr">
@@ -43381,7 +43401,7 @@
       </c>
       <c r="E186" s="28" t="inlineStr">
         <is>
-          <t>Global · Automated accessibility violation — heading-order — heading-order</t>
+          <t>Global · Text contrast below AA — Dr. Swati S. Mishra — Dr. Swati S. Mishra</t>
         </is>
       </c>
       <c r="F186" s="28" t="inlineStr">
@@ -43400,7 +43420,7 @@
       <c r="K186" s="28" t="n"/>
       <c r="L186" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-092, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M186" s="28" t="inlineStr">
@@ -43412,7 +43432,7 @@
     <row r="187">
       <c r="A187" s="27" t="inlineStr">
         <is>
-          <t>WEB-GLOBAL-084</t>
+          <t>WEB-GLOBAL-044</t>
         </is>
       </c>
       <c r="B187" s="28" t="inlineStr">
@@ -43432,7 +43452,7 @@
       </c>
       <c r="E187" s="28" t="inlineStr">
         <is>
-          <t>Global · The four audience pages share one description — Audience page standfirst — Audience page standfirst</t>
+          <t>Global · Touch target below the minimum — DAIC — DAIC</t>
         </is>
       </c>
       <c r="F187" s="28" t="inlineStr">
@@ -43451,7 +43471,7 @@
       <c r="K187" s="28" t="n"/>
       <c r="L187" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-356, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M187" s="28" t="inlineStr">
@@ -43463,7 +43483,7 @@
     <row r="188">
       <c r="A188" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-061</t>
+          <t>WEB-GLOBAL-061</t>
         </is>
       </c>
       <c r="B188" s="28" t="inlineStr">
@@ -43483,7 +43503,7 @@
       </c>
       <c r="E188" s="28" t="inlineStr">
         <is>
-          <t>About Us · desktop — discover the initiatives that drive national efforts to adva</t>
+          <t>Global · Built value differs from the design — mos3-msje[at]gov[dot]in — mos3-msje[at]gov[dot]in</t>
         </is>
       </c>
       <c r="F188" s="28" t="inlineStr">
@@ -43502,7 +43522,7 @@
       <c r="K188" s="28" t="n"/>
       <c r="L188" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
         </is>
       </c>
       <c r="M188" s="28" t="inlineStr">
@@ -43514,7 +43534,7 @@
     <row r="189">
       <c r="A189" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-072</t>
+          <t>WEB-GLOBAL-053</t>
         </is>
       </c>
       <c r="B189" s="28" t="inlineStr">
@@ -43534,7 +43554,7 @@
       </c>
       <c r="E189" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">About Us · desktop — the department of social justice &amp; empowerment is entrusted </t>
+          <t>Global · Content in the design is not in the build — target group — target group</t>
         </is>
       </c>
       <c r="F189" s="28" t="inlineStr">
@@ -43565,7 +43585,7 @@
     <row r="190">
       <c r="A190" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-074</t>
+          <t>WEB-GLOBAL-050</t>
         </is>
       </c>
       <c r="B190" s="28" t="inlineStr">
@@ -43585,7 +43605,7 @@
       </c>
       <c r="E190" s="28" t="inlineStr">
         <is>
-          <t>About Us · desktop — the ministry has been implementing various programmes/scheme</t>
+          <t>Global · Content in the design is not in the build — sort by recently added — sort by recently added</t>
         </is>
       </c>
       <c r="F190" s="28" t="inlineStr">
@@ -43616,7 +43636,7 @@
     <row r="191">
       <c r="A191" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-063</t>
+          <t>WEB-GLOBAL-066</t>
         </is>
       </c>
       <c r="B191" s="28" t="inlineStr">
@@ -43636,7 +43656,7 @@
       </c>
       <c r="E191" s="28" t="inlineStr">
         <is>
-          <t>About Us · desktop — in the year 1985-86, the erstwhile ministry of welfare was b</t>
+          <t>Global · Automated accessibility violation — heading-order — heading-order</t>
         </is>
       </c>
       <c r="F191" s="28" t="inlineStr">
@@ -43655,7 +43675,7 @@
       <c r="K191" s="28" t="n"/>
       <c r="L191" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Not reproduced on the re-capture of 18 September 2026.</t>
         </is>
       </c>
       <c r="M191" s="28" t="inlineStr">
@@ -43667,7 +43687,7 @@
     <row r="192">
       <c r="A192" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-062</t>
+          <t>WEB-GLOBAL-084</t>
         </is>
       </c>
       <c r="B192" s="28" t="inlineStr">
@@ -43687,7 +43707,7 @@
       </c>
       <c r="E192" s="28" t="inlineStr">
         <is>
-          <t>About Us · desktop — in january, 2007, the minorities division along with wakf un</t>
+          <t>Global · The four audience pages share one description — Audience page standfirst — Audience page standfirst</t>
         </is>
       </c>
       <c r="F192" s="28" t="inlineStr">
@@ -43706,7 +43726,7 @@
       <c r="K192" s="28" t="n"/>
       <c r="L192" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-356, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M192" s="28" t="inlineStr">
@@ -43718,7 +43738,7 @@
     <row r="193">
       <c r="A193" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-065</t>
+          <t>WEB-SCREEN-061</t>
         </is>
       </c>
       <c r="B193" s="28" t="inlineStr">
@@ -43738,7 +43758,7 @@
       </c>
       <c r="E193" s="28" t="inlineStr">
         <is>
-          <t>About Us · mobile — mrs. caralyn khongwar deshmukh, as</t>
+          <t>About Us · desktop — discover the initiatives that drive national efforts to adva</t>
         </is>
       </c>
       <c r="F193" s="28" t="inlineStr">
@@ -43769,7 +43789,7 @@
     <row r="194">
       <c r="A194" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-064</t>
+          <t>WEB-SCREEN-072</t>
         </is>
       </c>
       <c r="B194" s="28" t="inlineStr">
@@ -43789,7 +43809,7 @@
       </c>
       <c r="E194" s="28" t="inlineStr">
         <is>
-          <t>About Us · mobile — matters related to the national scheduled castes finance and</t>
+          <t xml:space="preserve">About Us · desktop — the department of social justice &amp; empowerment is entrusted </t>
         </is>
       </c>
       <c r="F194" s="28" t="inlineStr">
@@ -43820,7 +43840,7 @@
     <row r="195">
       <c r="A195" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-070</t>
+          <t>WEB-SCREEN-074</t>
         </is>
       </c>
       <c r="B195" s="28" t="inlineStr">
@@ -43840,7 +43860,7 @@
       </c>
       <c r="E195" s="28" t="inlineStr">
         <is>
-          <t>About Us · mobile — shri biswaranjan sasmal, as</t>
+          <t>About Us · desktop — the ministry has been implementing various programmes/scheme</t>
         </is>
       </c>
       <c r="F195" s="28" t="inlineStr">
@@ -43871,7 +43891,7 @@
     <row r="196">
       <c r="A196" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-066</t>
+          <t>WEB-SCREEN-063</t>
         </is>
       </c>
       <c r="B196" s="28" t="inlineStr">
@@ -43891,7 +43911,7 @@
       </c>
       <c r="E196" s="28" t="inlineStr">
         <is>
-          <t>About Us · mobile — mrs. yogita swaroop, sr. ea</t>
+          <t>About Us · desktop — in the year 1985-86, the erstwhile ministry of welfare was b</t>
         </is>
       </c>
       <c r="F196" s="28" t="inlineStr">
@@ -43922,7 +43942,7 @@
     <row r="197">
       <c r="A197" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-067</t>
+          <t>WEB-SCREEN-062</t>
         </is>
       </c>
       <c r="B197" s="28" t="inlineStr">
@@ -43942,7 +43962,7 @@
       </c>
       <c r="E197" s="28" t="inlineStr">
         <is>
-          <t>About Us · mobile — ms. latha ganapathy, js</t>
+          <t>About Us · desktop — in january, 2007, the minorities division along with wakf un</t>
         </is>
       </c>
       <c r="F197" s="28" t="inlineStr">
@@ -43973,7 +43993,7 @@
     <row r="198">
       <c r="A198" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-025</t>
+          <t>WEB-SCREEN-065</t>
         </is>
       </c>
       <c r="B198" s="28" t="inlineStr">
@@ -43993,7 +44013,7 @@
       </c>
       <c r="E198" s="28" t="inlineStr">
         <is>
-          <t>Acts Rules · mobile — NHAA</t>
+          <t>About Us · mobile — mrs. caralyn khongwar deshmukh, as</t>
         </is>
       </c>
       <c r="F198" s="28" t="inlineStr">
@@ -44012,7 +44032,7 @@
       <c r="K198" s="28" t="n"/>
       <c r="L198" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M198" s="28" t="inlineStr">
@@ -44024,7 +44044,7 @@
     <row r="199">
       <c r="A199" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-079</t>
+          <t>WEB-SCREEN-064</t>
         </is>
       </c>
       <c r="B199" s="28" t="inlineStr">
@@ -44044,7 +44064,7 @@
       </c>
       <c r="E199" s="28" t="inlineStr">
         <is>
-          <t>Annual Reports · desktop — access official reports released by the commission and its a</t>
+          <t>About Us · mobile — matters related to the national scheduled castes finance and</t>
         </is>
       </c>
       <c r="F199" s="28" t="inlineStr">
@@ -44063,7 +44083,7 @@
       <c r="K199" s="28" t="n"/>
       <c r="L199" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-114, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M199" s="28" t="inlineStr">
@@ -44075,7 +44095,7 @@
     <row r="200">
       <c r="A200" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-080</t>
+          <t>WEB-SCREEN-070</t>
         </is>
       </c>
       <c r="B200" s="28" t="inlineStr">
@@ -44095,7 +44115,7 @@
       </c>
       <c r="E200" s="28" t="inlineStr">
         <is>
-          <t>Annual Reports · desktop — download all reports</t>
+          <t>About Us · mobile — shri biswaranjan sasmal, as</t>
         </is>
       </c>
       <c r="F200" s="28" t="inlineStr">
@@ -44126,7 +44146,7 @@
     <row r="201">
       <c r="A201" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-027</t>
+          <t>WEB-SCREEN-066</t>
         </is>
       </c>
       <c r="B201" s="28" t="inlineStr">
@@ -44146,7 +44166,7 @@
       </c>
       <c r="E201" s="28" t="inlineStr">
         <is>
-          <t>Annual Reports · mobile — NISD</t>
+          <t>About Us · mobile — mrs. yogita swaroop, sr. ea</t>
         </is>
       </c>
       <c r="F201" s="28" t="inlineStr">
@@ -44165,7 +44185,7 @@
       <c r="K201" s="28" t="n"/>
       <c r="L201" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M201" s="28" t="inlineStr">
@@ -44177,7 +44197,7 @@
     <row r="202">
       <c r="A202" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-026</t>
+          <t>WEB-SCREEN-067</t>
         </is>
       </c>
       <c r="B202" s="28" t="inlineStr">
@@ -44197,7 +44217,7 @@
       </c>
       <c r="E202" s="28" t="inlineStr">
         <is>
-          <t>Annual Reports · mobile — BJRNF</t>
+          <t>About Us · mobile — ms. latha ganapathy, js</t>
         </is>
       </c>
       <c r="F202" s="28" t="inlineStr">
@@ -44216,7 +44236,7 @@
       <c r="K202" s="28" t="n"/>
       <c r="L202" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M202" s="28" t="inlineStr">
@@ -44228,7 +44248,7 @@
     <row r="203">
       <c r="A203" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-028</t>
+          <t>WEB-SCREEN-025</t>
         </is>
       </c>
       <c r="B203" s="28" t="inlineStr">
@@ -44248,7 +44268,7 @@
       </c>
       <c r="E203" s="28" t="inlineStr">
         <is>
-          <t>Circulars Notifications · mobile — PMAJAY</t>
+          <t>Acts Rules · mobile — NHAA</t>
         </is>
       </c>
       <c r="F203" s="28" t="inlineStr">
@@ -44279,7 +44299,7 @@
     <row r="204">
       <c r="A204" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-029</t>
+          <t>WEB-SCREEN-079</t>
         </is>
       </c>
       <c r="B204" s="28" t="inlineStr">
@@ -44299,7 +44319,7 @@
       </c>
       <c r="E204" s="28" t="inlineStr">
         <is>
-          <t>Circulars Notifications · mobile — Smile Beggary</t>
+          <t>Annual Reports · desktop — access official reports released by the commission and its a</t>
         </is>
       </c>
       <c r="F204" s="28" t="inlineStr">
@@ -44318,7 +44338,7 @@
       <c r="K204" s="28" t="n"/>
       <c r="L204" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-114, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M204" s="28" t="inlineStr">
@@ -44330,7 +44350,7 @@
     <row r="205">
       <c r="A205" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-083</t>
+          <t>WEB-SCREEN-080</t>
         </is>
       </c>
       <c r="B205" s="28" t="inlineStr">
@@ -44350,7 +44370,7 @@
       </c>
       <c r="E205" s="28" t="inlineStr">
         <is>
-          <t>Contact Us · desktop — contact details</t>
+          <t>Annual Reports · desktop — download all reports</t>
         </is>
       </c>
       <c r="F205" s="28" t="inlineStr">
@@ -44369,7 +44389,7 @@
       <c r="K205" s="28" t="n"/>
       <c r="L205" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-363, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M205" s="28" t="inlineStr">
@@ -44381,7 +44401,7 @@
     <row r="206">
       <c r="A206" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-082</t>
+          <t>WEB-SCREEN-027</t>
         </is>
       </c>
       <c r="B206" s="28" t="inlineStr">
@@ -44401,7 +44421,7 @@
       </c>
       <c r="E206" s="28" t="inlineStr">
         <is>
-          <t>Contact Us · desktop — connect directly with the ministry, reach the concerned depa</t>
+          <t>Annual Reports · mobile — NISD</t>
         </is>
       </c>
       <c r="F206" s="28" t="inlineStr">
@@ -44420,7 +44440,7 @@
       <c r="K206" s="28" t="n"/>
       <c r="L206" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M206" s="28" t="inlineStr">
@@ -44432,7 +44452,7 @@
     <row r="207">
       <c r="A207" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-087</t>
+          <t>WEB-SCREEN-026</t>
         </is>
       </c>
       <c r="B207" s="28" t="inlineStr">
@@ -44452,7 +44472,7 @@
       </c>
       <c r="E207" s="28" t="inlineStr">
         <is>
-          <t>Contact Us · desktop — ministry of social justice and empowerment (mosje) contact d</t>
+          <t>Annual Reports · mobile — BJRNF</t>
         </is>
       </c>
       <c r="F207" s="28" t="inlineStr">
@@ -44471,7 +44491,7 @@
       <c r="K207" s="28" t="n"/>
       <c r="L207" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M207" s="28" t="inlineStr">
@@ -44483,7 +44503,7 @@
     <row r="208">
       <c r="A208" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-090</t>
+          <t>WEB-SCREEN-028</t>
         </is>
       </c>
       <c r="B208" s="28" t="inlineStr">
@@ -44503,7 +44523,7 @@
       </c>
       <c r="E208" s="28" t="inlineStr">
         <is>
-          <t>Contact Us · desktop — room no. 631, a-wing, shastri bhawan, new delhi - 110001</t>
+          <t>Circulars Notifications · mobile — PMAJAY</t>
         </is>
       </c>
       <c r="F208" s="28" t="inlineStr">
@@ -44522,7 +44542,7 @@
       <c r="K208" s="28" t="n"/>
       <c r="L208" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M208" s="28" t="inlineStr">
@@ -44534,7 +44554,7 @@
     <row r="209">
       <c r="A209" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-081</t>
+          <t>WEB-SCREEN-029</t>
         </is>
       </c>
       <c r="B209" s="28" t="inlineStr">
@@ -44554,7 +44574,7 @@
       </c>
       <c r="E209" s="28" t="inlineStr">
         <is>
-          <t>Contact Us · desktop — complaint[at]ncsc[dot]gov[dot]in</t>
+          <t>Circulars Notifications · mobile — Smile Beggary</t>
         </is>
       </c>
       <c r="F209" s="28" t="inlineStr">
@@ -44573,7 +44593,7 @@
       <c r="K209" s="28" t="n"/>
       <c r="L209" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M209" s="28" t="inlineStr">
@@ -44585,7 +44605,7 @@
     <row r="210">
       <c r="A210" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-088</t>
+          <t>WEB-SCREEN-083</t>
         </is>
       </c>
       <c r="B210" s="28" t="inlineStr">
@@ -44605,7 +44625,7 @@
       </c>
       <c r="E210" s="28" t="inlineStr">
         <is>
-          <t>Contact Us · desktop — national commission for safai karamchari (ncsk)</t>
+          <t>Contact Us · desktop — contact details</t>
         </is>
       </c>
       <c r="F210" s="28" t="inlineStr">
@@ -44624,7 +44644,7 @@
       <c r="K210" s="28" t="n"/>
       <c r="L210" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-363, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M210" s="28" t="inlineStr">
@@ -44636,7 +44656,7 @@
     <row r="211">
       <c r="A211" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-285</t>
+          <t>WEB-SCREEN-082</t>
         </is>
       </c>
       <c r="B211" s="28" t="inlineStr">
@@ -44656,7 +44676,7 @@
       </c>
       <c r="E211" s="28" t="inlineStr">
         <is>
-          <t>Cookies · desktop — Session Cookies always active</t>
+          <t>Contact Us · desktop — connect directly with the ministry, reach the concerned depa</t>
         </is>
       </c>
       <c r="F211" s="28" t="inlineStr">
@@ -44675,7 +44695,7 @@
       <c r="K211" s="28" t="n"/>
       <c r="L211" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M211" s="28" t="inlineStr">
@@ -44687,7 +44707,7 @@
     <row r="212">
       <c r="A212" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-018</t>
+          <t>WEB-SCREEN-087</t>
         </is>
       </c>
       <c r="B212" s="28" t="inlineStr">
@@ -44707,7 +44727,7 @@
       </c>
       <c r="E212" s="28" t="inlineStr">
         <is>
-          <t>Cookies · desktop — Ensures user session persistence, allowing …</t>
+          <t>Contact Us · desktop — ministry of social justice and empowerment (mosje) contact d</t>
         </is>
       </c>
       <c r="F212" s="28" t="inlineStr">
@@ -44726,7 +44746,7 @@
       <c r="K212" s="28" t="n"/>
       <c r="L212" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-093, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M212" s="28" t="inlineStr">
@@ -44738,7 +44758,7 @@
     <row r="213">
       <c r="A213" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-104</t>
+          <t>WEB-SCREEN-090</t>
         </is>
       </c>
       <c r="B213" s="28" t="inlineStr">
@@ -44758,7 +44778,7 @@
       </c>
       <c r="E213" s="28" t="inlineStr">
         <is>
-          <t>Cpio · desktop — the designated authority responsible for providing timely an</t>
+          <t>Contact Us · desktop — room no. 631, a-wing, shastri bhawan, new delhi - 110001</t>
         </is>
       </c>
       <c r="F213" s="28" t="inlineStr">
@@ -44777,7 +44797,7 @@
       <c r="K213" s="28" t="n"/>
       <c r="L213" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-365, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M213" s="28" t="inlineStr">
@@ -44789,7 +44809,7 @@
     <row r="214">
       <c r="A214" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-103</t>
+          <t>WEB-SCREEN-081</t>
         </is>
       </c>
       <c r="B214" s="28" t="inlineStr">
@@ -44809,7 +44829,7 @@
       </c>
       <c r="E214" s="28" t="inlineStr">
         <is>
-          <t>Cpio · desktop — sort by recently updated</t>
+          <t>Contact Us · desktop — complaint[at]ncsc[dot]gov[dot]in</t>
         </is>
       </c>
       <c r="F214" s="28" t="inlineStr">
@@ -44840,7 +44860,7 @@
     <row r="215">
       <c r="A215" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-091</t>
+          <t>WEB-SCREEN-088</t>
         </is>
       </c>
       <c r="B215" s="28" t="inlineStr">
@@ -44860,7 +44880,7 @@
       </c>
       <c r="E215" s="28" t="inlineStr">
         <is>
-          <t>Cpio · desktop — designantion</t>
+          <t>Contact Us · desktop — national commission for safai karamchari (ncsk)</t>
         </is>
       </c>
       <c r="F215" s="28" t="inlineStr">
@@ -44891,7 +44911,7 @@
     <row r="216">
       <c r="A216" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-099</t>
+          <t>WEB-SCREEN-285</t>
         </is>
       </c>
       <c r="B216" s="28" t="inlineStr">
@@ -44911,7 +44931,7 @@
       </c>
       <c r="E216" s="28" t="inlineStr">
         <is>
-          <t>Cpio · desktop — shri gulshan kumar pahadia, ad</t>
+          <t>Cookies · desktop — Session Cookies always active</t>
         </is>
       </c>
       <c r="F216" s="28" t="inlineStr">
@@ -44930,7 +44950,7 @@
       <c r="K216" s="28" t="n"/>
       <c r="L216" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Re-measured on pixels with the element's own CSS colour: the pair passes on screen. The first version read an anti-aliased edge pixel as the text colour.</t>
         </is>
       </c>
       <c r="M216" s="28" t="inlineStr">
@@ -44942,7 +44962,7 @@
     <row r="217">
       <c r="A217" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-097</t>
+          <t>WEB-SCREEN-018</t>
         </is>
       </c>
       <c r="B217" s="28" t="inlineStr">
@@ -44962,7 +44982,7 @@
       </c>
       <c r="E217" s="28" t="inlineStr">
         <is>
-          <t>Cpio · desktop — ms. sanmeet kaur, dig(p)</t>
+          <t>Cookies · desktop — Ensures user session persistence, allowing …</t>
         </is>
       </c>
       <c r="F217" s="28" t="inlineStr">
@@ -44981,7 +45001,7 @@
       <c r="K217" s="28" t="n"/>
       <c r="L217" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-093, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M217" s="28" t="inlineStr">
@@ -44993,7 +45013,7 @@
     <row r="218">
       <c r="A218" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-098</t>
+          <t>WEB-SCREEN-104</t>
         </is>
       </c>
       <c r="B218" s="28" t="inlineStr">
@@ -45013,7 +45033,7 @@
       </c>
       <c r="E218" s="28" t="inlineStr">
         <is>
-          <t>Cpio · desktop — sanmeet[dot]kaur[at]ips[dot]gov[dot]in</t>
+          <t>Cpio · desktop — the designated authority responsible for providing timely an</t>
         </is>
       </c>
       <c r="F218" s="28" t="inlineStr">
@@ -45032,7 +45052,7 @@
       <c r="K218" s="28" t="n"/>
       <c r="L218" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-365, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M218" s="28" t="inlineStr">
@@ -45044,7 +45064,7 @@
     <row r="219">
       <c r="A219" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-093</t>
+          <t>WEB-SCREEN-103</t>
         </is>
       </c>
       <c r="B219" s="28" t="inlineStr">
@@ -45064,7 +45084,7 @@
       </c>
       <c r="E219" s="28" t="inlineStr">
         <is>
-          <t>Cpio · mobile — gk[dot]pahadia[at]gov[dot]in</t>
+          <t>Cpio · desktop — sort by recently updated</t>
         </is>
       </c>
       <c r="F219" s="28" t="inlineStr">
@@ -45095,7 +45115,7 @@
     <row r="220">
       <c r="A220" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-019</t>
+          <t>WEB-SCREEN-091</t>
         </is>
       </c>
       <c r="B220" s="28" t="inlineStr">
@@ -45115,7 +45135,7 @@
       </c>
       <c r="E220" s="28" t="inlineStr">
         <is>
-          <t>Dashboard · desktop — Pre-Matric (SCs &amp; Others)</t>
+          <t>Cpio · desktop — designantion</t>
         </is>
       </c>
       <c r="F220" s="28" t="inlineStr">
@@ -45134,7 +45154,7 @@
       <c r="K220" s="28" t="n"/>
       <c r="L220" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-331, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M220" s="28" t="inlineStr">
@@ -45146,7 +45166,7 @@
     <row r="221">
       <c r="A221" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-117</t>
+          <t>WEB-SCREEN-099</t>
         </is>
       </c>
       <c r="B221" s="28" t="inlineStr">
@@ -45166,7 +45186,7 @@
       </c>
       <c r="E221" s="28" t="inlineStr">
         <is>
-          <t>Dashboard · desktop — total sc/st beneficiary count</t>
+          <t>Cpio · desktop — shri gulshan kumar pahadia, ad</t>
         </is>
       </c>
       <c r="F221" s="28" t="inlineStr">
@@ -45185,7 +45205,7 @@
       <c r="K221" s="28" t="n"/>
       <c r="L221" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-366, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M221" s="28" t="inlineStr">
@@ -45197,7 +45217,7 @@
     <row r="222">
       <c r="A222" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-109</t>
+          <t>WEB-SCREEN-097</t>
         </is>
       </c>
       <c r="B222" s="28" t="inlineStr">
@@ -45217,7 +45237,7 @@
       </c>
       <c r="E222" s="28" t="inlineStr">
         <is>
-          <t>Dashboard · desktop — sc/st coverage rate</t>
+          <t>Cpio · desktop — ms. sanmeet kaur, dig(p)</t>
         </is>
       </c>
       <c r="F222" s="28" t="inlineStr">
@@ -45248,7 +45268,7 @@
     <row r="223">
       <c r="A223" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-107</t>
+          <t>WEB-SCREEN-098</t>
         </is>
       </c>
       <c r="B223" s="28" t="inlineStr">
@@ -45268,7 +45288,7 @@
       </c>
       <c r="E223" s="28" t="inlineStr">
         <is>
-          <t>Dashboard · desktop — dapsc budget utilization rate</t>
+          <t>Cpio · desktop — sanmeet[dot]kaur[at]ips[dot]gov[dot]in</t>
         </is>
       </c>
       <c r="F223" s="28" t="inlineStr">
@@ -45299,7 +45319,7 @@
     <row r="224">
       <c r="A224" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-112</t>
+          <t>WEB-SCREEN-093</t>
         </is>
       </c>
       <c r="B224" s="28" t="inlineStr">
@@ -45319,7 +45339,7 @@
       </c>
       <c r="E224" s="28" t="inlineStr">
         <is>
-          <t>Dashboard · desktop — sc/st women beneficiary percentage</t>
+          <t>Cpio · mobile — gk[dot]pahadia[at]gov[dot]in</t>
         </is>
       </c>
       <c r="F224" s="28" t="inlineStr">
@@ -45338,7 +45358,7 @@
       <c r="K224" s="28" t="n"/>
       <c r="L224" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-366, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M224" s="28" t="inlineStr">
@@ -45350,7 +45370,7 @@
     <row r="225">
       <c r="A225" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-111</t>
+          <t>WEB-SCREEN-019</t>
         </is>
       </c>
       <c r="B225" s="28" t="inlineStr">
@@ -45370,7 +45390,7 @@
       </c>
       <c r="E225" s="28" t="inlineStr">
         <is>
-          <t>Dashboard · desktop — sc/st scholarship beneficiaries</t>
+          <t>Dashboard · desktop — Pre-Matric (SCs &amp; Others)</t>
         </is>
       </c>
       <c r="F225" s="28" t="inlineStr">
@@ -45389,7 +45409,7 @@
       <c r="K225" s="28" t="n"/>
       <c r="L225" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-331, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M225" s="28" t="inlineStr">
@@ -45401,7 +45421,7 @@
     <row r="226">
       <c r="A226" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-004</t>
+          <t>WEB-SCREEN-117</t>
         </is>
       </c>
       <c r="B226" s="28" t="inlineStr">
@@ -45421,7 +45441,7 @@
       </c>
       <c r="E226" s="28" t="inlineStr">
         <is>
-          <t>Dashboard · mobile — 29,015</t>
+          <t>Dashboard · desktop — total sc/st beneficiary count</t>
         </is>
       </c>
       <c r="F226" s="28" t="inlineStr">
@@ -45440,7 +45460,7 @@
       <c r="K226" s="28" t="n"/>
       <c r="L226" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-328, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-366, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M226" s="28" t="inlineStr">
@@ -45452,7 +45472,7 @@
     <row r="227">
       <c r="A227" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-122</t>
+          <t>WEB-SCREEN-109</t>
         </is>
       </c>
       <c r="B227" s="28" t="inlineStr">
@@ -45472,7 +45492,7 @@
       </c>
       <c r="E227" s="28" t="inlineStr">
         <is>
-          <t>Events · desktop — discover initiatives, workshops, and awareness programs that</t>
+          <t>Dashboard · desktop — sc/st coverage rate</t>
         </is>
       </c>
       <c r="F227" s="28" t="inlineStr">
@@ -45503,7 +45523,7 @@
     <row r="228">
       <c r="A228" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-132</t>
+          <t>WEB-SCREEN-107</t>
         </is>
       </c>
       <c r="B228" s="28" t="inlineStr">
@@ -45523,7 +45543,7 @@
       </c>
       <c r="E228" s="28" t="inlineStr">
         <is>
-          <t>Events · desktop — view all</t>
+          <t>Dashboard · desktop — dapsc budget utilization rate</t>
         </is>
       </c>
       <c r="F228" s="28" t="inlineStr">
@@ -45542,7 +45562,7 @@
       <c r="K228" s="28" t="n"/>
       <c r="L228" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-368, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M228" s="28" t="inlineStr">
@@ -45554,7 +45574,7 @@
     <row r="229">
       <c r="A229" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-124</t>
+          <t>WEB-SCREEN-112</t>
         </is>
       </c>
       <c r="B229" s="28" t="inlineStr">
@@ -45574,7 +45594,7 @@
       </c>
       <c r="E229" s="28" t="inlineStr">
         <is>
-          <t>Events · desktop — hard to reach population-smile (beggary)</t>
+          <t>Dashboard · desktop — sc/st women beneficiary percentage</t>
         </is>
       </c>
       <c r="F229" s="28" t="inlineStr">
@@ -45593,7 +45613,7 @@
       <c r="K229" s="28" t="n"/>
       <c r="L229" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-366, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M229" s="28" t="inlineStr">
@@ -45605,7 +45625,7 @@
     <row r="230">
       <c r="A230" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-126</t>
+          <t>WEB-SCREEN-111</t>
         </is>
       </c>
       <c r="B230" s="28" t="inlineStr">
@@ -45625,7 +45645,7 @@
       </c>
       <c r="E230" s="28" t="inlineStr">
         <is>
-          <t>Events · desktop — nov 10th, 2025 • 05:00 pm onwards</t>
+          <t>Dashboard · desktop — sc/st scholarship beneficiaries</t>
         </is>
       </c>
       <c r="F230" s="28" t="inlineStr">
@@ -45656,7 +45676,7 @@
     <row r="231">
       <c r="A231" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-123</t>
+          <t>WEB-SCREEN-004</t>
         </is>
       </c>
       <c r="B231" s="28" t="inlineStr">
@@ -45676,7 +45696,7 @@
       </c>
       <c r="E231" s="28" t="inlineStr">
         <is>
-          <t>Events · desktop — dr. ambedkar international centre</t>
+          <t>Dashboard · mobile — 29,015</t>
         </is>
       </c>
       <c r="F231" s="28" t="inlineStr">
@@ -45695,7 +45715,7 @@
       <c r="K231" s="28" t="n"/>
       <c r="L231" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-328, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M231" s="28" t="inlineStr">
@@ -45707,7 +45727,7 @@
     <row r="232">
       <c r="A232" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-120</t>
+          <t>WEB-SCREEN-122</t>
         </is>
       </c>
       <c r="B232" s="28" t="inlineStr">
@@ -45727,7 +45747,7 @@
       </c>
       <c r="E232" s="28" t="inlineStr">
         <is>
-          <t>Events · desktop — "chandalika" - musical dance drama</t>
+          <t>Events · desktop — discover initiatives, workshops, and awareness programs that</t>
         </is>
       </c>
       <c r="F232" s="28" t="inlineStr">
@@ -45758,7 +45778,7 @@
     <row r="233">
       <c r="A233" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-130</t>
+          <t>WEB-SCREEN-132</t>
         </is>
       </c>
       <c r="B233" s="28" t="inlineStr">
@@ -45778,7 +45798,7 @@
       </c>
       <c r="E233" s="28" t="inlineStr">
         <is>
-          <t>Events · mobile — painting exhibition and yamuna sustaibablity run</t>
+          <t>Events · desktop — view all</t>
         </is>
       </c>
       <c r="F233" s="28" t="inlineStr">
@@ -45797,7 +45817,7 @@
       <c r="K233" s="28" t="n"/>
       <c r="L233" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-368, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M233" s="28" t="inlineStr">
@@ -45809,7 +45829,7 @@
     <row r="234">
       <c r="A234" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-020</t>
+          <t>WEB-SCREEN-124</t>
         </is>
       </c>
       <c r="B234" s="28" t="inlineStr">
@@ -45829,7 +45849,7 @@
       </c>
       <c r="E234" s="28" t="inlineStr">
         <is>
-          <t>Events  Ek Ped Maa Ke Naam 6 · desktop — Declared</t>
+          <t>Events · desktop — hard to reach population-smile (beggary)</t>
         </is>
       </c>
       <c r="F234" s="28" t="inlineStr">
@@ -45848,7 +45868,7 @@
       <c r="K234" s="28" t="n"/>
       <c r="L234" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-332, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M234" s="28" t="inlineStr">
@@ -45860,7 +45880,7 @@
     <row r="235">
       <c r="A235" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-021</t>
+          <t>WEB-SCREEN-126</t>
         </is>
       </c>
       <c r="B235" s="28" t="inlineStr">
@@ -45880,7 +45900,7 @@
       </c>
       <c r="E235" s="28" t="inlineStr">
         <is>
-          <t>Events  Ek Ped Maa Ke Naam 7 · desktop — Declared</t>
+          <t>Events · desktop — nov 10th, 2025 • 05:00 pm onwards</t>
         </is>
       </c>
       <c r="F235" s="28" t="inlineStr">
@@ -45899,7 +45919,7 @@
       <c r="K235" s="28" t="n"/>
       <c r="L235" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-332, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M235" s="28" t="inlineStr">
@@ -45911,7 +45931,7 @@
     <row r="236">
       <c r="A236" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-134</t>
+          <t>WEB-SCREEN-123</t>
         </is>
       </c>
       <c r="B236" s="28" t="inlineStr">
@@ -45931,7 +45951,7 @@
       </c>
       <c r="E236" s="28" t="inlineStr">
         <is>
-          <t>For Researchers · desktop — discover all welfare initiatives, social justice schemes, an</t>
+          <t>Events · desktop — dr. ambedkar international centre</t>
         </is>
       </c>
       <c r="F236" s="28" t="inlineStr">
@@ -45962,7 +45982,7 @@
     <row r="237">
       <c r="A237" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-133</t>
+          <t>WEB-SCREEN-120</t>
         </is>
       </c>
       <c r="B237" s="28" t="inlineStr">
@@ -45982,7 +46002,7 @@
       </c>
       <c r="E237" s="28" t="inlineStr">
         <is>
-          <t>For Researchers · desktop — browse the key legislations, policy frameworks, and governme</t>
+          <t>Events · desktop — "chandalika" - musical dance drama</t>
         </is>
       </c>
       <c r="F237" s="28" t="inlineStr">
@@ -46013,7 +46033,7 @@
     <row r="238">
       <c r="A238" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-031</t>
+          <t>WEB-SCREEN-130</t>
         </is>
       </c>
       <c r="B238" s="28" t="inlineStr">
@@ -46033,7 +46053,7 @@
       </c>
       <c r="E238" s="28" t="inlineStr">
         <is>
-          <t>Forms Templates · mobile — PMAJAY</t>
+          <t>Events · mobile — painting exhibition and yamuna sustaibablity run</t>
         </is>
       </c>
       <c r="F238" s="28" t="inlineStr">
@@ -46052,7 +46072,7 @@
       <c r="K238" s="28" t="n"/>
       <c r="L238" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M238" s="28" t="inlineStr">
@@ -46064,7 +46084,7 @@
     <row r="239">
       <c r="A239" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-030</t>
+          <t>WEB-SCREEN-020</t>
         </is>
       </c>
       <c r="B239" s="28" t="inlineStr">
@@ -46084,7 +46104,7 @@
       </c>
       <c r="E239" s="28" t="inlineStr">
         <is>
-          <t>Forms Templates · mobile — NOS</t>
+          <t>Events  Ek Ped Maa Ke Naam 6 · desktop — Declared</t>
         </is>
       </c>
       <c r="F239" s="28" t="inlineStr">
@@ -46103,7 +46123,7 @@
       <c r="K239" s="28" t="n"/>
       <c r="L239" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-332, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M239" s="28" t="inlineStr">
@@ -46115,7 +46135,7 @@
     <row r="240">
       <c r="A240" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-280</t>
+          <t>WEB-SCREEN-021</t>
         </is>
       </c>
       <c r="B240" s="28" t="inlineStr">
@@ -46135,7 +46155,7 @@
       </c>
       <c r="E240" s="28" t="inlineStr">
         <is>
-          <t>Forms Templates · mobile — access official reports released by the commission and its a</t>
+          <t>Events  Ek Ped Maa Ke Naam 7 · desktop — Declared</t>
         </is>
       </c>
       <c r="F240" s="28" t="inlineStr">
@@ -46154,7 +46174,7 @@
       <c r="K240" s="28" t="n"/>
       <c r="L240" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-114, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-332, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M240" s="28" t="inlineStr">
@@ -46166,7 +46186,7 @@
     <row r="241">
       <c r="A241" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-139</t>
+          <t>WEB-SCREEN-134</t>
         </is>
       </c>
       <c r="B241" s="28" t="inlineStr">
@@ -46186,7 +46206,7 @@
       </c>
       <c r="E241" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gallery · desktop — explore photos, videos and news from the ministry of social </t>
+          <t>For Researchers · desktop — discover all welfare initiatives, social justice schemes, an</t>
         </is>
       </c>
       <c r="F241" s="28" t="inlineStr">
@@ -46217,7 +46237,7 @@
     <row r="242">
       <c r="A242" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-145</t>
+          <t>WEB-SCREEN-133</t>
         </is>
       </c>
       <c r="B242" s="28" t="inlineStr">
@@ -46237,7 +46257,7 @@
       </c>
       <c r="E242" s="28" t="inlineStr">
         <is>
-          <t>Gallery · desktop — search by keyword or event</t>
+          <t>For Researchers · desktop — browse the key legislations, policy frameworks, and governme</t>
         </is>
       </c>
       <c r="F242" s="28" t="inlineStr">
@@ -46256,7 +46276,7 @@
       <c r="K242" s="28" t="n"/>
       <c r="L242" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-371, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M242" s="28" t="inlineStr">
@@ -46268,7 +46288,7 @@
     <row r="243">
       <c r="A243" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-135</t>
+          <t>WEB-SCREEN-031</t>
         </is>
       </c>
       <c r="B243" s="28" t="inlineStr">
@@ -46288,7 +46308,7 @@
       </c>
       <c r="E243" s="28" t="inlineStr">
         <is>
-          <t>Gallery · desktop — ambedkar jayanti celebration 2025</t>
+          <t>Forms Templates · mobile — PMAJAY</t>
         </is>
       </c>
       <c r="F243" s="28" t="inlineStr">
@@ -46307,7 +46327,7 @@
       <c r="K243" s="28" t="n"/>
       <c r="L243" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M243" s="28" t="inlineStr">
@@ -46319,7 +46339,7 @@
     <row r="244">
       <c r="A244" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-140</t>
+          <t>WEB-SCREEN-030</t>
         </is>
       </c>
       <c r="B244" s="28" t="inlineStr">
@@ -46339,7 +46359,7 @@
       </c>
       <c r="E244" s="28" t="inlineStr">
         <is>
-          <t>Gallery · desktop — glimpses from the national celebration</t>
+          <t>Forms Templates · mobile — NOS</t>
         </is>
       </c>
       <c r="F244" s="28" t="inlineStr">
@@ -46358,7 +46378,7 @@
       <c r="K244" s="28" t="n"/>
       <c r="L244" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M244" s="28" t="inlineStr">
@@ -46370,7 +46390,7 @@
     <row r="245">
       <c r="A245" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-138</t>
+          <t>WEB-SCREEN-280</t>
         </is>
       </c>
       <c r="B245" s="28" t="inlineStr">
@@ -46390,7 +46410,7 @@
       </c>
       <c r="E245" s="28" t="inlineStr">
         <is>
-          <t>Gallery · desktop — elder care workshop</t>
+          <t>Forms Templates · mobile — access official reports released by the commission and its a</t>
         </is>
       </c>
       <c r="F245" s="28" t="inlineStr">
@@ -46409,7 +46429,7 @@
       <c r="K245" s="28" t="n"/>
       <c r="L245" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-114, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M245" s="28" t="inlineStr">
@@ -46421,7 +46441,7 @@
     <row r="246">
       <c r="A246" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-147</t>
+          <t>WEB-SCREEN-139</t>
         </is>
       </c>
       <c r="B246" s="28" t="inlineStr">
@@ -46441,7 +46461,7 @@
       </c>
       <c r="E246" s="28" t="inlineStr">
         <is>
-          <t>Gallery · desktop — training for caregivers and elder care professionals</t>
+          <t xml:space="preserve">Gallery · desktop — explore photos, videos and news from the ministry of social </t>
         </is>
       </c>
       <c r="F246" s="28" t="inlineStr">
@@ -46472,7 +46492,7 @@
     <row r="247">
       <c r="A247" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-032</t>
+          <t>WEB-SCREEN-145</t>
         </is>
       </c>
       <c r="B247" s="28" t="inlineStr">
@@ -46492,7 +46512,7 @@
       </c>
       <c r="E247" s="28" t="inlineStr">
         <is>
-          <t>Gallery · mobile — “Ek Ped Maa Ke Naam”</t>
+          <t>Gallery · desktop — search by keyword or event</t>
         </is>
       </c>
       <c r="F247" s="28" t="inlineStr">
@@ -46511,7 +46531,7 @@
       <c r="K247" s="28" t="n"/>
       <c r="L247" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-371, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M247" s="28" t="inlineStr">
@@ -46523,7 +46543,7 @@
     <row r="248">
       <c r="A248" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-144</t>
+          <t>WEB-SCREEN-135</t>
         </is>
       </c>
       <c r="B248" s="28" t="inlineStr">
@@ -46543,7 +46563,7 @@
       </c>
       <c r="E248" s="28" t="inlineStr">
         <is>
-          <t>Gallery · mobile — scholars present research on ambedkar studies</t>
+          <t>Gallery · desktop — ambedkar jayanti celebration 2025</t>
         </is>
       </c>
       <c r="F248" s="28" t="inlineStr">
@@ -46574,7 +46594,7 @@
     <row r="249">
       <c r="A249" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-152</t>
+          <t>WEB-SCREEN-140</t>
         </is>
       </c>
       <c r="B249" s="28" t="inlineStr">
@@ -46594,7 +46614,7 @@
       </c>
       <c r="E249" s="28" t="inlineStr">
         <is>
-          <t>Home · desktop — empowering india, every day</t>
+          <t>Gallery · desktop — glimpses from the national celebration</t>
         </is>
       </c>
       <c r="F249" s="28" t="inlineStr">
@@ -46613,7 +46633,7 @@
       <c r="K249" s="28" t="n"/>
       <c r="L249" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-374, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M249" s="28" t="inlineStr">
@@ -46625,7 +46645,7 @@
     <row r="250">
       <c r="A250" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-150</t>
+          <t>WEB-SCREEN-138</t>
         </is>
       </c>
       <c r="B250" s="28" t="inlineStr">
@@ -46645,7 +46665,7 @@
       </c>
       <c r="E250" s="28" t="inlineStr">
         <is>
-          <t>Home · desktop — bringing social justice to every doorstep through digital ac</t>
+          <t>Gallery · desktop — elder care workshop</t>
         </is>
       </c>
       <c r="F250" s="28" t="inlineStr">
@@ -46676,7 +46696,7 @@
     <row r="251">
       <c r="A251" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-153</t>
+          <t>WEB-SCREEN-147</t>
         </is>
       </c>
       <c r="B251" s="28" t="inlineStr">
@@ -46696,7 +46716,7 @@
       </c>
       <c r="E251" s="28" t="inlineStr">
         <is>
-          <t>Home · desktop — explore opportunities</t>
+          <t>Gallery · desktop — training for caregivers and elder care professionals</t>
         </is>
       </c>
       <c r="F251" s="28" t="inlineStr">
@@ -46727,7 +46747,7 @@
     <row r="252">
       <c r="A252" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-169</t>
+          <t>WEB-SCREEN-032</t>
         </is>
       </c>
       <c r="B252" s="28" t="inlineStr">
@@ -46747,7 +46767,7 @@
       </c>
       <c r="E252" s="28" t="inlineStr">
         <is>
-          <t>Home · desktop — view schemes</t>
+          <t>Gallery · mobile — “Ek Ped Maa Ke Naam”</t>
         </is>
       </c>
       <c r="F252" s="28" t="inlineStr">
@@ -46766,7 +46786,7 @@
       <c r="K252" s="28" t="n"/>
       <c r="L252" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M252" s="28" t="inlineStr">
@@ -46778,7 +46798,7 @@
     <row r="253">
       <c r="A253" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-157</t>
+          <t>WEB-SCREEN-144</t>
         </is>
       </c>
       <c r="B253" s="28" t="inlineStr">
@@ -46798,7 +46818,7 @@
       </c>
       <c r="E253" s="28" t="inlineStr">
         <is>
-          <t>Home · desktop — latest updates</t>
+          <t>Gallery · mobile — scholars present research on ambedkar studies</t>
         </is>
       </c>
       <c r="F253" s="28" t="inlineStr">
@@ -46829,7 +46849,7 @@
     <row r="254">
       <c r="A254" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-158</t>
+          <t>WEB-SCREEN-152</t>
         </is>
       </c>
       <c r="B254" s="28" t="inlineStr">
@@ -46849,7 +46869,7 @@
       </c>
       <c r="E254" s="28" t="inlineStr">
         <is>
-          <t>Home · desktop — new funding alert!</t>
+          <t>Home · desktop — empowering india, every day</t>
         </is>
       </c>
       <c r="F254" s="28" t="inlineStr">
@@ -46868,7 +46888,7 @@
       <c r="K254" s="28" t="n"/>
       <c r="L254" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-374, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M254" s="28" t="inlineStr">
@@ -46880,7 +46900,7 @@
     <row r="255">
       <c r="A255" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-033</t>
+          <t>WEB-SCREEN-150</t>
         </is>
       </c>
       <c r="B255" s="28" t="inlineStr">
@@ -46900,7 +46920,7 @@
       </c>
       <c r="E255" s="28" t="inlineStr">
         <is>
-          <t>Home · mobile — Go to slide 1</t>
+          <t>Home · desktop — bringing social justice to every doorstep through digital ac</t>
         </is>
       </c>
       <c r="F255" s="28" t="inlineStr">
@@ -46919,7 +46939,7 @@
       <c r="K255" s="28" t="n"/>
       <c r="L255" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M255" s="28" t="inlineStr">
@@ -46931,7 +46951,7 @@
     <row r="256">
       <c r="A256" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-036</t>
+          <t>WEB-SCREEN-153</t>
         </is>
       </c>
       <c r="B256" s="28" t="inlineStr">
@@ -46951,7 +46971,7 @@
       </c>
       <c r="E256" s="28" t="inlineStr">
         <is>
-          <t>Home · mobile — Go to slide 2</t>
+          <t>Home · desktop — explore opportunities</t>
         </is>
       </c>
       <c r="F256" s="28" t="inlineStr">
@@ -46970,7 +46990,7 @@
       <c r="K256" s="28" t="n"/>
       <c r="L256" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M256" s="28" t="inlineStr">
@@ -46982,7 +47002,7 @@
     <row r="257">
       <c r="A257" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-034</t>
+          <t>WEB-SCREEN-169</t>
         </is>
       </c>
       <c r="B257" s="28" t="inlineStr">
@@ -47002,7 +47022,7 @@
       </c>
       <c r="E257" s="28" t="inlineStr">
         <is>
-          <t>Home · mobile — Go to slide 3</t>
+          <t>Home · desktop — view schemes</t>
         </is>
       </c>
       <c r="F257" s="28" t="inlineStr">
@@ -47021,7 +47041,7 @@
       <c r="K257" s="28" t="n"/>
       <c r="L257" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M257" s="28" t="inlineStr">
@@ -47033,7 +47053,7 @@
     <row r="258">
       <c r="A258" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-035</t>
+          <t>WEB-SCREEN-157</t>
         </is>
       </c>
       <c r="B258" s="28" t="inlineStr">
@@ -47053,7 +47073,7 @@
       </c>
       <c r="E258" s="28" t="inlineStr">
         <is>
-          <t>Home · mobile — Go to slide 4</t>
+          <t>Home · desktop — latest updates</t>
         </is>
       </c>
       <c r="F258" s="28" t="inlineStr">
@@ -47072,7 +47092,7 @@
       <c r="K258" s="28" t="n"/>
       <c r="L258" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M258" s="28" t="inlineStr">
@@ -47084,7 +47104,7 @@
     <row r="259">
       <c r="A259" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-163</t>
+          <t>WEB-SCREEN-158</t>
         </is>
       </c>
       <c r="B259" s="28" t="inlineStr">
@@ -47104,7 +47124,7 @@
       </c>
       <c r="E259" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Home · mobile — smile - support for marginalised individuals for livelihood </t>
+          <t>Home · desktop — new funding alert!</t>
         </is>
       </c>
       <c r="F259" s="28" t="inlineStr">
@@ -47135,7 +47155,7 @@
     <row r="260">
       <c r="A260" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-156</t>
+          <t>WEB-SCREEN-033</t>
         </is>
       </c>
       <c r="B260" s="28" t="inlineStr">
@@ -47155,7 +47175,7 @@
       </c>
       <c r="E260" s="28" t="inlineStr">
         <is>
-          <t>Home · mobile — integrated rehabilitation, skills training and livelihood su</t>
+          <t>Home · mobile — Go to slide 1</t>
         </is>
       </c>
       <c r="F260" s="28" t="inlineStr">
@@ -47174,7 +47194,7 @@
       <c r="K260" s="28" t="n"/>
       <c r="L260" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M260" s="28" t="inlineStr">
@@ -47186,7 +47206,7 @@
     <row r="261">
       <c r="A261" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-037</t>
+          <t>WEB-SCREEN-036</t>
         </is>
       </c>
       <c r="B261" s="28" t="inlineStr">
@@ -47206,7 +47226,7 @@
       </c>
       <c r="E261" s="28" t="inlineStr">
         <is>
-          <t>Lok Sabha Question Answer · mobile — NCSK</t>
+          <t>Home · mobile — Go to slide 2</t>
         </is>
       </c>
       <c r="F261" s="28" t="inlineStr">
@@ -47237,7 +47257,7 @@
     <row r="262">
       <c r="A262" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-179</t>
+          <t>WEB-SCREEN-034</t>
         </is>
       </c>
       <c r="B262" s="28" t="inlineStr">
@@ -47257,7 +47277,7 @@
       </c>
       <c r="E262" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · desktop — discover the commissions, corporations, institutes and found</t>
+          <t>Home · mobile — Go to slide 3</t>
         </is>
       </c>
       <c r="F262" s="28" t="inlineStr">
@@ -47276,7 +47296,7 @@
       <c r="K262" s="28" t="n"/>
       <c r="L262" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-377, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M262" s="28" t="inlineStr">
@@ -47288,7 +47308,7 @@
     <row r="263">
       <c r="A263" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-189</t>
+          <t>WEB-SCREEN-035</t>
         </is>
       </c>
       <c r="B263" s="28" t="inlineStr">
@@ -47308,7 +47328,7 @@
       </c>
       <c r="E263" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · desktop — reset filters</t>
+          <t>Home · mobile — Go to slide 4</t>
         </is>
       </c>
       <c r="F263" s="28" t="inlineStr">
@@ -47327,7 +47347,7 @@
       <c r="K263" s="28" t="n"/>
       <c r="L263" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M263" s="28" t="inlineStr">
@@ -47339,7 +47359,7 @@
     <row r="264">
       <c r="A264" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-187</t>
+          <t>WEB-SCREEN-163</t>
         </is>
       </c>
       <c r="B264" s="28" t="inlineStr">
@@ -47359,7 +47379,7 @@
       </c>
       <c r="E264" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · desktop — organization</t>
+          <t xml:space="preserve">Home · mobile — smile - support for marginalised individuals for livelihood </t>
         </is>
       </c>
       <c r="F264" s="28" t="inlineStr">
@@ -47378,7 +47398,7 @@
       <c r="K264" s="28" t="n"/>
       <c r="L264" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-052, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M264" s="28" t="inlineStr">
@@ -47390,7 +47410,7 @@
     <row r="265">
       <c r="A265" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-172</t>
+          <t>WEB-SCREEN-156</t>
         </is>
       </c>
       <c r="B265" s="28" t="inlineStr">
@@ -47410,7 +47430,7 @@
       </c>
       <c r="E265" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · desktop — ashutosh niranjan</t>
+          <t>Home · mobile — integrated rehabilitation, skills training and livelihood su</t>
         </is>
       </c>
       <c r="F265" s="28" t="inlineStr">
@@ -47441,7 +47461,7 @@
     <row r="266">
       <c r="A266" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-186</t>
+          <t>WEB-SCREEN-037</t>
         </is>
       </c>
       <c r="B266" s="28" t="inlineStr">
@@ -47461,7 +47481,7 @@
       </c>
       <c r="E266" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · desktop — ms. priya sharma</t>
+          <t>Lok Sabha Question Answer · mobile — NCSK</t>
         </is>
       </c>
       <c r="F266" s="28" t="inlineStr">
@@ -47480,7 +47500,7 @@
       <c r="K266" s="28" t="n"/>
       <c r="L266" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M266" s="28" t="inlineStr">
@@ -47492,7 +47512,7 @@
     <row r="267">
       <c r="A267" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-188</t>
+          <t>WEB-SCREEN-179</t>
         </is>
       </c>
       <c r="B267" s="28" t="inlineStr">
@@ -47512,7 +47532,7 @@
       </c>
       <c r="E267" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · desktop — private secretary to the minister</t>
+          <t>Mosje Directory · desktop — discover the commissions, corporations, institutes and found</t>
         </is>
       </c>
       <c r="F267" s="28" t="inlineStr">
@@ -47531,7 +47551,7 @@
       <c r="K267" s="28" t="n"/>
       <c r="L267" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-377, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M267" s="28" t="inlineStr">
@@ -47543,7 +47563,7 @@
     <row r="268">
       <c r="A268" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-175</t>
+          <t>WEB-SCREEN-189</t>
         </is>
       </c>
       <c r="B268" s="28" t="inlineStr">
@@ -47563,7 +47583,7 @@
       </c>
       <c r="E268" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · mobile — browse our directory for key contact information of commissi</t>
+          <t>Mosje Directory · desktop — reset filters</t>
         </is>
       </c>
       <c r="F268" s="28" t="inlineStr">
@@ -47594,7 +47614,7 @@
     <row r="269">
       <c r="A269" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-180</t>
+          <t>WEB-SCREEN-187</t>
         </is>
       </c>
       <c r="B269" s="28" t="inlineStr">
@@ -47614,7 +47634,7 @@
       </c>
       <c r="E269" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · mobile — download directory</t>
+          <t>Mosje Directory · desktop — organization</t>
         </is>
       </c>
       <c r="F269" s="28" t="inlineStr">
@@ -47633,7 +47653,7 @@
       <c r="K269" s="28" t="n"/>
       <c r="L269" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-052, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M269" s="28" t="inlineStr">
@@ -47645,7 +47665,7 @@
     <row r="270">
       <c r="A270" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-190</t>
+          <t>WEB-SCREEN-172</t>
         </is>
       </c>
       <c r="B270" s="28" t="inlineStr">
@@ -47665,7 +47685,7 @@
       </c>
       <c r="E270" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · mobile — telephone(res./mobile)</t>
+          <t>Mosje Directory · desktop — ashutosh niranjan</t>
         </is>
       </c>
       <c r="F270" s="28" t="inlineStr">
@@ -47696,7 +47716,7 @@
     <row r="271">
       <c r="A271" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-173</t>
+          <t>WEB-SCREEN-186</t>
         </is>
       </c>
       <c r="B271" s="28" t="inlineStr">
@@ -47716,7 +47736,7 @@
       </c>
       <c r="E271" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · mobile — ashutosh niranjan, ias</t>
+          <t>Mosje Directory · desktop — ms. priya sharma</t>
         </is>
       </c>
       <c r="F271" s="28" t="inlineStr">
@@ -47747,7 +47767,7 @@
     <row r="272">
       <c r="A272" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-177</t>
+          <t>WEB-SCREEN-188</t>
         </is>
       </c>
       <c r="B272" s="28" t="inlineStr">
@@ -47767,7 +47787,7 @@
       </c>
       <c r="E272" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · mobile — devansh wathrey</t>
+          <t>Mosje Directory · desktop — private secretary to the minister</t>
         </is>
       </c>
       <c r="F272" s="28" t="inlineStr">
@@ -47798,7 +47818,7 @@
     <row r="273">
       <c r="A273" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-191</t>
+          <t>WEB-SCREEN-175</t>
         </is>
       </c>
       <c r="B273" s="28" t="inlineStr">
@@ -47818,7 +47838,7 @@
       </c>
       <c r="E273" s="28" t="inlineStr">
         <is>
-          <t>Mosje Directory · mobile — tripathi[dot]yogesh[at]nic[dot]in</t>
+          <t>Mosje Directory · mobile — browse our directory for key contact information of commissi</t>
         </is>
       </c>
       <c r="F273" s="28" t="inlineStr">
@@ -47849,7 +47869,7 @@
     <row r="274">
       <c r="A274" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-038</t>
+          <t>WEB-SCREEN-180</t>
         </is>
       </c>
       <c r="B274" s="28" t="inlineStr">
@@ -47869,7 +47889,7 @@
       </c>
       <c r="E274" s="28" t="inlineStr">
         <is>
-          <t>Notices · mobile — BJRNF</t>
+          <t>Mosje Directory · mobile — download directory</t>
         </is>
       </c>
       <c r="F274" s="28" t="inlineStr">
@@ -47888,7 +47908,7 @@
       <c r="K274" s="28" t="n"/>
       <c r="L274" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M274" s="28" t="inlineStr">
@@ -47900,7 +47920,7 @@
     <row r="275">
       <c r="A275" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-039</t>
+          <t>WEB-SCREEN-190</t>
         </is>
       </c>
       <c r="B275" s="28" t="inlineStr">
@@ -47920,7 +47940,7 @@
       </c>
       <c r="E275" s="28" t="inlineStr">
         <is>
-          <t>Notices · mobile — E-Anudaan</t>
+          <t>Mosje Directory · mobile — telephone(res./mobile)</t>
         </is>
       </c>
       <c r="F275" s="28" t="inlineStr">
@@ -47939,7 +47959,7 @@
       <c r="K275" s="28" t="n"/>
       <c r="L275" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M275" s="28" t="inlineStr">
@@ -47951,7 +47971,7 @@
     <row r="276">
       <c r="A276" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-192</t>
+          <t>WEB-SCREEN-173</t>
         </is>
       </c>
       <c r="B276" s="28" t="inlineStr">
@@ -47971,7 +47991,7 @@
       </c>
       <c r="E276" s="28" t="inlineStr">
         <is>
-          <t>Policies · desktop — 1. information collection we do not automatically gather any</t>
+          <t>Mosje Directory · mobile — ashutosh niranjan, ias</t>
         </is>
       </c>
       <c r="F276" s="28" t="inlineStr">
@@ -47990,7 +48010,7 @@
       <c r="K276" s="28" t="n"/>
       <c r="L276" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-379, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M276" s="28" t="inlineStr">
@@ -48002,7 +48022,7 @@
     <row r="277">
       <c r="A277" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-041</t>
+          <t>WEB-SCREEN-177</t>
         </is>
       </c>
       <c r="B277" s="28" t="inlineStr">
@@ -48022,7 +48042,7 @@
       </c>
       <c r="E277" s="28" t="inlineStr">
         <is>
-          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Home</t>
+          <t>Mosje Directory · mobile — devansh wathrey</t>
         </is>
       </c>
       <c r="F277" s="28" t="inlineStr">
@@ -48041,7 +48061,7 @@
       <c r="K277" s="28" t="n"/>
       <c r="L277" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M277" s="28" t="inlineStr">
@@ -48053,7 +48073,7 @@
     <row r="278">
       <c r="A278" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-042</t>
+          <t>WEB-SCREEN-191</t>
         </is>
       </c>
       <c r="B278" s="28" t="inlineStr">
@@ -48073,7 +48093,7 @@
       </c>
       <c r="E278" s="28" t="inlineStr">
         <is>
-          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Department</t>
+          <t>Mosje Directory · mobile — tripathi[dot]yogesh[at]nic[dot]in</t>
         </is>
       </c>
       <c r="F278" s="28" t="inlineStr">
@@ -48092,7 +48112,7 @@
       <c r="K278" s="28" t="n"/>
       <c r="L278" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M278" s="28" t="inlineStr">
@@ -48104,7 +48124,7 @@
     <row r="279">
       <c r="A279" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-040</t>
+          <t>WEB-SCREEN-038</t>
         </is>
       </c>
       <c r="B279" s="28" t="inlineStr">
@@ -48124,7 +48144,7 @@
       </c>
       <c r="E279" s="28" t="inlineStr">
         <is>
-          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Associated Organisations</t>
+          <t>Notices · mobile — BJRNF</t>
         </is>
       </c>
       <c r="F279" s="28" t="inlineStr">
@@ -48155,7 +48175,7 @@
     <row r="280">
       <c r="A280" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-043</t>
+          <t>WEB-SCREEN-039</t>
         </is>
       </c>
       <c r="B280" s="28" t="inlineStr">
@@ -48175,7 +48195,7 @@
       </c>
       <c r="E280" s="28" t="inlineStr">
         <is>
-          <t>Resources · mobile — DWBDNC</t>
+          <t>Notices · mobile — E-Anudaan</t>
         </is>
       </c>
       <c r="F280" s="28" t="inlineStr">
@@ -48206,7 +48226,7 @@
     <row r="281">
       <c r="A281" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-194</t>
+          <t>WEB-SCREEN-192</t>
         </is>
       </c>
       <c r="B281" s="28" t="inlineStr">
@@ -48226,7 +48246,7 @@
       </c>
       <c r="E281" s="28" t="inlineStr">
         <is>
-          <t>Rti · desktop — suo-moto disclosure</t>
+          <t>Policies · desktop — 1. information collection we do not automatically gather any</t>
         </is>
       </c>
       <c r="F281" s="28" t="inlineStr">
@@ -48245,7 +48265,7 @@
       <c r="K281" s="28" t="n"/>
       <c r="L281" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-113, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-379, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M281" s="28" t="inlineStr">
@@ -48257,7 +48277,7 @@
     <row r="282">
       <c r="A282" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-193</t>
+          <t>WEB-SCREEN-041</t>
         </is>
       </c>
       <c r="B282" s="28" t="inlineStr">
@@ -48277,7 +48297,7 @@
       </c>
       <c r="E282" s="28" t="inlineStr">
         <is>
-          <t>Rti · desktop — right to information act 2005</t>
+          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Home</t>
         </is>
       </c>
       <c r="F282" s="28" t="inlineStr">
@@ -48296,7 +48316,7 @@
       <c r="K282" s="28" t="n"/>
       <c r="L282" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-380, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M282" s="28" t="inlineStr">
@@ -48308,7 +48328,7 @@
     <row r="283">
       <c r="A283" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-195</t>
+          <t>WEB-SCREEN-042</t>
         </is>
       </c>
       <c r="B283" s="28" t="inlineStr">
@@ -48328,7 +48348,7 @@
       </c>
       <c r="E283" s="28" t="inlineStr">
         <is>
-          <t>Rti · desktop — the national commission for scheduled castes (ncsc) is a con</t>
+          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Department</t>
         </is>
       </c>
       <c r="F283" s="28" t="inlineStr">
@@ -48347,7 +48367,7 @@
       <c r="K283" s="28" t="n"/>
       <c r="L283" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M283" s="28" t="inlineStr">
@@ -48359,7 +48379,7 @@
     <row r="284">
       <c r="A284" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-009</t>
+          <t>WEB-SCREEN-040</t>
         </is>
       </c>
       <c r="B284" s="28" t="inlineStr">
@@ -48379,7 +48399,7 @@
       </c>
       <c r="E284" s="28" t="inlineStr">
         <is>
-          <t>Scheme Documents  Dr Ambedkar National Merit Award Scheme  · desktop — Scheme: Dr. Ambedkar National Merit Award S…</t>
+          <t>Procedure For Processing Grant In Aid Cases In Respect Of Voluntary Organisations · desktop — Associated Organisations</t>
         </is>
       </c>
       <c r="F284" s="28" t="inlineStr">
@@ -48398,7 +48418,7 @@
       <c r="K284" s="28" t="n"/>
       <c r="L284" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-329, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M284" s="28" t="inlineStr">
@@ -48410,7 +48430,7 @@
     <row r="285">
       <c r="A285" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-010</t>
+          <t>WEB-SCREEN-043</t>
         </is>
       </c>
       <c r="B285" s="28" t="inlineStr">
@@ -48430,7 +48450,7 @@
       </c>
       <c r="E285" s="28" t="inlineStr">
         <is>
-          <t>Scheme Documents  Merger Order · desktop — Scheme: Dr. Ambedkar Scheme for Social Inte…</t>
+          <t>Resources · mobile — DWBDNC</t>
         </is>
       </c>
       <c r="F285" s="28" t="inlineStr">
@@ -48449,7 +48469,7 @@
       <c r="K285" s="28" t="n"/>
       <c r="L285" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-330, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M285" s="28" t="inlineStr">
@@ -48461,7 +48481,7 @@
     <row r="286">
       <c r="A286" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-044</t>
+          <t>WEB-SCREEN-194</t>
         </is>
       </c>
       <c r="B286" s="28" t="inlineStr">
@@ -48481,7 +48501,7 @@
       </c>
       <c r="E286" s="28" t="inlineStr">
         <is>
-          <t>Schemes And Services  Geriatric Caregivers Training · mobile — Senior Citizens Welfare(SCW)</t>
+          <t>Rti · desktop — suo-moto disclosure</t>
         </is>
       </c>
       <c r="F286" s="28" t="inlineStr">
@@ -48500,7 +48520,7 @@
       <c r="K286" s="28" t="n"/>
       <c r="L286" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-113, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M286" s="28" t="inlineStr">
@@ -48512,7 +48532,7 @@
     <row r="287">
       <c r="A287" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-204</t>
+          <t>WEB-SCREEN-193</t>
         </is>
       </c>
       <c r="B287" s="28" t="inlineStr">
@@ -48532,7 +48552,7 @@
       </c>
       <c r="E287" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop — schemes and services</t>
+          <t>Rti · desktop — right to information act 2005</t>
         </is>
       </c>
       <c r="F287" s="28" t="inlineStr">
@@ -48551,7 +48571,7 @@
       <c r="K287" s="28" t="n"/>
       <c r="L287" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-380, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M287" s="28" t="inlineStr">
@@ -48563,7 +48583,7 @@
     <row r="288">
       <c r="A288" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-199</t>
+          <t>WEB-SCREEN-195</t>
         </is>
       </c>
       <c r="B288" s="28" t="inlineStr">
@@ -48583,7 +48603,7 @@
       </c>
       <c r="E288" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop — explore welfare schemes, social empowerment programs, and ci</t>
+          <t>Rti · desktop — the national commission for scheduled castes (ncsc) is a con</t>
         </is>
       </c>
       <c r="F288" s="28" t="inlineStr">
@@ -48614,7 +48634,7 @@
     <row r="289">
       <c r="A289" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-205</t>
+          <t>WEB-SCREEN-009</t>
         </is>
       </c>
       <c r="B289" s="28" t="inlineStr">
@@ -48634,7 +48654,7 @@
       </c>
       <c r="E289" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop — search by scheme name or keyword</t>
+          <t>Scheme Documents  Dr Ambedkar National Merit Award Scheme  · desktop — Scheme: Dr. Ambedkar National Merit Award S…</t>
         </is>
       </c>
       <c r="F289" s="28" t="inlineStr">
@@ -48653,7 +48673,7 @@
       <c r="K289" s="28" t="n"/>
       <c r="L289" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-381, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-329, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M289" s="28" t="inlineStr">
@@ -48665,7 +48685,7 @@
     <row r="290">
       <c r="A290" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-207</t>
+          <t>WEB-SCREEN-010</t>
         </is>
       </c>
       <c r="B290" s="28" t="inlineStr">
@@ -48685,7 +48705,7 @@
       </c>
       <c r="E290" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Schemes Services · desktop — smile - support for marginalised individuals for livelihood </t>
+          <t>Scheme Documents  Merger Order · desktop — Scheme: Dr. Ambedkar Scheme for Social Inte…</t>
         </is>
       </c>
       <c r="F290" s="28" t="inlineStr">
@@ -48704,7 +48724,7 @@
       <c r="K290" s="28" t="n"/>
       <c r="L290" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-330, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M290" s="28" t="inlineStr">
@@ -48716,7 +48736,7 @@
     <row r="291">
       <c r="A291" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-200</t>
+          <t>WEB-SCREEN-044</t>
         </is>
       </c>
       <c r="B291" s="28" t="inlineStr">
@@ -48736,7 +48756,7 @@
       </c>
       <c r="E291" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop — integrated rehabilitation, skills training and livelihood su</t>
+          <t>Schemes And Services  Geriatric Caregivers Training · mobile — Senior Citizens Welfare(SCW)</t>
         </is>
       </c>
       <c r="F291" s="28" t="inlineStr">
@@ -48755,7 +48775,7 @@
       <c r="K291" s="28" t="n"/>
       <c r="L291" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M291" s="28" t="inlineStr">
@@ -48767,7 +48787,7 @@
     <row r="292">
       <c r="A292" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-203</t>
+          <t>WEB-SCREEN-204</t>
         </is>
       </c>
       <c r="B292" s="28" t="inlineStr">
@@ -48787,7 +48807,7 @@
       </c>
       <c r="E292" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · desktop — scheme for economic empowerment of dnts (seed)</t>
+          <t>Schemes Services · desktop — schemes and services</t>
         </is>
       </c>
       <c r="F292" s="28" t="inlineStr">
@@ -48818,7 +48838,7 @@
     <row r="293">
       <c r="A293" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-209</t>
+          <t>WEB-SCREEN-199</t>
         </is>
       </c>
       <c r="B293" s="28" t="inlineStr">
@@ -48838,7 +48858,7 @@
       </c>
       <c r="E293" s="28" t="inlineStr">
         <is>
-          <t>Schemes Services · mobile — venture capital fund for scs &amp; obcs</t>
+          <t>Schemes Services · desktop — explore welfare schemes, social empowerment programs, and ci</t>
         </is>
       </c>
       <c r="F293" s="28" t="inlineStr">
@@ -48869,7 +48889,7 @@
     <row r="294">
       <c r="A294" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-048</t>
+          <t>WEB-SCREEN-205</t>
         </is>
       </c>
       <c r="B294" s="28" t="inlineStr">
@@ -48889,7 +48909,7 @@
       </c>
       <c r="E294" s="28" t="inlineStr">
         <is>
-          <t>State · Home 320 · mobile320 — Go to slide 1</t>
+          <t>Schemes Services · desktop — search by scheme name or keyword</t>
         </is>
       </c>
       <c r="F294" s="28" t="inlineStr">
@@ -48908,7 +48928,7 @@
       <c r="K294" s="28" t="n"/>
       <c r="L294" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-381, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M294" s="28" t="inlineStr">
@@ -48920,7 +48940,7 @@
     <row r="295">
       <c r="A295" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-045</t>
+          <t>WEB-SCREEN-207</t>
         </is>
       </c>
       <c r="B295" s="28" t="inlineStr">
@@ -48940,7 +48960,7 @@
       </c>
       <c r="E295" s="28" t="inlineStr">
         <is>
-          <t>State · Home 320 · mobile320 — Go to slide 2</t>
+          <t xml:space="preserve">Schemes Services · desktop — smile - support for marginalised individuals for livelihood </t>
         </is>
       </c>
       <c r="F295" s="28" t="inlineStr">
@@ -48959,7 +48979,7 @@
       <c r="K295" s="28" t="n"/>
       <c r="L295" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M295" s="28" t="inlineStr">
@@ -48971,7 +48991,7 @@
     <row r="296">
       <c r="A296" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-046</t>
+          <t>WEB-SCREEN-200</t>
         </is>
       </c>
       <c r="B296" s="28" t="inlineStr">
@@ -48991,7 +49011,7 @@
       </c>
       <c r="E296" s="28" t="inlineStr">
         <is>
-          <t>State · Home 320 · mobile320 — Go to slide 3</t>
+          <t>Schemes Services · desktop — integrated rehabilitation, skills training and livelihood su</t>
         </is>
       </c>
       <c r="F296" s="28" t="inlineStr">
@@ -49010,7 +49030,7 @@
       <c r="K296" s="28" t="n"/>
       <c r="L296" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M296" s="28" t="inlineStr">
@@ -49022,7 +49042,7 @@
     <row r="297">
       <c r="A297" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-047</t>
+          <t>WEB-SCREEN-203</t>
         </is>
       </c>
       <c r="B297" s="28" t="inlineStr">
@@ -49042,7 +49062,7 @@
       </c>
       <c r="E297" s="28" t="inlineStr">
         <is>
-          <t>State · Home 320 · mobile320 — Go to slide 4</t>
+          <t>Schemes Services · desktop — scheme for economic empowerment of dnts (seed)</t>
         </is>
       </c>
       <c r="F297" s="28" t="inlineStr">
@@ -49061,7 +49081,7 @@
       <c r="K297" s="28" t="n"/>
       <c r="L297" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M297" s="28" t="inlineStr">
@@ -49073,7 +49093,7 @@
     <row r="298">
       <c r="A298" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-049</t>
+          <t>WEB-SCREEN-209</t>
         </is>
       </c>
       <c r="B298" s="28" t="inlineStr">
@@ -49093,7 +49113,7 @@
       </c>
       <c r="E298" s="28" t="inlineStr">
         <is>
-          <t>State · Home Hindi · desktop — घर</t>
+          <t>Schemes Services · mobile — venture capital fund for scs &amp; obcs</t>
         </is>
       </c>
       <c r="F298" s="28" t="inlineStr">
@@ -49112,7 +49132,7 @@
       <c r="K298" s="28" t="n"/>
       <c r="L298" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M298" s="28" t="inlineStr">
@@ -49124,7 +49144,7 @@
     <row r="299">
       <c r="A299" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-050</t>
+          <t>WEB-SCREEN-048</t>
         </is>
       </c>
       <c r="B299" s="28" t="inlineStr">
@@ -49144,7 +49164,7 @@
       </c>
       <c r="E299" s="28" t="inlineStr">
         <is>
-          <t>State · Home Hindi · desktop — विभाग</t>
+          <t>State · Home 320 · mobile320 — Go to slide 1</t>
         </is>
       </c>
       <c r="F299" s="28" t="inlineStr">
@@ -49175,7 +49195,7 @@
     <row r="300">
       <c r="A300" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-051</t>
+          <t>WEB-SCREEN-045</t>
         </is>
       </c>
       <c r="B300" s="28" t="inlineStr">
@@ -49195,7 +49215,7 @@
       </c>
       <c r="E300" s="28" t="inlineStr">
         <is>
-          <t>State · Home Hindi · desktop — संबद्ध संगठन</t>
+          <t>State · Home 320 · mobile320 — Go to slide 2</t>
         </is>
       </c>
       <c r="F300" s="28" t="inlineStr">
@@ -49226,7 +49246,7 @@
     <row r="301">
       <c r="A301" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-052</t>
+          <t>WEB-SCREEN-046</t>
         </is>
       </c>
       <c r="B301" s="28" t="inlineStr">
@@ -49246,7 +49266,7 @@
       </c>
       <c r="E301" s="28" t="inlineStr">
         <is>
-          <t>State · Mega Menu Department · desktop — Close Department</t>
+          <t>State · Home 320 · mobile320 — Go to slide 3</t>
         </is>
       </c>
       <c r="F301" s="28" t="inlineStr">
@@ -49277,7 +49297,7 @@
     <row r="302">
       <c r="A302" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-022</t>
+          <t>WEB-SCREEN-047</t>
         </is>
       </c>
       <c r="B302" s="28" t="inlineStr">
@@ -49297,7 +49317,7 @@
       </c>
       <c r="E302" s="28" t="inlineStr">
         <is>
-          <t>State · Search Scholarship · desktop — Scholarship</t>
+          <t>State · Home 320 · mobile320 — Go to slide 4</t>
         </is>
       </c>
       <c r="F302" s="28" t="inlineStr">
@@ -49316,7 +49336,7 @@
       <c r="K302" s="28" t="n"/>
       <c r="L302" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-334, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M302" s="28" t="inlineStr">
@@ -49328,7 +49348,7 @@
     <row r="303">
       <c r="A303" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-023</t>
+          <t>WEB-SCREEN-049</t>
         </is>
       </c>
       <c r="B303" s="28" t="inlineStr">
@@ -49348,7 +49368,7 @@
       </c>
       <c r="E303" s="28" t="inlineStr">
         <is>
-          <t>State · Search Scholarship · desktop — …</t>
+          <t>State · Home Hindi · desktop — घर</t>
         </is>
       </c>
       <c r="F303" s="28" t="inlineStr">
@@ -49367,7 +49387,7 @@
       <c r="K303" s="28" t="n"/>
       <c r="L303" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-093, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M303" s="28" t="inlineStr">
@@ -49379,7 +49399,7 @@
     <row r="304">
       <c r="A304" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-212</t>
+          <t>WEB-SCREEN-050</t>
         </is>
       </c>
       <c r="B304" s="28" t="inlineStr">
@@ -49399,7 +49419,7 @@
       </c>
       <c r="E304" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suo Moto Disclosure · desktop — government's proactive release of key information to ensure </t>
+          <t>State · Home Hindi · desktop — विभाग</t>
         </is>
       </c>
       <c r="F304" s="28" t="inlineStr">
@@ -49418,7 +49438,7 @@
       <c r="K304" s="28" t="n"/>
       <c r="L304" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M304" s="28" t="inlineStr">
@@ -49430,7 +49450,7 @@
     <row r="305">
       <c r="A305" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-221</t>
+          <t>WEB-SCREEN-051</t>
         </is>
       </c>
       <c r="B305" s="28" t="inlineStr">
@@ -49450,7 +49470,7 @@
       </c>
       <c r="E305" s="28" t="inlineStr">
         <is>
-          <t>Suo Moto Disclosure · desktop — sort by recently updated</t>
+          <t>State · Home Hindi · desktop — संबद्ध संगठन</t>
         </is>
       </c>
       <c r="F305" s="28" t="inlineStr">
@@ -49469,7 +49489,7 @@
       <c r="K305" s="28" t="n"/>
       <c r="L305" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M305" s="28" t="inlineStr">
@@ -49481,7 +49501,7 @@
     <row r="306">
       <c r="A306" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-218</t>
+          <t>WEB-SCREEN-052</t>
         </is>
       </c>
       <c r="B306" s="28" t="inlineStr">
@@ -49501,7 +49521,7 @@
       </c>
       <c r="E306" s="28" t="inlineStr">
         <is>
-          <t>Suo Moto Disclosure · desktop — list of faa</t>
+          <t>State · Mega Menu Department · desktop — Close Department</t>
         </is>
       </c>
       <c r="F306" s="28" t="inlineStr">
@@ -49520,7 +49540,7 @@
       <c r="K306" s="28" t="n"/>
       <c r="L306" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M306" s="28" t="inlineStr">
@@ -49532,7 +49552,7 @@
     <row r="307">
       <c r="A307" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-215</t>
+          <t>WEB-SCREEN-022</t>
         </is>
       </c>
       <c r="B307" s="28" t="inlineStr">
@@ -49552,7 +49572,7 @@
       </c>
       <c r="E307" s="28" t="inlineStr">
         <is>
-          <t>Suo Moto Disclosure · desktop — list of cpio</t>
+          <t>State · Search Scholarship · desktop — Scholarship</t>
         </is>
       </c>
       <c r="F307" s="28" t="inlineStr">
@@ -49571,7 +49591,7 @@
       <c r="K307" s="28" t="n"/>
       <c r="L307" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-398, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-334, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M307" s="28" t="inlineStr">
@@ -49583,7 +49603,7 @@
     <row r="308">
       <c r="A308" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-216</t>
+          <t>WEB-SCREEN-023</t>
         </is>
       </c>
       <c r="B308" s="28" t="inlineStr">
@@ -49603,7 +49623,7 @@
       </c>
       <c r="E308" s="28" t="inlineStr">
         <is>
-          <t>Suo Moto Disclosure · desktop — list of cpio and faa</t>
+          <t>State · Search Scholarship · desktop — …</t>
         </is>
       </c>
       <c r="F308" s="28" t="inlineStr">
@@ -49622,7 +49642,7 @@
       <c r="K308" s="28" t="n"/>
       <c r="L308" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-093, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M308" s="28" t="inlineStr">
@@ -49634,7 +49654,7 @@
     <row r="309">
       <c r="A309" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-217</t>
+          <t>WEB-SCREEN-212</t>
         </is>
       </c>
       <c r="B309" s="28" t="inlineStr">
@@ -49654,7 +49674,7 @@
       </c>
       <c r="E309" s="28" t="inlineStr">
         <is>
-          <t>Suo Moto Disclosure · desktop — list of cpios and faas</t>
+          <t xml:space="preserve">Suo Moto Disclosure · desktop — government's proactive release of key information to ensure </t>
         </is>
       </c>
       <c r="F309" s="28" t="inlineStr">
@@ -49685,7 +49705,7 @@
     <row r="310">
       <c r="A310" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-053</t>
+          <t>WEB-SCREEN-221</t>
         </is>
       </c>
       <c r="B310" s="28" t="inlineStr">
@@ -49705,7 +49725,7 @@
       </c>
       <c r="E310" s="28" t="inlineStr">
         <is>
-          <t>Supreme Court Judgement · mobile — NCSK</t>
+          <t>Suo Moto Disclosure · desktop — sort by recently updated</t>
         </is>
       </c>
       <c r="F310" s="28" t="inlineStr">
@@ -49724,7 +49744,7 @@
       <c r="K310" s="28" t="n"/>
       <c r="L310" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M310" s="28" t="inlineStr">
@@ -49736,7 +49756,7 @@
     <row r="311">
       <c r="A311" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-222</t>
+          <t>WEB-SCREEN-218</t>
         </is>
       </c>
       <c r="B311" s="28" t="inlineStr">
@@ -49756,7 +49776,7 @@
       </c>
       <c r="E311" s="28" t="inlineStr">
         <is>
-          <t>Tenders · desktop — search by tender name or keyword</t>
+          <t>Suo Moto Disclosure · desktop — list of faa</t>
         </is>
       </c>
       <c r="F311" s="28" t="inlineStr">
@@ -49775,7 +49795,7 @@
       <c r="K311" s="28" t="n"/>
       <c r="L311" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-387, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M311" s="28" t="inlineStr">
@@ -49787,7 +49807,7 @@
     <row r="312">
       <c r="A312" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-278</t>
+          <t>WEB-SCREEN-215</t>
         </is>
       </c>
       <c r="B312" s="28" t="inlineStr">
@@ -49807,7 +49827,7 @@
       </c>
       <c r="E312" s="28" t="inlineStr">
         <is>
-          <t>Tenders · desktop — archived</t>
+          <t>Suo Moto Disclosure · desktop — list of cpio</t>
         </is>
       </c>
       <c r="F312" s="28" t="inlineStr">
@@ -49826,7 +49846,7 @@
       <c r="K312" s="28" t="n"/>
       <c r="L312" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-276, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-398, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M312" s="28" t="inlineStr">
@@ -49838,7 +49858,7 @@
     <row r="313">
       <c r="A313" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-054</t>
+          <t>WEB-SCREEN-216</t>
         </is>
       </c>
       <c r="B313" s="28" t="inlineStr">
@@ -49858,7 +49878,7 @@
       </c>
       <c r="E313" s="28" t="inlineStr">
         <is>
-          <t>Tenders · mobile — NSFDC</t>
+          <t>Suo Moto Disclosure · desktop — list of cpio and faa</t>
         </is>
       </c>
       <c r="F313" s="28" t="inlineStr">
@@ -49877,7 +49897,7 @@
       <c r="K313" s="28" t="n"/>
       <c r="L313" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M313" s="28" t="inlineStr">
@@ -49889,7 +49909,7 @@
     <row r="314">
       <c r="A314" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-282</t>
+          <t>WEB-SCREEN-217</t>
         </is>
       </c>
       <c r="B314" s="28" t="inlineStr">
@@ -49909,7 +49929,7 @@
       </c>
       <c r="E314" s="28" t="inlineStr">
         <is>
-          <t>Tenders · mobile — explore current tender notices, eligibility details, and sub</t>
+          <t>Suo Moto Disclosure · desktop — list of cpios and faas</t>
         </is>
       </c>
       <c r="F314" s="28" t="inlineStr">
@@ -49928,7 +49948,7 @@
       <c r="K314" s="28" t="n"/>
       <c r="L314" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M314" s="28" t="inlineStr">
@@ -49940,7 +49960,7 @@
     <row r="315">
       <c r="A315" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-283</t>
+          <t>WEB-SCREEN-053</t>
         </is>
       </c>
       <c r="B315" s="28" t="inlineStr">
@@ -49960,7 +49980,7 @@
       </c>
       <c r="E315" s="28" t="inlineStr">
         <is>
-          <t>Tenders · mobile — active tenders</t>
+          <t>Supreme Court Judgement · mobile — NCSK</t>
         </is>
       </c>
       <c r="F315" s="28" t="inlineStr">
@@ -49979,7 +49999,7 @@
       <c r="K315" s="28" t="n"/>
       <c r="L315" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M315" s="28" t="inlineStr">
@@ -49991,7 +50011,7 @@
     <row r="316">
       <c r="A316" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-055</t>
+          <t>WEB-SCREEN-222</t>
         </is>
       </c>
       <c r="B316" s="28" t="inlineStr">
@@ -50011,7 +50031,7 @@
       </c>
       <c r="E316" s="28" t="inlineStr">
         <is>
-          <t>Updates · mobile — NOS</t>
+          <t>Tenders · desktop — search by tender name or keyword</t>
         </is>
       </c>
       <c r="F316" s="28" t="inlineStr">
@@ -50030,7 +50050,7 @@
       <c r="K316" s="28" t="n"/>
       <c r="L316" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-387, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M316" s="28" t="inlineStr">
@@ -50042,7 +50062,7 @@
     <row r="317">
       <c r="A317" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-230</t>
+          <t>WEB-SCREEN-278</t>
         </is>
       </c>
       <c r="B317" s="28" t="inlineStr">
@@ -50062,7 +50082,7 @@
       </c>
       <c r="E317" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · desktop — search by vacancy name or keyword</t>
+          <t>Tenders · desktop — archived</t>
         </is>
       </c>
       <c r="F317" s="28" t="inlineStr">
@@ -50081,7 +50101,7 @@
       <c r="K317" s="28" t="n"/>
       <c r="L317" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-388, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-276, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M317" s="28" t="inlineStr">
@@ -50093,7 +50113,7 @@
     <row r="318">
       <c r="A318" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-225</t>
+          <t>WEB-SCREEN-054</t>
         </is>
       </c>
       <c r="B318" s="28" t="inlineStr">
@@ -50113,7 +50133,7 @@
       </c>
       <c r="E318" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · desktop — engagement of supervisor/consultant (contract)</t>
+          <t>Tenders · mobile — NSFDC</t>
         </is>
       </c>
       <c r="F318" s="28" t="inlineStr">
@@ -50132,7 +50152,7 @@
       <c r="K318" s="28" t="n"/>
       <c r="L318" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M318" s="28" t="inlineStr">
@@ -50144,7 +50164,7 @@
     <row r="319">
       <c r="A319" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-227</t>
+          <t>WEB-SCREEN-282</t>
         </is>
       </c>
       <c r="B319" s="28" t="inlineStr">
@@ -50164,7 +50184,7 @@
       </c>
       <c r="E319" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · desktop — new delhi · contract · apply by 30 nov 2025</t>
+          <t>Tenders · mobile — explore current tender notices, eligibility details, and sub</t>
         </is>
       </c>
       <c r="F319" s="28" t="inlineStr">
@@ -50183,7 +50203,7 @@
       <c r="K319" s="28" t="n"/>
       <c r="L319" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
         </is>
       </c>
       <c r="M319" s="28" t="inlineStr">
@@ -50195,7 +50215,7 @@
     <row r="320">
       <c r="A320" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-233</t>
+          <t>WEB-SCREEN-283</t>
         </is>
       </c>
       <c r="B320" s="28" t="inlineStr">
@@ -50215,7 +50235,7 @@
       </c>
       <c r="E320" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vacancies · desktop — supervisory and consultant roles for project implementation </t>
+          <t>Tenders · mobile — active tenders</t>
         </is>
       </c>
       <c r="F320" s="28" t="inlineStr">
@@ -50234,7 +50254,7 @@
       <c r="K320" s="28" t="n"/>
       <c r="L320" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Withdrawn: on the re-capture the design and build values could not both be proven on screen (the element was covered by the sticky header or not painted where the page says it is), so the comparison is not published.</t>
         </is>
       </c>
       <c r="M320" s="28" t="inlineStr">
@@ -50246,7 +50266,7 @@
     <row r="321">
       <c r="A321" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-234</t>
+          <t>WEB-SCREEN-055</t>
         </is>
       </c>
       <c r="B321" s="28" t="inlineStr">
@@ -50266,7 +50286,7 @@
       </c>
       <c r="E321" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · desktop — temporary / short-term consultants</t>
+          <t>Updates · mobile — NOS</t>
         </is>
       </c>
       <c r="F321" s="28" t="inlineStr">
@@ -50285,7 +50305,7 @@
       <c r="K321" s="28" t="n"/>
       <c r="L321" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M321" s="28" t="inlineStr">
@@ -50297,7 +50317,7 @@
     <row r="322">
       <c r="A322" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-226</t>
+          <t>WEB-SCREEN-230</t>
         </is>
       </c>
       <c r="B322" s="28" t="inlineStr">
@@ -50317,7 +50337,7 @@
       </c>
       <c r="E322" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · desktop — multiple locations · contract · ongoing</t>
+          <t>Vacancies · desktop — search by vacancy name or keyword</t>
         </is>
       </c>
       <c r="F322" s="28" t="inlineStr">
@@ -50336,7 +50356,7 @@
       <c r="K322" s="28" t="n"/>
       <c r="L322" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-388, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M322" s="28" t="inlineStr">
@@ -50348,7 +50368,7 @@
     <row r="323">
       <c r="A323" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-229</t>
+          <t>WEB-SCREEN-225</t>
         </is>
       </c>
       <c r="B323" s="28" t="inlineStr">
@@ -50368,7 +50388,7 @@
       </c>
       <c r="E323" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · mobile — search by scheme name or keyword</t>
+          <t>Vacancies · desktop — engagement of supervisor/consultant (contract)</t>
         </is>
       </c>
       <c r="F323" s="28" t="inlineStr">
@@ -50387,7 +50407,7 @@
       <c r="K323" s="28" t="n"/>
       <c r="L323" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-381, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M323" s="28" t="inlineStr">
@@ -50399,7 +50419,7 @@
     <row r="324">
       <c r="A324" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-224</t>
+          <t>WEB-SCREEN-227</t>
         </is>
       </c>
       <c r="B324" s="28" t="inlineStr">
@@ -50419,7 +50439,7 @@
       </c>
       <c r="E324" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · mobile — contact &amp; support</t>
+          <t>Vacancies · desktop — new delhi · contract · apply by 30 nov 2025</t>
         </is>
       </c>
       <c r="F324" s="28" t="inlineStr">
@@ -50438,7 +50458,7 @@
       <c r="K324" s="28" t="n"/>
       <c r="L324" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-389, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M324" s="28" t="inlineStr">
@@ -50450,7 +50470,7 @@
     <row r="325">
       <c r="A325" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-228</t>
+          <t>WEB-SCREEN-233</t>
         </is>
       </c>
       <c r="B325" s="28" t="inlineStr">
@@ -50470,7 +50490,7 @@
       </c>
       <c r="E325" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · mobile — nodal ministry</t>
+          <t xml:space="preserve">Vacancies · desktop — supervisory and consultant roles for project implementation </t>
         </is>
       </c>
       <c r="F325" s="28" t="inlineStr">
@@ -50501,7 +50521,7 @@
     <row r="326">
       <c r="A326" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-232</t>
+          <t>WEB-SCREEN-234</t>
         </is>
       </c>
       <c r="B326" s="28" t="inlineStr">
@@ -50521,7 +50541,7 @@
       </c>
       <c r="E326" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · mobile — shreshta@dosje.gov.in</t>
+          <t>Vacancies · desktop — temporary / short-term consultants</t>
         </is>
       </c>
       <c r="F326" s="28" t="inlineStr">
@@ -50552,7 +50572,7 @@
     <row r="327">
       <c r="A327" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-223</t>
+          <t>WEB-SCREEN-226</t>
         </is>
       </c>
       <c r="B327" s="28" t="inlineStr">
@@ -50572,7 +50592,7 @@
       </c>
       <c r="E327" s="28" t="inlineStr">
         <is>
-          <t>Vacancies · mobile — 5th floor, lok nayak bhawan, khan market, new delhi - 110003</t>
+          <t>Vacancies · desktop — multiple locations · contract · ongoing</t>
         </is>
       </c>
       <c r="F327" s="28" t="inlineStr">
@@ -50603,7 +50623,7 @@
     <row r="328">
       <c r="A328" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-024</t>
+          <t>WEB-SCREEN-229</t>
         </is>
       </c>
       <c r="B328" s="28" t="inlineStr">
@@ -50623,7 +50643,7 @@
       </c>
       <c r="E328" s="28" t="inlineStr">
         <is>
-          <t>Visitor Analytics · desktop — Previous</t>
+          <t>Vacancies · mobile — search by scheme name or keyword</t>
         </is>
       </c>
       <c r="F328" s="28" t="inlineStr">
@@ -50642,7 +50662,7 @@
       <c r="K328" s="28" t="n"/>
       <c r="L328" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-085, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-381, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M328" s="28" t="inlineStr">
@@ -50654,7 +50674,7 @@
     <row r="329">
       <c r="A329" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-240</t>
+          <t>WEB-SCREEN-224</t>
         </is>
       </c>
       <c r="B329" s="28" t="inlineStr">
@@ -50674,7 +50694,7 @@
       </c>
       <c r="E329" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop — discover the commissions, corporations, institutes and found</t>
+          <t>Vacancies · mobile — contact &amp; support</t>
         </is>
       </c>
       <c r="F329" s="28" t="inlineStr">
@@ -50693,7 +50713,7 @@
       <c r="K329" s="28" t="n"/>
       <c r="L329" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-SCREEN-377, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-389, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M329" s="28" t="inlineStr">
@@ -50705,7 +50725,7 @@
     <row r="330">
       <c r="A330" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-245</t>
+          <t>WEB-SCREEN-228</t>
         </is>
       </c>
       <c r="B330" s="28" t="inlineStr">
@@ -50725,7 +50745,7 @@
       </c>
       <c r="E330" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop — mosje officials</t>
+          <t>Vacancies · mobile — nodal ministry</t>
         </is>
       </c>
       <c r="F330" s="28" t="inlineStr">
@@ -50756,7 +50776,7 @@
     <row r="331">
       <c r="A331" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-243</t>
+          <t>WEB-SCREEN-232</t>
         </is>
       </c>
       <c r="B331" s="28" t="inlineStr">
@@ -50776,7 +50796,7 @@
       </c>
       <c r="E331" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop — min-sje@nic.in</t>
+          <t>Vacancies · mobile — shreshta@dosje.gov.in</t>
         </is>
       </c>
       <c r="F331" s="28" t="inlineStr">
@@ -50807,7 +50827,7 @@
     <row r="332">
       <c r="A332" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-236</t>
+          <t>WEB-SCREEN-223</t>
         </is>
       </c>
       <c r="B332" s="28" t="inlineStr">
@@ -50827,7 +50847,7 @@
       </c>
       <c r="E332" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop — 201 c-wing, shastri bhawan, new delhi</t>
+          <t>Vacancies · mobile — 5th floor, lok nayak bhawan, khan market, new delhi - 110003</t>
         </is>
       </c>
       <c r="F332" s="28" t="inlineStr">
@@ -50858,7 +50878,7 @@
     <row r="333">
       <c r="A333" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-244</t>
+          <t>WEB-SCREEN-024</t>
         </is>
       </c>
       <c r="B333" s="28" t="inlineStr">
@@ -50878,7 +50898,7 @@
       </c>
       <c r="E333" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop — mosathawale@gmail.com</t>
+          <t>Visitor Analytics · desktop — Previous</t>
         </is>
       </c>
       <c r="F333" s="28" t="inlineStr">
@@ -50897,7 +50917,7 @@
       <c r="K333" s="28" t="n"/>
       <c r="L333" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-085, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M333" s="28" t="inlineStr">
@@ -50909,7 +50929,7 @@
     <row r="334">
       <c r="A334" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-250</t>
+          <t>WEB-SCREEN-240</t>
         </is>
       </c>
       <c r="B334" s="28" t="inlineStr">
@@ -50929,7 +50949,7 @@
       </c>
       <c r="E334" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · desktop — shri b l verma</t>
+          <t>Whos Who · desktop — discover the commissions, corporations, institutes and found</t>
         </is>
       </c>
       <c r="F334" s="28" t="inlineStr">
@@ -50948,7 +50968,7 @@
       <c r="K334" s="28" t="n"/>
       <c r="L334" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-SCREEN-377, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M334" s="28" t="inlineStr">
@@ -50960,7 +50980,7 @@
     <row r="335">
       <c r="A335" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-057</t>
+          <t>WEB-SCREEN-245</t>
         </is>
       </c>
       <c r="B335" s="28" t="inlineStr">
@@ -50980,7 +51000,7 @@
       </c>
       <c r="E335" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile — Dr. Virendra Kumar</t>
+          <t>Whos Who · desktop — mosje officials</t>
         </is>
       </c>
       <c r="F335" s="28" t="inlineStr">
@@ -50999,7 +51019,7 @@
       <c r="K335" s="28" t="n"/>
       <c r="L335" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M335" s="28" t="inlineStr">
@@ -51011,7 +51031,7 @@
     <row r="336">
       <c r="A336" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-058</t>
+          <t>WEB-SCREEN-243</t>
         </is>
       </c>
       <c r="B336" s="28" t="inlineStr">
@@ -51031,7 +51051,7 @@
       </c>
       <c r="E336" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile — Shri Kishor Makwana</t>
+          <t>Whos Who · desktop — min-sje@nic.in</t>
         </is>
       </c>
       <c r="F336" s="28" t="inlineStr">
@@ -51050,7 +51070,7 @@
       <c r="K336" s="28" t="n"/>
       <c r="L336" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M336" s="28" t="inlineStr">
@@ -51062,7 +51082,7 @@
     <row r="337">
       <c r="A337" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-288</t>
+          <t>WEB-SCREEN-236</t>
         </is>
       </c>
       <c r="B337" s="28" t="inlineStr">
@@ -51082,7 +51102,7 @@
       </c>
       <c r="E337" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile — Shri Kaishab Bihari</t>
+          <t>Whos Who · desktop — 201 c-wing, shastri bhawan, new delhi</t>
         </is>
       </c>
       <c r="F337" s="28" t="inlineStr">
@@ -51101,7 +51121,7 @@
       <c r="K337" s="28" t="n"/>
       <c r="L337" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M337" s="28" t="inlineStr">
@@ -51113,7 +51133,7 @@
     <row r="338">
       <c r="A338" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-289</t>
+          <t>WEB-SCREEN-244</t>
         </is>
       </c>
       <c r="B338" s="28" t="inlineStr">
@@ -51133,7 +51153,7 @@
       </c>
       <c r="E338" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile — Sadhvi Niranjan Jyoti</t>
+          <t>Whos Who · desktop — mosathawale@gmail.com</t>
         </is>
       </c>
       <c r="F338" s="28" t="inlineStr">
@@ -51152,7 +51172,7 @@
       <c r="K338" s="28" t="n"/>
       <c r="L338" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
         </is>
       </c>
       <c r="M338" s="28" t="inlineStr">
@@ -51164,7 +51184,7 @@
     <row r="339">
       <c r="A339" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-235</t>
+          <t>WEB-SCREEN-250</t>
         </is>
       </c>
       <c r="B339" s="28" t="inlineStr">
@@ -51184,7 +51204,7 @@
       </c>
       <c r="E339" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile — 101c-wing, shastri bhawan, new delhi</t>
+          <t>Whos Who · desktop — shri b l verma</t>
         </is>
       </c>
       <c r="F339" s="28" t="inlineStr">
@@ -51215,7 +51235,7 @@
     <row r="340">
       <c r="A340" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-249</t>
+          <t>WEB-SCREEN-057</t>
         </is>
       </c>
       <c r="B340" s="28" t="inlineStr">
@@ -51235,7 +51255,7 @@
       </c>
       <c r="E340" s="28" t="inlineStr">
         <is>
-          <t>Whos Who · mobile — room no. 623, a-wing, shastri bhawan</t>
+          <t>Whos Who · mobile — Dr. Virendra Kumar</t>
         </is>
       </c>
       <c r="F340" s="28" t="inlineStr">
@@ -51254,7 +51274,7 @@
       <c r="K340" s="28" t="n"/>
       <c r="L340" s="28" t="inlineStr">
         <is>
-          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
         </is>
       </c>
       <c r="M340" s="28" t="inlineStr">
@@ -51266,7 +51286,7 @@
     <row r="341">
       <c r="A341" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-317</t>
+          <t>WEB-SCREEN-058</t>
         </is>
       </c>
       <c r="B341" s="28" t="inlineStr">
@@ -51286,7 +51306,7 @@
       </c>
       <c r="E341" s="28" t="inlineStr">
         <is>
-          <t>Home · mobile — Go to slide 1</t>
+          <t>Whos Who · mobile — Shri Kishor Makwana</t>
         </is>
       </c>
       <c r="F341" s="28" t="inlineStr">
@@ -51317,7 +51337,7 @@
     <row r="342">
       <c r="A342" s="27" t="inlineStr">
         <is>
-          <t>WEB-SCREEN-316</t>
+          <t>WEB-SCREEN-288</t>
         </is>
       </c>
       <c r="B342" s="28" t="inlineStr">
@@ -51337,7 +51357,7 @@
       </c>
       <c r="E342" s="28" t="inlineStr">
         <is>
-          <t>Home · mobile — Go to slide 2</t>
+          <t>Whos Who · mobile — Shri Kaishab Bihari</t>
         </is>
       </c>
       <c r="F342" s="28" t="inlineStr">
@@ -51365,8 +51385,263 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-289</t>
+        </is>
+      </c>
+      <c r="B343" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C343" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D343" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E343" s="28" t="inlineStr">
+        <is>
+          <t>Whos Who · mobile — Sadhvi Niranjan Jyoti</t>
+        </is>
+      </c>
+      <c r="F343" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G343" s="28" t="n"/>
+      <c r="H343" s="28" t="n"/>
+      <c r="I343" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J343" s="28" t="n"/>
+      <c r="K343" s="28" t="n"/>
+      <c r="L343" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+        </is>
+      </c>
+      <c r="M343" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-235</t>
+        </is>
+      </c>
+      <c r="B344" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C344" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D344" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E344" s="28" t="inlineStr">
+        <is>
+          <t>Whos Who · mobile — 101c-wing, shastri bhawan, new delhi</t>
+        </is>
+      </c>
+      <c r="F344" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G344" s="28" t="n"/>
+      <c r="H344" s="28" t="n"/>
+      <c r="I344" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J344" s="28" t="n"/>
+      <c r="K344" s="28" t="n"/>
+      <c r="L344" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+        </is>
+      </c>
+      <c r="M344" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-249</t>
+        </is>
+      </c>
+      <c r="B345" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C345" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D345" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E345" s="28" t="inlineStr">
+        <is>
+          <t>Whos Who · mobile — room no. 623, a-wing, shastri bhawan</t>
+        </is>
+      </c>
+      <c r="F345" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G345" s="28" t="n"/>
+      <c r="H345" s="28" t="n"/>
+      <c r="I345" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J345" s="28" t="n"/>
+      <c r="K345" s="28" t="n"/>
+      <c r="L345" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Withdrawn: the design text is sample content in a repeated list or data field — names, e-mail addresses, dates, figures, event or album titles — which the live page fills with real entries. It is different data, not missing interface copy.</t>
+        </is>
+      </c>
+      <c r="M345" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-317</t>
+        </is>
+      </c>
+      <c r="B346" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C346" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D346" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E346" s="28" t="inlineStr">
+        <is>
+          <t>Home · mobile — Go to slide 1</t>
+        </is>
+      </c>
+      <c r="F346" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G346" s="28" t="n"/>
+      <c r="H346" s="28" t="n"/>
+      <c r="I346" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J346" s="28" t="n"/>
+      <c r="K346" s="28" t="n"/>
+      <c r="L346" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+        </is>
+      </c>
+      <c r="M346" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="27" t="inlineStr">
+        <is>
+          <t>WEB-SCREEN-316</t>
+        </is>
+      </c>
+      <c r="B347" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C347" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D347" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E347" s="28" t="inlineStr">
+        <is>
+          <t>Home · mobile — Go to slide 2</t>
+        </is>
+      </c>
+      <c r="F347" s="28" t="inlineStr">
+        <is>
+          <t>No fix required — this finding was withdrawn.</t>
+        </is>
+      </c>
+      <c r="G347" s="28" t="n"/>
+      <c r="H347" s="28" t="n"/>
+      <c r="I347" s="28" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="J347" s="28" t="n"/>
+      <c r="K347" s="28" t="n"/>
+      <c r="L347" s="28" t="inlineStr">
+        <is>
+          <t>WITHDRAWN: Merged into WEB-GLOBAL-111 / WEB-GLOBAL-110 / WEB-GLOBAL-112, which now carries this defect together with the others of the same kind — one fix, one row.</t>
+        </is>
+      </c>
+      <c r="M347" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M342"/>
+  <autoFilter ref="A1:M347"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
